--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C873DEE1-1248-49D4-955A-3B074A73BBF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A06DEF-214E-457C-9057-A31ACC0318AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
   <sheets>
     <sheet name="Branding" sheetId="1" r:id="rId1"/>
@@ -42,10 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="77">
-  <si>
-    <t>Business Name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="79">
   <si>
     <t>Contact</t>
   </si>
@@ -273,6 +270,15 @@
   </si>
   <si>
     <t>Falcon,1253.Adas,India,54652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E: other number optional, </t>
+  </si>
+  <si>
+    <t>Items Name</t>
+  </si>
+  <si>
+    <t>Burger</t>
   </si>
 </sst>
 </file>
@@ -872,46 +878,46 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
       <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
       <c r="J1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.55000000000000004">
@@ -919,7 +925,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C2">
         <v>1254653</v>
@@ -931,22 +937,22 @@
         <v>5242332</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" t="s">
         <v>75</v>
       </c>
-      <c r="H2" t="s">
-        <v>76</v>
-      </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L2">
         <v>15</v>
@@ -974,22 +980,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
-        <v>11</v>
-      </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" t="s">
         <v>21</v>
-      </c>
-      <c r="F1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -997,10 +1003,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2">
         <v>115</v>
@@ -1014,10 +1020,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3">
         <v>55</v>
@@ -1031,10 +1037,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -1048,10 +1054,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5">
         <v>200</v>
@@ -1065,10 +1071,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6">
         <v>65</v>
@@ -1102,40 +1108,40 @@
   <sheetData>
     <row r="1" spans="1:12" s="8" customFormat="1" ht="30.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1143,13 +1149,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>
@@ -1158,17 +1164,17 @@
         <v>15</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H2" s="4">
         <v>225</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L2" s="3"/>
     </row>
@@ -1177,13 +1183,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3" s="4">
         <v>2</v>
@@ -1192,16 +1198,18 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H3" s="4">
         <v>124</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
+      <c r="K3" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1209,13 +1217,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E4" s="4">
         <v>3</v>
@@ -1224,16 +1232,18 @@
         <v>21</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H4" s="4">
         <v>521</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="K4" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1241,13 +1251,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5" s="4">
         <v>4</v>
@@ -1256,16 +1266,18 @@
         <v>17</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H5" s="4">
         <v>600</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="K5" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L5" s="3"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1273,13 +1285,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" s="4">
         <v>5</v>
@@ -1288,18 +1300,20 @@
         <v>10</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="4">
         <v>562</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K6" s="3"/>
+      <c r="K6" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1307,13 +1321,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E7" s="4">
         <v>5</v>
@@ -1322,16 +1336,18 @@
         <v>5</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H7" s="4">
         <v>532</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="K7" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L7" s="3"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1339,13 +1355,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" s="4">
         <v>4</v>
@@ -1354,16 +1370,18 @@
         <v>12</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H8" s="4">
         <v>623</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="K8" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1371,13 +1389,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E9" s="4">
         <v>3</v>
@@ -1386,16 +1404,18 @@
         <v>11</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H9" s="4">
         <v>120</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="K9" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1403,13 +1423,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" s="4">
         <v>2</v>
@@ -1418,16 +1438,18 @@
         <v>10</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H10" s="4">
         <v>154</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="K10" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1435,13 +1457,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="E11" s="4">
         <v>1</v>
@@ -1450,16 +1472,18 @@
         <v>8</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H11" s="4">
         <v>521</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="K11" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1467,13 +1491,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E12" s="4">
         <v>1</v>
@@ -1482,16 +1506,18 @@
         <v>6</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H12" s="4">
         <v>523</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="K12" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1499,13 +1525,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" s="4">
         <v>2</v>
@@ -1514,16 +1540,18 @@
         <v>35</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H13" s="4">
         <v>856</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+      <c r="K13" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1531,13 +1559,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E14" s="4">
         <v>3</v>
@@ -1546,16 +1574,18 @@
         <v>51</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H14" s="4">
         <v>162</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+      <c r="K14" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1563,13 +1593,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E15" s="4">
         <v>4</v>
@@ -1578,16 +1608,18 @@
         <v>12</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H15" s="4">
         <v>100</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+      <c r="K15" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L15" s="3"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1595,13 +1627,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E16" s="4">
         <v>5</v>
@@ -1610,18 +1642,20 @@
         <v>10</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H16" s="4">
         <v>521</v>
       </c>
       <c r="I16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K16" s="3"/>
+      <c r="K16" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L16" s="3"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1629,13 +1663,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E17" s="4">
         <v>1</v>
@@ -1644,16 +1678,18 @@
         <v>32</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H17" s="4">
         <v>125</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
+      <c r="K17" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1661,13 +1697,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E18" s="4">
         <v>2</v>
@@ -1676,16 +1712,18 @@
         <v>10</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H18" s="4">
         <v>135</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+      <c r="K18" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1693,13 +1731,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E19" s="4">
         <v>3</v>
@@ -1708,16 +1746,18 @@
         <v>5</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H19" s="4">
         <v>145</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
+      <c r="K19" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1725,13 +1765,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E20" s="4">
         <v>4</v>
@@ -1740,18 +1780,20 @@
         <v>3</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H20" s="4">
         <v>162</v>
       </c>
       <c r="I20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K20" s="3"/>
+      <c r="K20" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L20" s="3"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1759,13 +1801,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21" s="4">
         <v>5</v>
@@ -1774,21 +1816,24 @@
         <v>15</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H21" s="4">
         <v>143</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+      <c r="K21" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="L21" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" xr:uid="{069B7175-BDC1-4A87-8176-6859CF68488E}"/>
+    <hyperlink ref="K3:K21" r:id="rId2" display="https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/burgers/beef-burgers/5101579-1.jpg" xr:uid="{9D55A198-2C06-489A-B14A-CA00350356D2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1815,40 +1860,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A06DEF-214E-457C-9057-A31ACC0318AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CAE1B87-7D18-44B6-93F9-859E3157DA5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
   <sheets>
     <sheet name="Branding" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="79">
   <si>
     <t>Contact</t>
   </si>
@@ -1014,6 +1014,7 @@
       <c r="E2">
         <v>103</v>
       </c>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
@@ -1065,6 +1066,9 @@
       <c r="E5">
         <v>100</v>
       </c>
+      <c r="F5" s="2" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
@@ -1084,6 +1088,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F5" r:id="rId1" xr:uid="{36646985-90DA-4849-823A-CD1D6DB5B41A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CAE1B87-7D18-44B6-93F9-859E3157DA5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D1F9DF-6FDA-4F2B-8115-AB0F3EDAB00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
   <sheets>
     <sheet name="Branding" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="80">
   <si>
     <t>Contact</t>
   </si>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t>Burger</t>
+  </si>
+  <si>
+    <t>Social Media</t>
   </si>
 </sst>
 </file>
@@ -859,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ADBC54D-F271-4DEA-9173-59A93EEE3FAE}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.83984375" style="1"/>
@@ -870,13 +873,14 @@
     <col min="7" max="7" width="14.41796875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.20703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="39.15625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="9.9453125" customWidth="1"/>
-    <col min="12" max="12" width="13.20703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.3671875" customWidth="1"/>
-    <col min="14" max="14" width="12.15625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="39.15625" customWidth="1"/>
+    <col min="11" max="12" width="9.9453125" customWidth="1"/>
+    <col min="13" max="13" width="13.20703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.3671875" customWidth="1"/>
+    <col min="15" max="15" width="12.15625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -905,22 +909,25 @@
         <v>7</v>
       </c>
       <c r="J1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K1" t="s">
         <v>18</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>68</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>61</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>72</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -948,13 +955,13 @@
       <c r="I2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>69</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>15</v>
       </c>
     </row>
@@ -974,7 +981,7 @@
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="32.9453125" customWidth="1"/>
     <col min="4" max="4" width="11.3671875" customWidth="1"/>
-    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.47265625" customWidth="1"/>
     <col min="6" max="6" width="11.62890625" customWidth="1"/>
   </cols>
   <sheetData>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D1F9DF-6FDA-4F2B-8115-AB0F3EDAB00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382B2C79-5A89-48BA-AC45-8E9EC0046BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="83">
   <si>
     <t>Contact</t>
   </si>
@@ -282,6 +282,15 @@
   </si>
   <si>
     <t>Social Media</t>
+  </si>
+  <si>
+    <t>Review Map</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com,https://maps.app.goo.gl/AHQsZChqfBk3TTuV8</t>
+  </si>
+  <si>
+    <t>https://lh3.googleusercontent.com/ogw/AF2bZyhKqj5qfYsu30Iy9LeElT13L-xk7R2DVTSw7TqahGtd=s32-c-mo</t>
   </si>
 </sst>
 </file>
@@ -952,8 +961,11 @@
       <c r="H2" t="s">
         <v>75</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>8</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="K2" t="s">
         <v>19</v>
@@ -963,11 +975,16 @@
       </c>
       <c r="M2">
         <v>15</v>
+      </c>
+      <c r="N2" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{2F801368-BE40-40B3-A874-EF23D36AFEF8}"/>
+    <hyperlink ref="I2" r:id="rId2" xr:uid="{1FEE94DC-E760-44CD-B2C1-6BC052C20F3D}"/>
+    <hyperlink ref="J2" r:id="rId3" xr:uid="{E1AD14C0-21E3-4C09-A07A-B1FA633CDCCB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1104,7 +1121,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5776FB66-05B3-4E8B-A01A-C673F3C5AC7F}">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.83984375" style="1"/>
@@ -1117,10 +1134,12 @@
     <col min="8" max="8" width="8.83984375" style="1"/>
     <col min="9" max="9" width="32.83984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.68359375" customWidth="1"/>
-    <col min="11" max="11" width="26.89453125" customWidth="1"/>
+    <col min="11" max="11" width="28.20703125" customWidth="1"/>
+    <col min="12" max="12" width="10.3125" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="8" customFormat="1" ht="30.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13" s="8" customFormat="1" ht="30.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>65</v>
       </c>
@@ -1157,8 +1176,11 @@
       <c r="L1" s="6" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M1" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1191,8 +1213,11 @@
         <v>70</v>
       </c>
       <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M2" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1226,7 +1251,7 @@
       </c>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1260,7 +1285,7 @@
       </c>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -1294,7 +1319,7 @@
       </c>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -1330,7 +1355,7 @@
       </c>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -1364,7 +1389,7 @@
       </c>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -1398,7 +1423,7 @@
       </c>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -1431,8 +1456,11 @@
         <v>70</v>
       </c>
       <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M9" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -1466,7 +1494,7 @@
       </c>
       <c r="L10" s="3"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -1500,7 +1528,7 @@
       </c>
       <c r="L11" s="3"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -1534,7 +1562,7 @@
       </c>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -1568,7 +1596,7 @@
       </c>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -1602,7 +1630,7 @@
       </c>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -1636,7 +1664,7 @@
       </c>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -1671,6 +1699,9 @@
         <v>70</v>
       </c>
       <c r="L16" s="3"/>
+      <c r="M16" s="2" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="4">
@@ -1848,6 +1879,9 @@
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" xr:uid="{069B7175-BDC1-4A87-8176-6859CF68488E}"/>
     <hyperlink ref="K3:K21" r:id="rId2" display="https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/burgers/beef-burgers/5101579-1.jpg" xr:uid="{9D55A198-2C06-489A-B14A-CA00350356D2}"/>
+    <hyperlink ref="M2" r:id="rId3" xr:uid="{CC6AA61B-4B14-4866-B2B1-44E08A6246DE}"/>
+    <hyperlink ref="M9" r:id="rId4" xr:uid="{58671AAD-F2F2-47B6-9253-073208E89680}"/>
+    <hyperlink ref="M16" r:id="rId5" xr:uid="{9936B76F-B377-4FE6-9BE3-317950F81D0C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1855,7 +1889,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{514E08CF-4A2A-487B-B8DA-F4FE3F992158}">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="3.20703125" bestFit="1" customWidth="1"/>
@@ -1872,7 +1906,7 @@
     <col min="12" max="12" width="5.47265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>65</v>
       </c>
@@ -1909,8 +1943,11 @@
       <c r="L1" s="6" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M1" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1926,7 +1963,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="3"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1942,7 +1979,7 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1958,7 +1995,7 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -1974,7 +2011,7 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -1990,7 +2027,7 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -2006,7 +2043,7 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -2022,7 +2059,7 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -2038,7 +2075,7 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -2054,7 +2091,7 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -2070,7 +2107,7 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -2086,7 +2123,7 @@
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -2102,7 +2139,7 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -2118,7 +2155,7 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -2134,7 +2171,7 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4">
         <v>15</v>
       </c>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382B2C79-5A89-48BA-AC45-8E9EC0046BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB779B3-EFE7-46A8-A4DA-76DF9CF2AAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="84">
   <si>
     <t>Contact</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>https://lh3.googleusercontent.com/ogw/AF2bZyhKqj5qfYsu30Iy9LeElT13L-xk7R2DVTSw7TqahGtd=s32-c-mo</t>
+  </si>
+  <si>
+    <t>Game</t>
   </si>
 </sst>
 </file>
@@ -871,7 +874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ADBC54D-F271-4DEA-9173-59A93EEE3FAE}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.83984375" style="1"/>
@@ -889,7 +892,7 @@
     <col min="15" max="15" width="12.15625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -935,8 +938,11 @@
       <c r="O1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="P1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -978,6 +984,9 @@
       </c>
       <c r="N2" t="s">
         <v>82</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB779B3-EFE7-46A8-A4DA-76DF9CF2AAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AAC585C-A273-4BE5-82F7-2D03482D3748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
   <sheets>
     <sheet name="Branding" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="84">
   <si>
     <t>Contact</t>
   </si>
@@ -1393,9 +1393,7 @@
         <v>63</v>
       </c>
       <c r="J7" s="3"/>
-      <c r="K7" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="K7" s="2"/>
       <c r="L7" s="3"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1427,9 +1425,7 @@
         <v>63</v>
       </c>
       <c r="J8" s="3"/>
-      <c r="K8" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="K8" s="2"/>
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -1887,10 +1883,9 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" xr:uid="{069B7175-BDC1-4A87-8176-6859CF68488E}"/>
-    <hyperlink ref="K3:K21" r:id="rId2" display="https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/burgers/beef-burgers/5101579-1.jpg" xr:uid="{9D55A198-2C06-489A-B14A-CA00350356D2}"/>
-    <hyperlink ref="M2" r:id="rId3" xr:uid="{CC6AA61B-4B14-4866-B2B1-44E08A6246DE}"/>
-    <hyperlink ref="M9" r:id="rId4" xr:uid="{58671AAD-F2F2-47B6-9253-073208E89680}"/>
-    <hyperlink ref="M16" r:id="rId5" xr:uid="{9936B76F-B377-4FE6-9BE3-317950F81D0C}"/>
+    <hyperlink ref="M2" r:id="rId2" xr:uid="{CC6AA61B-4B14-4866-B2B1-44E08A6246DE}"/>
+    <hyperlink ref="M9" r:id="rId3" xr:uid="{58671AAD-F2F2-47B6-9253-073208E89680}"/>
+    <hyperlink ref="M16" r:id="rId4" xr:uid="{9936B76F-B377-4FE6-9BE3-317950F81D0C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AAC585C-A273-4BE5-82F7-2D03482D3748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54CDABC-34D8-403C-81AC-C0FA8437B0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
   <sheets>
     <sheet name="Branding" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="85">
   <si>
     <t>Contact</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t>Game</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/Banner.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1065,6 +1068,9 @@
       <c r="E3">
         <v>20</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
@@ -1100,7 +1106,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1123,6 +1129,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F5" r:id="rId1" xr:uid="{36646985-90DA-4849-823A-CD1D6DB5B41A}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{A1250854-E734-4599-AFB8-95F5375F4F23}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54CDABC-34D8-403C-81AC-C0FA8437B0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B0EBE9-17F4-442F-8388-398F0CC753C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
@@ -296,7 +296,7 @@
     <t>Game</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/Banner.jpeg</t>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/branding/Banner.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1128,8 +1128,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F5" r:id="rId1" xr:uid="{36646985-90DA-4849-823A-CD1D6DB5B41A}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{A1250854-E734-4599-AFB8-95F5375F4F23}"/>
+    <hyperlink ref="F3" r:id="rId1" xr:uid="{A1250854-E734-4599-AFB8-95F5375F4F23}"/>
+    <hyperlink ref="F5" r:id="rId2" xr:uid="{5B6ACCA9-437B-4F9A-9CB2-C2B93F023C17}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B0EBE9-17F4-442F-8388-398F0CC753C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DEA3B1-9579-4851-A4C1-1A69728EBDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
   <sheets>
     <sheet name="Branding" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="85">
   <si>
     <t>Contact</t>
   </si>
@@ -985,8 +985,11 @@
       <c r="M2">
         <v>15</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="2" t="s">
         <v>82</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -997,6 +1000,8 @@
     <hyperlink ref="F2" r:id="rId1" xr:uid="{2F801368-BE40-40B3-A874-EF23D36AFEF8}"/>
     <hyperlink ref="I2" r:id="rId2" xr:uid="{1FEE94DC-E760-44CD-B2C1-6BC052C20F3D}"/>
     <hyperlink ref="J2" r:id="rId3" xr:uid="{E1AD14C0-21E3-4C09-A07A-B1FA633CDCCB}"/>
+    <hyperlink ref="N2" r:id="rId4" xr:uid="{DE44FFED-6D3D-4D02-BCFB-34B09E80FC50}"/>
+    <hyperlink ref="O2" r:id="rId5" xr:uid="{81AFF1C3-240D-468E-995A-5B6703C1D34C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DEA3B1-9579-4851-A4C1-1A69728EBDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{556FD467-693D-4EF9-B8D4-A57EFFF6CA8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="SpecialOffer" sheetId="2" r:id="rId2"/>
     <sheet name="Menu-English" sheetId="3" r:id="rId3"/>
     <sheet name="Menu-Arabic" sheetId="5" r:id="rId4"/>
+    <sheet name="RelatedItems" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="108">
   <si>
     <t>Contact</t>
   </si>
@@ -158,9 +159,6 @@
     <t>Ice Creams</t>
   </si>
   <si>
-    <t>Items</t>
-  </si>
-  <si>
     <t>Biriyani</t>
   </si>
   <si>
@@ -297,13 +295,85 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/branding/Banner.jpeg</t>
+  </si>
+  <si>
+    <t>ITM001</t>
+  </si>
+  <si>
+    <t>ITM002</t>
+  </si>
+  <si>
+    <t>ITM003</t>
+  </si>
+  <si>
+    <t>ITM004</t>
+  </si>
+  <si>
+    <t>ITM005</t>
+  </si>
+  <si>
+    <t>ITM006</t>
+  </si>
+  <si>
+    <t>ITM007</t>
+  </si>
+  <si>
+    <t>ITM008</t>
+  </si>
+  <si>
+    <t>ITM009</t>
+  </si>
+  <si>
+    <t>ITM010</t>
+  </si>
+  <si>
+    <t>ITM011</t>
+  </si>
+  <si>
+    <t>ITM012</t>
+  </si>
+  <si>
+    <t>ITM013</t>
+  </si>
+  <si>
+    <t>ITM014</t>
+  </si>
+  <si>
+    <t>ITM015</t>
+  </si>
+  <si>
+    <t>ITM016</t>
+  </si>
+  <si>
+    <t>ITM017</t>
+  </si>
+  <si>
+    <t>ITM018</t>
+  </si>
+  <si>
+    <t>ITM019</t>
+  </si>
+  <si>
+    <t>ITM020</t>
+  </si>
+  <si>
+    <t>Related IDs</t>
+  </si>
+  <si>
+    <t>Flash cards</t>
+  </si>
+  <si>
+    <t>Review social and Map</t>
+  </si>
+  <si>
+    <t>ItemID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -329,6 +399,12 @@
       <u/>
       <sz val="10"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -378,7 +454,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -398,6 +474,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -900,7 +985,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -924,25 +1009,25 @@
         <v>7</v>
       </c>
       <c r="J1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K1" t="s">
         <v>18</v>
       </c>
       <c r="L1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -950,7 +1035,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2">
         <v>1254653</v>
@@ -965,31 +1050,31 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" t="s">
         <v>74</v>
-      </c>
-      <c r="H2" t="s">
-        <v>75</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K2" t="s">
         <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M2">
         <v>15</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -1074,7 +1159,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1111,7 +1196,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -1142,7 +1227,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5776FB66-05B3-4E8B-A01A-C673F3C5AC7F}">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.83984375" style="1"/>
@@ -1151,18 +1236,19 @@
     <col min="4" max="4" width="17.7890625" customWidth="1"/>
     <col min="5" max="5" width="17.26171875" style="1" customWidth="1"/>
     <col min="6" max="6" width="4.9453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="71" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.62890625" customWidth="1"/>
     <col min="8" max="8" width="8.83984375" style="1"/>
     <col min="9" max="9" width="32.83984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.68359375" customWidth="1"/>
     <col min="11" max="11" width="28.20703125" customWidth="1"/>
-    <col min="12" max="12" width="10.3125" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="12" max="12" width="18.20703125" customWidth="1"/>
+    <col min="13" max="13" width="24.5234375" customWidth="1"/>
+    <col min="14" max="14" width="10.3125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="8" customFormat="1" ht="30.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:14" s="8" customFormat="1" ht="30.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>30</v>
@@ -1171,39 +1257,42 @@
         <v>31</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>15</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>21</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="4">
-        <v>1</v>
+        <v>66</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>27</v>
@@ -1212,7 +1301,7 @@
         <v>33</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>
@@ -1221,26 +1310,26 @@
         <v>15</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H2" s="4">
         <v>225</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="4">
-        <v>2</v>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>27</v>
@@ -1249,7 +1338,7 @@
         <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" s="4">
         <v>2</v>
@@ -1258,23 +1347,23 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H3" s="4">
         <v>124</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="4">
-        <v>3</v>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>27</v>
@@ -1283,7 +1372,7 @@
         <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E4" s="4">
         <v>3</v>
@@ -1292,23 +1381,23 @@
         <v>21</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H4" s="4">
         <v>521</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="4">
-        <v>4</v>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>27</v>
@@ -1317,7 +1406,7 @@
         <v>34</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5" s="4">
         <v>4</v>
@@ -1326,23 +1415,23 @@
         <v>17</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H5" s="4">
         <v>600</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="4">
-        <v>5</v>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>27</v>
@@ -1351,7 +1440,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" s="4">
         <v>5</v>
@@ -1360,34 +1449,34 @@
         <v>10</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H6" s="4">
         <v>562</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="K6" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="4">
-        <v>6</v>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="4" t="s">
+        <v>89</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" s="4">
         <v>5</v>
@@ -1396,30 +1485,33 @@
         <v>5</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H7" s="4">
         <v>532</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="2"/>
       <c r="L7" s="3"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="4">
-        <v>7</v>
+      <c r="N7" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" s="4">
         <v>4</v>
@@ -1428,30 +1520,30 @@
         <v>12</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H8" s="4">
         <v>623</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="2"/>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="4">
-        <v>8</v>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" s="4">
         <v>3</v>
@@ -1460,35 +1552,35 @@
         <v>11</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H9" s="4">
         <v>120</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="4">
-        <v>9</v>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" s="4">
         <v>2</v>
@@ -1497,32 +1589,32 @@
         <v>10</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H10" s="4">
         <v>154</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L10" s="3"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="4">
-        <v>10</v>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="E11" s="4">
         <v>1</v>
@@ -1531,32 +1623,32 @@
         <v>8</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H11" s="4">
         <v>521</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L11" s="3"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="4">
-        <v>11</v>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E12" s="4">
         <v>1</v>
@@ -1565,32 +1657,32 @@
         <v>6</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H12" s="4">
         <v>523</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="4">
-        <v>12</v>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E13" s="4">
         <v>2</v>
@@ -1599,32 +1691,32 @@
         <v>35</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H13" s="4">
         <v>856</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="4">
-        <v>13</v>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14" s="4">
         <v>3</v>
@@ -1633,32 +1725,32 @@
         <v>51</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H14" s="4">
         <v>162</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="4">
-        <v>14</v>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E15" s="4">
         <v>4</v>
@@ -1667,23 +1759,26 @@
         <v>12</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H15" s="4">
         <v>100</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="4">
-        <v>15</v>
+      <c r="N15" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>29</v>
@@ -1692,7 +1787,7 @@
         <v>35</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E16" s="4">
         <v>5</v>
@@ -1701,28 +1796,28 @@
         <v>10</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H16" s="4">
         <v>521</v>
       </c>
       <c r="I16" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="K16" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="4">
-        <v>16</v>
+      <c r="A17" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>32</v>
@@ -1731,7 +1826,7 @@
         <v>36</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E17" s="4">
         <v>1</v>
@@ -1740,23 +1835,23 @@
         <v>32</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H17" s="4">
         <v>125</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="4">
-        <v>17</v>
+      <c r="A18" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>32</v>
@@ -1765,7 +1860,7 @@
         <v>36</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E18" s="4">
         <v>2</v>
@@ -1774,23 +1869,23 @@
         <v>10</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H18" s="4">
         <v>135</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="4">
-        <v>18</v>
+      <c r="A19" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>32</v>
@@ -1799,7 +1894,7 @@
         <v>36</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E19" s="4">
         <v>3</v>
@@ -1808,23 +1903,23 @@
         <v>5</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H19" s="4">
         <v>145</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="4">
-        <v>19</v>
+      <c r="A20" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>32</v>
@@ -1833,7 +1928,7 @@
         <v>37</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" s="4">
         <v>4</v>
@@ -1842,25 +1937,25 @@
         <v>3</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H20" s="4">
         <v>162</v>
       </c>
       <c r="I20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="K20" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L20" s="3"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="4">
-        <v>20</v>
+      <c r="A21" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>32</v>
@@ -1869,7 +1964,7 @@
         <v>37</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" s="4">
         <v>5</v>
@@ -1878,26 +1973,29 @@
         <v>15</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H21" s="4">
         <v>143</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L21" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" xr:uid="{069B7175-BDC1-4A87-8176-6859CF68488E}"/>
     <hyperlink ref="M2" r:id="rId2" xr:uid="{CC6AA61B-4B14-4866-B2B1-44E08A6246DE}"/>
     <hyperlink ref="M9" r:id="rId3" xr:uid="{58671AAD-F2F2-47B6-9253-073208E89680}"/>
     <hyperlink ref="M16" r:id="rId4" xr:uid="{9936B76F-B377-4FE6-9BE3-317950F81D0C}"/>
+    <hyperlink ref="N7" r:id="rId5" xr:uid="{34EB5817-7AEF-4055-973E-042FD52EDB95}"/>
+    <hyperlink ref="N15" r:id="rId6" xr:uid="{E3E1759E-257E-4884-9127-0D5E5FB4AA12}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1908,7 +2006,7 @@
   <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="3.20703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5234375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.41796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.26171875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.15625" bestFit="1" customWidth="1"/>
@@ -1922,50 +2020,50 @@
     <col min="12" max="12" width="5.47265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>62</v>
+      <c r="H1" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>105</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>21</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="4">
-        <v>1</v>
+      <c r="A2" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1980,8 +2078,8 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="4">
-        <v>2</v>
+      <c r="A3" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1996,8 +2094,8 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="4">
-        <v>3</v>
+      <c r="A4" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -2012,8 +2110,8 @@
       <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="4">
-        <v>4</v>
+      <c r="A5" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -2028,8 +2126,8 @@
       <c r="L5" s="3"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="4">
-        <v>5</v>
+      <c r="A6" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -2044,8 +2142,8 @@
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="4">
-        <v>6</v>
+      <c r="A7" s="4" t="s">
+        <v>89</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -2060,8 +2158,8 @@
       <c r="L7" s="3"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="4">
-        <v>7</v>
+      <c r="A8" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -2076,8 +2174,8 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="4">
-        <v>8</v>
+      <c r="A9" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -2092,8 +2190,8 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="4">
-        <v>9</v>
+      <c r="A10" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -2108,8 +2206,8 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="4">
-        <v>10</v>
+      <c r="A11" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -2124,8 +2222,8 @@
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="4">
-        <v>11</v>
+      <c r="A12" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -2140,8 +2238,8 @@
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="4">
-        <v>12</v>
+      <c r="A13" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -2156,8 +2254,8 @@
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="4">
-        <v>13</v>
+      <c r="A14" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -2172,8 +2270,8 @@
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="4">
-        <v>14</v>
+      <c r="A15" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -2188,8 +2286,8 @@
       <c r="L15" s="3"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="4">
-        <v>15</v>
+      <c r="A16" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -2204,8 +2302,8 @@
       <c r="L16" s="3"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="4">
-        <v>16</v>
+      <c r="A17" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -2220,8 +2318,8 @@
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="4">
-        <v>17</v>
+      <c r="A18" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -2236,8 +2334,8 @@
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="4">
-        <v>18</v>
+      <c r="A19" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -2252,8 +2350,8 @@
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="4">
-        <v>19</v>
+      <c r="A20" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -2268,8 +2366,8 @@
       <c r="L20" s="3"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="4">
-        <v>20</v>
+      <c r="A21" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -2286,4 +2384,706 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D4CA371-CE34-405E-BD66-2ABB6E4FC501}">
+  <dimension ref="A1:M23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="8.83984375" style="1"/>
+    <col min="2" max="2" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.41796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="4">
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="9"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{556FD467-693D-4EF9-B8D4-A57EFFF6CA8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054153EF-38AD-48D1-AB4B-3795ED199A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
   <sheets>
     <sheet name="Branding" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Menu-English" sheetId="3" r:id="rId3"/>
     <sheet name="Menu-Arabic" sheetId="5" r:id="rId4"/>
     <sheet name="RelatedItems" sheetId="6" r:id="rId5"/>
+    <sheet name="Content rule" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="310">
   <si>
     <t>Contact</t>
   </si>
@@ -141,9 +142,6 @@
     <t>Sub Category</t>
   </si>
   <si>
-    <t>Desert</t>
-  </si>
-  <si>
     <t>Rice</t>
   </si>
   <si>
@@ -219,9 +217,6 @@
     <t>Price</t>
   </si>
   <si>
-    <t>Detailed descriptions for the item goes here in ths area, So please specify those data.</t>
-  </si>
-  <si>
     <t>Calories</t>
   </si>
   <si>
@@ -231,9 +226,6 @@
     <t>Recipe</t>
   </si>
   <si>
-    <t>Rice 1KG, water 500ml, Oil2ts, Salt1gm,</t>
-  </si>
-  <si>
     <t>Today Special</t>
   </si>
   <si>
@@ -276,9 +268,6 @@
     <t>Items Name</t>
   </si>
   <si>
-    <t>Burger</t>
-  </si>
-  <si>
     <t>Social Media</t>
   </si>
   <si>
@@ -357,6 +346,9 @@
     <t>ITM020</t>
   </si>
   <si>
+    <t>ITM023</t>
+  </si>
+  <si>
     <t>Related IDs</t>
   </si>
   <si>
@@ -367,13 +359,1197 @@
   </si>
   <si>
     <t>ItemID</t>
+  </si>
+  <si>
+    <t>ITM021</t>
+  </si>
+  <si>
+    <t>Breads</t>
+  </si>
+  <si>
+    <t>Kerala Porotta</t>
+  </si>
+  <si>
+    <t>Flour 500g, Water 200ml, Oil 2ts, Salt 1gm</t>
+  </si>
+  <si>
+    <t>ITM022</t>
+  </si>
+  <si>
+    <t>Idiyappam</t>
+  </si>
+  <si>
+    <t>Traditional steamed rice string hoppers</t>
+  </si>
+  <si>
+    <t>Rice flour 200g, Water 100ml, Salt 1gm</t>
+  </si>
+  <si>
+    <t>Curry</t>
+  </si>
+  <si>
+    <t>Kadala Curry</t>
+  </si>
+  <si>
+    <t>Spicy black chickpea curry</t>
+  </si>
+  <si>
+    <t>Chickpeas 200g, Onion 2, Spices 10g</t>
+  </si>
+  <si>
+    <t>ITM024</t>
+  </si>
+  <si>
+    <t>Egg Roast</t>
+  </si>
+  <si>
+    <t>Boiled eggs in a rich tomato-onion gravy</t>
+  </si>
+  <si>
+    <t>Eggs 2, Onion 2, Tomato 1, Spices 10g</t>
+  </si>
+  <si>
+    <t>ITM025</t>
+  </si>
+  <si>
+    <t>Tiffin</t>
+  </si>
+  <si>
+    <t>Masala Dosa</t>
+  </si>
+  <si>
+    <t>Crispy crepe stuffed with spiced potatoes</t>
+  </si>
+  <si>
+    <t>Rice batter 200ml, Potato 100g, Oil 1ts</t>
+  </si>
+  <si>
+    <t>ITM026</t>
+  </si>
+  <si>
+    <t>Ghee Rice (Neychoru)</t>
+  </si>
+  <si>
+    <t>Fragrant Kaima rice cooked in pure ghee</t>
+  </si>
+  <si>
+    <t>Kaima Rice 500g, Ghee 50g, Spices 5g</t>
+  </si>
+  <si>
+    <t>ITM027</t>
+  </si>
+  <si>
+    <t>Pothichoru</t>
+  </si>
+  <si>
+    <t>Traditional meal wrapped in a banana leaf</t>
+  </si>
+  <si>
+    <t>Rice 300g, Veg Curries, Omelette, Pickle</t>
+  </si>
+  <si>
+    <t>ITM028</t>
+  </si>
+  <si>
+    <t>Seafood</t>
+  </si>
+  <si>
+    <t>Ayala Fish Curry</t>
+  </si>
+  <si>
+    <t>Mackerel fish in spicy red tamarind curry</t>
+  </si>
+  <si>
+    <t>Mackerel 250g, Kokum 2, Chilli powder 10g</t>
+  </si>
+  <si>
+    <t>ITM029</t>
+  </si>
+  <si>
+    <t>Fish Pollichathu</t>
+  </si>
+  <si>
+    <t>Karimeen 1, Masala 50g, Coconut oil 2ts</t>
+  </si>
+  <si>
+    <t>ITM030</t>
+  </si>
+  <si>
+    <t>Arabian</t>
+  </si>
+  <si>
+    <t>Charcoal-grilled Arabic marinated chicken</t>
+  </si>
+  <si>
+    <t>Chicken 500g, Arabic Spices 20g, Oil 2ts</t>
+  </si>
+  <si>
+    <t>ITM031</t>
+  </si>
+  <si>
+    <t>Chicken Shawarma</t>
+  </si>
+  <si>
+    <t>Slices of roasted chicken wrapped in kuboos</t>
+  </si>
+  <si>
+    <t>Chicken 150g, Kuboos 1, Garlic Paste 20g</t>
+  </si>
+  <si>
+    <t>ITM032</t>
+  </si>
+  <si>
+    <t>Chicken 400g, Flour 100g, Oil for frying</t>
+  </si>
+  <si>
+    <t>ITM033</t>
+  </si>
+  <si>
+    <t>Beef Roast (Nadan)</t>
+  </si>
+  <si>
+    <t>Spicy Kerala-style dry beef roast</t>
+  </si>
+  <si>
+    <t>Beef 300g, Onion 2, Coconut slices 50g</t>
+  </si>
+  <si>
+    <t>ITM034</t>
+  </si>
+  <si>
+    <t>Mutton Curry</t>
+  </si>
+  <si>
+    <t>Mutton 300g, Onion 2, Tomato 1, Spices 15g</t>
+  </si>
+  <si>
+    <t>ITM035</t>
+  </si>
+  <si>
+    <t>Nadan Pathiri</t>
+  </si>
+  <si>
+    <t>Soft, thin roasted rice flour flatbread</t>
+  </si>
+  <si>
+    <t>Rice flour 200g, Water 150ml, Salt 1gm</t>
+  </si>
+  <si>
+    <t>ITM036</t>
+  </si>
+  <si>
+    <t>Fresh Lemon Mint</t>
+  </si>
+  <si>
+    <t>Refreshing blended lemon and mint cooler</t>
+  </si>
+  <si>
+    <t>Lemon 2, Mint leaves 10, Sugar 20g</t>
+  </si>
+  <si>
+    <t>ITM037</t>
+  </si>
+  <si>
+    <t>Shakes</t>
+  </si>
+  <si>
+    <t>Sharjah Shake</t>
+  </si>
+  <si>
+    <t>Classic banana and milk shake with malt</t>
+  </si>
+  <si>
+    <t>Milk 200ml, Banana 1, Horlicks 2ts</t>
+  </si>
+  <si>
+    <t>ITM038</t>
+  </si>
+  <si>
+    <t>Sulaimani</t>
+  </si>
+  <si>
+    <t>Spiced black tea with a drop of lemon</t>
+  </si>
+  <si>
+    <t>ITM039</t>
+  </si>
+  <si>
+    <t>Dessert</t>
+  </si>
+  <si>
+    <t>Mixed fresh seasonal fruits with vanilla</t>
+  </si>
+  <si>
+    <t>Fruits 150g, Ice cream 1 scoop, Nuts 10g</t>
+  </si>
+  <si>
+    <t>ITM040</t>
+  </si>
+  <si>
+    <t>Layered rose milk dessert with vermicelli</t>
+  </si>
+  <si>
+    <t>Milk 200ml, Vermicelli 20g, Basil seeds 10g</t>
+  </si>
+  <si>
+    <t>ITM041</t>
+  </si>
+  <si>
+    <t>Mixed Grill</t>
+  </si>
+  <si>
+    <t>Assortment of kebabs and grilled meats</t>
+  </si>
+  <si>
+    <t>Mutton 100g, Chicken 200g, Beef 100g</t>
+  </si>
+  <si>
+    <t>ITM042</t>
+  </si>
+  <si>
+    <t>Butter Chicken</t>
+  </si>
+  <si>
+    <t>Creamy tomato-based chicken curry</t>
+  </si>
+  <si>
+    <t>Chicken 300g, Butter 50g, Tomato puree</t>
+  </si>
+  <si>
+    <t>ITM043</t>
+  </si>
+  <si>
+    <t>Plain Dosa</t>
+  </si>
+  <si>
+    <t>Thin and crispy savory rice crepe</t>
+  </si>
+  <si>
+    <t>Rice batter 200ml, Oil 1ts</t>
+  </si>
+  <si>
+    <t>ITM044</t>
+  </si>
+  <si>
+    <t>Fish Meals</t>
+  </si>
+  <si>
+    <t>Standard rice meal with daily fish fry</t>
+  </si>
+  <si>
+    <t>Rice 300g, Veg Curries, Fish Fry 1 pc</t>
+  </si>
+  <si>
+    <t>ITM045</t>
+  </si>
+  <si>
+    <t>Avocado Shake</t>
+  </si>
+  <si>
+    <t>Creamy fresh avocado blended with milk</t>
+  </si>
+  <si>
+    <t>Avocado 1, Milk 200ml, Honey 1ts</t>
+  </si>
+  <si>
+    <t>Traditional steamed rice flour cylinder</t>
+  </si>
+  <si>
+    <t>Rice flour 500g, Coconut 100g, Water, Salt</t>
+  </si>
+  <si>
+    <t>Soft, lace-edged fermented rice pancake</t>
+  </si>
+  <si>
+    <t>Rice 500g, Coconut milk 200ml, Yeast, Sugar</t>
+  </si>
+  <si>
+    <t>Flaky, multi-layered roasted flatbread</t>
+  </si>
+  <si>
+    <t>Traditional boiled matta rice</t>
+  </si>
+  <si>
+    <t>Matta Rice 1KG, Water, Salt</t>
+  </si>
+  <si>
+    <t>Premium white long-grain rice</t>
+  </si>
+  <si>
+    <t>White Rice 1KG, Water, Salt</t>
+  </si>
+  <si>
+    <t>Biriyani Rice</t>
+  </si>
+  <si>
+    <t>Flavorful spiced basmati rice</t>
+  </si>
+  <si>
+    <t>Basmati 1KG, Spices 20g, Ghee 50g</t>
+  </si>
+  <si>
+    <t>Authentic Malabar style chicken biriyani</t>
+  </si>
+  <si>
+    <t>Rice 500g, Chicken 300g, Spices 25g</t>
+  </si>
+  <si>
+    <t>Spicy, aromatic beef biriyani</t>
+  </si>
+  <si>
+    <t>Rice 500g, Beef 300g, Spices 30g</t>
+  </si>
+  <si>
+    <t>Pearl spot fish roasted in banana leaves</t>
+  </si>
+  <si>
+    <t>Alfaham Chicken</t>
+  </si>
+  <si>
+    <t>Broasted Chicken</t>
+  </si>
+  <si>
+    <t>Crispy fried chicken (4 Pcs) with fries</t>
+  </si>
+  <si>
+    <t>Crispy pan-fried beef with curry leaves</t>
+  </si>
+  <si>
+    <t>Beef 250g, Spices 15g, Coconut Oil</t>
+  </si>
+  <si>
+    <t>Tender mutton pieces in a rich gravy</t>
+  </si>
+  <si>
+    <t>Deep-fried spiced chicken pieces</t>
+  </si>
+  <si>
+    <t>Chicken 250g, Spices 20g, Oil for frying</t>
+  </si>
+  <si>
+    <t>Normal Tea (Black)</t>
+  </si>
+  <si>
+    <t>Classic brewed black tea</t>
+  </si>
+  <si>
+    <t>Water 150ml, Tea Leaves 5g, Sugar 10g</t>
+  </si>
+  <si>
+    <t>Milk Tea</t>
+  </si>
+  <si>
+    <t>Rich brewed tea with fresh milk</t>
+  </si>
+  <si>
+    <t>Milk 100ml, Water 50ml, Tea Leaves, Sugar</t>
+  </si>
+  <si>
+    <t>Water 150ml, Tea, Lemon, Cardamom</t>
+  </si>
+  <si>
+    <t>Black Coffee</t>
+  </si>
+  <si>
+    <t>Strong brewed black coffee</t>
+  </si>
+  <si>
+    <t>Water 150ml, Coffee Powder 10g, Sugar</t>
+  </si>
+  <si>
+    <t>Milk Coffee</t>
+  </si>
+  <si>
+    <t>Hot coffee brewed with fresh milk</t>
+  </si>
+  <si>
+    <t>Milk 150ml, Coffee Powder 10g, Sugar</t>
+  </si>
+  <si>
+    <t>Water Cup 250ml</t>
+  </si>
+  <si>
+    <t>Sealed purified drinking water cup</t>
+  </si>
+  <si>
+    <t>100% Purified Water</t>
+  </si>
+  <si>
+    <t>Water Bottle 500ml</t>
+  </si>
+  <si>
+    <t>Purified bottled drinking water</t>
+  </si>
+  <si>
+    <t>Water Bottle 1Ltr</t>
+  </si>
+  <si>
+    <t>Large purified bottled drinking water</t>
+  </si>
+  <si>
+    <t>Soft Drinks</t>
+  </si>
+  <si>
+    <t>Pepsi 330ml</t>
+  </si>
+  <si>
+    <t>Chilled carbonated cola beverage</t>
+  </si>
+  <si>
+    <t>Carbonated Water, Sugar, Color, Flavor</t>
+  </si>
+  <si>
+    <t>Coca-Cola 330ml</t>
+  </si>
+  <si>
+    <t>7 Up 330ml</t>
+  </si>
+  <si>
+    <t>Chilled lemon-lime carbonated beverage</t>
+  </si>
+  <si>
+    <t>Carbonated Water, Sugar, Lemon Flavor</t>
+  </si>
+  <si>
+    <t>Mirinda 330ml</t>
+  </si>
+  <si>
+    <t>Chilled orange carbonated beverage</t>
+  </si>
+  <si>
+    <t>Carbonated Water, Sugar, Orange Flavor</t>
+  </si>
+  <si>
+    <t>Kinza Cola 330ml</t>
+  </si>
+  <si>
+    <t>Local premium carbonated cola</t>
+  </si>
+  <si>
+    <t>Kinza Citrus 330ml</t>
+  </si>
+  <si>
+    <t>Local premium citrus soda</t>
+  </si>
+  <si>
+    <t>Carbonated Water, Sugar, Citrus Flavor</t>
+  </si>
+  <si>
+    <t>Fresh Orange Juice</t>
+  </si>
+  <si>
+    <t>Freshly squeezed orange juice</t>
+  </si>
+  <si>
+    <t>Fresh Oranges 3 pcs, Sugar syrup</t>
+  </si>
+  <si>
+    <t>Fresh Mango Juice</t>
+  </si>
+  <si>
+    <t>Thick, sweet blended mango juice</t>
+  </si>
+  <si>
+    <t>Fresh Mango 1, Water 50ml, Sugar syrup</t>
+  </si>
+  <si>
+    <t>ITM046</t>
+  </si>
+  <si>
+    <t>ITM047</t>
+  </si>
+  <si>
+    <t>ITM048</t>
+  </si>
+  <si>
+    <t>Vanilla Ice Cream</t>
+  </si>
+  <si>
+    <t>Classic creamy vanilla ice cream (2 Scoops)</t>
+  </si>
+  <si>
+    <t>Cream, Milk, Sugar, Vanilla Extract</t>
+  </si>
+  <si>
+    <t>ITM049</t>
+  </si>
+  <si>
+    <t>Strawberry Ice Cream</t>
+  </si>
+  <si>
+    <t>Sweet strawberry ice cream (2 Scoops)</t>
+  </si>
+  <si>
+    <t>Cream, Milk, Sugar, Strawberry puree</t>
+  </si>
+  <si>
+    <t>ITM050</t>
+  </si>
+  <si>
+    <t>Sweets</t>
+  </si>
+  <si>
+    <t>Fruit Salad w/ Ice Cream</t>
+  </si>
+  <si>
+    <t>ITM051</t>
+  </si>
+  <si>
+    <t>Royal Falooda</t>
+  </si>
+  <si>
+    <t>1. The Perfect Image Size &amp; Ratio</t>
+  </si>
+  <si>
+    <t>Consistency is the most important rule. Pick one aspect ratio and use it for every single food item.</t>
+  </si>
+  <si>
+    <r>
+      <t>Aspect Ratio:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4:3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Landscape) or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1:1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Square) work best for your card layouts.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Dimensions:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>800 x 600 pixels</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (for 4:3) or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>800 x 800 pixels</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (for 1:1).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Why:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> This resolution is large enough to look crisp when a desktop user clicks to expand the item modal, but small enough that it won't ruin your loading speeds.</t>
+    </r>
+  </si>
+  <si>
+    <t>2. File Size &amp; Format (Crucial)</t>
+  </si>
+  <si>
+    <t>Because GitHub Pages is hosting this for free, heavy images will make the app feel sluggish.</t>
+  </si>
+  <si>
+    <r>
+      <t>Target File Size:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Strictly under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>150KB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> per image.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Best Formats:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Save your files as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WebP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or highly compressed </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>JPG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Avoid PNGs unless you absolutely need a transparent background, as they are far too heavy.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Pro Tip:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Run your final batches through a compressor like TinyPNG or Squoosh.app before uploading them.</t>
+    </r>
+  </si>
+  <si>
+    <t>3. Video Management</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Since video files are massive, hosting raw </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> files directly on GitHub will quickly eat up your 100GB monthly bandwidth limit and cause buffering for mobile users on slow connections.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The Best Method:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Upload your food videos to YouTube, Vimeo, or Instagram Reels.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>How to use them:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Simply paste the URL of that uploaded video into the "Video" column (Column L) of your Excel sheet. Your app is already coded to display a "Watch Video" button that smartly links out to it!</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Main Promotional Banners (Top Header &amp; Inline Menu Banner)</t>
+  </si>
+  <si>
+    <t>These are the wide banners that stretch across the whole screen (like the one we just injected after the 5th category using Column O).</t>
+  </si>
+  <si>
+    <r>
+      <t>Aspect Ratio:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>16:9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Widescreen) or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3:1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Ultra-wide).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Perfect Dimensions:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1200 x 600 pixels</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1200 x 400 pixels</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The "Safe Zone" Rule:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Because a mobile phone is tall and narrow, but a desktop monitor is wide, the browser will chop off the far left and far right edges of the banner on mobile. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Always put your main focus, text, or logos dead-center in the image</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> so they never get cropped out.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Max File Size:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Keep these under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>250KB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Offer Banners (The Sliding Carousel Cards)</t>
+  </si>
+  <si>
+    <t>These are the cards that slide at the top of the menu. They don't stretch the full width of the screen; they sit inside a rounded card container.</t>
+  </si>
+  <si>
+    <r>
+      <t>Aspect Ratio:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>16:9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Standard Widescreen).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Perfect Dimensions:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>800 x 450 pixels</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Design Tip:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Since we added a dark, semi-transparent overlay over these images so the white offer text is readable, make sure the original images you upload are bright and high-contrast! If you are designing the text </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>directly onto the image itself</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (like a Photoshop flyer), leave the Excel text columns (B, C, D, E) completely blank so the code doesn't write text over your graphic.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Max File Size:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Keep these under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>150KB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -404,7 +1580,42 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -454,7 +1665,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -484,6 +1695,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -963,7 +2195,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ADBC54D-F271-4DEA-9173-59A93EEE3FAE}">
   <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.83984375" style="1"/>
     <col min="2" max="2" width="13.3671875" bestFit="1" customWidth="1"/>
@@ -980,12 +2212,12 @@
     <col min="15" max="15" width="12.15625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -1009,33 +2241,33 @@
         <v>7</v>
       </c>
       <c r="J1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K1" t="s">
         <v>18</v>
       </c>
       <c r="L1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O1" t="s">
         <v>67</v>
       </c>
-      <c r="M1" t="s">
-        <v>60</v>
-      </c>
-      <c r="N1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O1" t="s">
-        <v>70</v>
-      </c>
       <c r="P1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C2">
         <v>1254653</v>
@@ -1050,31 +2282,31 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="K2" t="s">
         <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M2">
         <v>15</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -1095,7 +2327,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7BBC53C-7D22-49C5-B4EB-590F6754435F}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="32.9453125" customWidth="1"/>
@@ -1104,7 +2336,7 @@
     <col min="6" max="6" width="11.62890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,7 +2356,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1142,7 +2374,7 @@
       </c>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1159,10 +2391,10 @@
         <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1179,7 +2411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1196,10 +2428,10 @@
         <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1227,18 +2459,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5776FB66-05B3-4E8B-A01A-C673F3C5AC7F}">
-  <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:N75"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.83984375" style="1"/>
     <col min="2" max="2" width="12.41796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.7890625" customWidth="1"/>
+    <col min="4" max="4" width="27.68359375" customWidth="1"/>
     <col min="5" max="5" width="17.26171875" style="1" customWidth="1"/>
     <col min="6" max="6" width="4.9453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.62890625" customWidth="1"/>
+    <col min="7" max="7" width="41.26171875" customWidth="1"/>
     <col min="8" max="8" width="8.83984375" style="1"/>
-    <col min="9" max="9" width="32.83984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43.89453125" customWidth="1"/>
     <col min="10" max="10" width="17.68359375" customWidth="1"/>
     <col min="11" max="11" width="28.20703125" customWidth="1"/>
     <col min="12" max="12" width="18.20703125" customWidth="1"/>
@@ -1246,9 +2478,9 @@
     <col min="14" max="14" width="10.3125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="8" customFormat="1" ht="30.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:14" s="8" customFormat="1" ht="28.8">
       <c r="A1" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>30</v>
@@ -1257,738 +2489,1985 @@
         <v>31</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>15</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="J1" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>21</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M1" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="N1" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="D2" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="15">
         <v>1</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="13">
         <v>15</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H2" s="4">
+      <c r="G2" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="H2" s="13">
         <v>225</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>62</v>
+      <c r="I2" s="14" t="s">
+        <v>203</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="4">
+      <c r="C3" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="15">
         <v>2</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="13">
         <v>20</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H3" s="4">
+      <c r="G3" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="H3" s="13">
         <v>124</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>62</v>
+      <c r="I3" s="14" t="s">
+        <v>205</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:14">
+      <c r="A4" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="C4" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="15">
         <v>3</v>
       </c>
-      <c r="F4" s="4">
-        <v>21</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H4" s="4">
-        <v>521</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>62</v>
+      <c r="F4" s="13">
+        <v>2</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="H4" s="13">
+        <v>300</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>108</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:14">
+      <c r="A5" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="C5" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="15">
         <v>4</v>
       </c>
-      <c r="F5" s="4">
-        <v>17</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H5" s="4">
-        <v>600</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>62</v>
+      <c r="F5" s="13">
+        <v>2</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H5" s="13">
+        <v>150</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:14">
+      <c r="A6" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="4">
-        <v>5</v>
-      </c>
-      <c r="F6" s="4">
-        <v>10</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H6" s="4">
-        <v>562</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>62</v>
+      <c r="C6" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="15">
+        <v>1</v>
+      </c>
+      <c r="F6" s="13">
+        <v>12</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="H6" s="13">
+        <v>350</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="4">
-        <v>5</v>
-      </c>
-      <c r="F7" s="4">
-        <v>5</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H7" s="4">
-        <v>532</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>62</v>
+    <row r="7" spans="1:14">
+      <c r="A7" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="E7" s="15">
+        <v>2</v>
+      </c>
+      <c r="F7" s="13">
+        <v>8</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="H7" s="13">
+        <v>200</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>193</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="2"/>
       <c r="L7" s="3"/>
       <c r="N7" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="4">
-        <v>4</v>
-      </c>
-      <c r="F8" s="4">
-        <v>12</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" s="4">
-        <v>623</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>62</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="15">
+        <v>1</v>
+      </c>
+      <c r="F8" s="13">
+        <v>8</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="H8" s="13">
+        <v>250</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>116</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="2"/>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="4">
-        <v>3</v>
-      </c>
-      <c r="F9" s="4">
-        <v>11</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H9" s="4">
+    <row r="9" spans="1:14">
+      <c r="A9" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" s="15">
+        <v>2</v>
+      </c>
+      <c r="F9" s="13">
+        <v>9</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="H9" s="13">
+        <v>220</v>
+      </c>
+      <c r="I9" s="14" t="s">
         <v>120</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="4">
-        <v>2</v>
-      </c>
-      <c r="F10" s="4">
-        <v>10</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H10" s="4">
-        <v>154</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>62</v>
+      <c r="E10" s="15">
+        <v>1</v>
+      </c>
+      <c r="F10" s="13">
+        <v>8</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="H10" s="13">
+        <v>521</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>208</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:14">
+      <c r="A11" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="C11" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="4">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4">
-        <v>8</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H11" s="4">
-        <v>521</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>62</v>
+      <c r="E11" s="15">
+        <v>2</v>
+      </c>
+      <c r="F11" s="13">
+        <v>10</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="H11" s="13">
+        <v>154</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>210</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L11" s="3"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="4">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4">
-        <v>6</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H12" s="4">
-        <v>523</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>62</v>
+    <row r="12" spans="1:14">
+      <c r="A12" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" s="15">
+        <v>3</v>
+      </c>
+      <c r="F12" s="13">
+        <v>12</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="H12" s="13">
+        <v>450</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>129</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="4">
-        <v>2</v>
-      </c>
-      <c r="F13" s="4">
-        <v>35</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H13" s="4">
-        <v>856</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>62</v>
+    <row r="13" spans="1:14">
+      <c r="A13" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="E13" s="15">
+        <v>1</v>
+      </c>
+      <c r="F13" s="13">
+        <v>6</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="H13" s="13">
+        <v>523</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>213</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="4">
-        <v>3</v>
-      </c>
-      <c r="F14" s="4">
-        <v>51</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H14" s="4">
-        <v>162</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>62</v>
+    <row r="14" spans="1:14">
+      <c r="A14" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="15">
+        <v>2</v>
+      </c>
+      <c r="F14" s="13">
+        <v>11</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="H14" s="13">
+        <v>620</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>215</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="4">
-        <v>4</v>
-      </c>
-      <c r="F15" s="4">
+    <row r="15" spans="1:14">
+      <c r="A15" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="15">
+        <v>3</v>
+      </c>
+      <c r="F15" s="13">
         <v>12</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H15" s="4">
-        <v>100</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>62</v>
+      <c r="G15" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="H15" s="13">
+        <v>856</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>217</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L15" s="3"/>
       <c r="N15" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="4">
-        <v>5</v>
-      </c>
-      <c r="F16" s="4">
-        <v>10</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H16" s="4">
-        <v>521</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>62</v>
+      <c r="D16" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="E16" s="15">
+        <v>1</v>
+      </c>
+      <c r="F16" s="13">
+        <v>15</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H16" s="13">
+        <v>650</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>197</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="4">
-        <v>1</v>
-      </c>
-      <c r="F17" s="4">
-        <v>32</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H17" s="4">
-        <v>125</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>62</v>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E17" s="15">
+        <v>2</v>
+      </c>
+      <c r="F17" s="13">
+        <v>18</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="H17" s="13">
+        <v>600</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>133</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="4">
-        <v>2</v>
-      </c>
-      <c r="F18" s="4">
-        <v>10</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H18" s="4">
+    <row r="18" spans="1:12">
+      <c r="A18" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>62</v>
+      <c r="D18" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="E18" s="15">
+        <v>1</v>
+      </c>
+      <c r="F18" s="13">
+        <v>15</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="H18" s="13">
+        <v>320</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>138</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L18" s="3"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="4">
-        <v>3</v>
-      </c>
-      <c r="F19" s="4">
-        <v>5</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H19" s="4">
-        <v>145</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>62</v>
+    <row r="19" spans="1:12">
+      <c r="A19" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E19" s="15">
+        <v>2</v>
+      </c>
+      <c r="F19" s="13">
+        <v>25</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="H19" s="13">
+        <v>400</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>141</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L19" s="3"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" s="4">
-        <v>4</v>
-      </c>
-      <c r="F20" s="4">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H20" s="4">
-        <v>162</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>62</v>
+    <row r="20" spans="1:12">
+      <c r="A20" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="E20" s="15">
+        <v>1</v>
+      </c>
+      <c r="F20" s="13">
+        <v>6</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="H20" s="13">
+        <v>450</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L20" s="3"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="4">
-        <v>5</v>
-      </c>
-      <c r="F21" s="4">
-        <v>15</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H21" s="4">
+    <row r="21" spans="1:12">
+      <c r="A21" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>62</v>
+      <c r="D21" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="E21" s="15">
+        <v>2</v>
+      </c>
+      <c r="F21" s="13">
+        <v>20</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="H21" s="13">
+        <v>750</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>145</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L21" s="3"/>
     </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="E22" s="15">
+        <v>3</v>
+      </c>
+      <c r="F22" s="13">
+        <v>17</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="H22" s="13">
+        <v>850</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" s="15">
+        <v>4</v>
+      </c>
+      <c r="F23" s="13">
+        <v>35</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="H23" s="13">
+        <v>900</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E24" s="15">
+        <v>1</v>
+      </c>
+      <c r="F24" s="13">
+        <v>16</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="H24" s="13">
+        <v>550</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="15">
+        <v>2</v>
+      </c>
+      <c r="F25" s="13">
+        <v>12</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="H25" s="13">
+        <v>450</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="E26" s="15">
+        <v>3</v>
+      </c>
+      <c r="F26" s="13">
+        <v>22</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="H26" s="13">
+        <v>600</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="15">
+        <v>4</v>
+      </c>
+      <c r="F27" s="13">
+        <v>10</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="H27" s="13">
+        <v>521</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="E28" s="15">
+        <v>1</v>
+      </c>
+      <c r="F28" s="13">
+        <v>20</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="H28" s="13">
+        <v>650</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="E29" s="15">
+        <v>1</v>
+      </c>
+      <c r="F29" s="13">
+        <v>2</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="H29" s="13">
+        <v>120</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E30" s="15">
+        <v>1</v>
+      </c>
+      <c r="F30" s="13">
+        <v>2</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="H30" s="13">
+        <v>5</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="E31" s="15">
+        <v>2</v>
+      </c>
+      <c r="F31" s="13">
+        <v>3</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="H31" s="13">
+        <v>65</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E32" s="15">
+        <v>3</v>
+      </c>
+      <c r="F32" s="13">
+        <v>2</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="H32" s="13">
+        <v>30</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="E33" s="15">
+        <v>1</v>
+      </c>
+      <c r="F33" s="13">
+        <v>3</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="H33" s="13">
+        <v>10</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="E34" s="15">
+        <v>2</v>
+      </c>
+      <c r="F34" s="13">
+        <v>4</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="H34" s="13">
+        <v>85</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E35" s="15">
+        <v>1</v>
+      </c>
+      <c r="F35" s="13">
+        <v>1</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="H35" s="13">
+        <v>0</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="E36" s="15">
+        <v>2</v>
+      </c>
+      <c r="F36" s="13">
+        <v>2</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="H36" s="13">
+        <v>0</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="E37" s="15">
+        <v>3</v>
+      </c>
+      <c r="F37" s="13">
+        <v>3</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="H37" s="13">
+        <v>0</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="E38" s="15">
+        <v>1</v>
+      </c>
+      <c r="F38" s="13">
+        <v>3</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="H38" s="13">
+        <v>150</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="E39" s="15">
+        <v>2</v>
+      </c>
+      <c r="F39" s="13">
+        <v>3</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="H39" s="13">
+        <v>140</v>
+      </c>
+      <c r="I39" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="E40" s="15">
+        <v>3</v>
+      </c>
+      <c r="F40" s="13">
+        <v>3</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="H40" s="13">
+        <v>140</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="E41" s="15">
+        <v>4</v>
+      </c>
+      <c r="F41" s="13">
+        <v>3</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="H41" s="13">
+        <v>160</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E42" s="15">
+        <v>5</v>
+      </c>
+      <c r="F42" s="13">
+        <v>3</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H42" s="13">
+        <v>145</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="J42" s="12"/>
+      <c r="K42" s="12"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E43" s="15">
+        <v>6</v>
+      </c>
+      <c r="F43" s="13">
+        <v>3</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="H43" s="13">
+        <v>150</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="E44" s="15">
+        <v>1</v>
+      </c>
+      <c r="F44" s="13">
+        <v>10</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="H44" s="13">
+        <v>135</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="J44" s="12"/>
+      <c r="K44" s="12"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="E45" s="15">
+        <v>2</v>
+      </c>
+      <c r="F45" s="13">
+        <v>12</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="H45" s="13">
+        <v>150</v>
+      </c>
+      <c r="I45" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="J45" s="12"/>
+      <c r="K45" s="12"/>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E46" s="15">
+        <v>3</v>
+      </c>
+      <c r="F46" s="13">
+        <v>8</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="H46" s="13">
+        <v>110</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E47" s="15">
+        <v>1</v>
+      </c>
+      <c r="F47" s="13">
+        <v>15</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="H47" s="13">
+        <v>420</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="J47" s="12"/>
+      <c r="K47" s="12"/>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="E48" s="15">
+        <v>2</v>
+      </c>
+      <c r="F48" s="13">
+        <v>12</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="H48" s="13">
+        <v>350</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="E49" s="15">
+        <v>1</v>
+      </c>
+      <c r="F49" s="13">
+        <v>5</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="H49" s="13">
+        <v>220</v>
+      </c>
+      <c r="I49" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="J49" s="12"/>
+      <c r="K49" s="12"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="E50" s="15">
+        <v>2</v>
+      </c>
+      <c r="F50" s="13">
+        <v>5</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="H50" s="13">
+        <v>210</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="J50" s="12"/>
+      <c r="K50" s="12"/>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="E51" s="15">
+        <v>1</v>
+      </c>
+      <c r="F51" s="13">
+        <v>12</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="H51" s="13">
+        <v>250</v>
+      </c>
+      <c r="I51" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="J51" s="12"/>
+      <c r="K51" s="12"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="E52" s="15">
+        <v>2</v>
+      </c>
+      <c r="F52" s="13">
+        <v>15</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="H52" s="13">
+        <v>400</v>
+      </c>
+      <c r="I52" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="J52" s="12"/>
+      <c r="K52" s="12"/>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="12"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="12"/>
+      <c r="K53" s="12"/>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="12"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="12"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="12"/>
+      <c r="K55" s="12"/>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" s="12"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="12"/>
+      <c r="K56" s="12"/>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="12"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="12"/>
+      <c r="K57" s="12"/>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="12"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="12"/>
+      <c r="K58" s="12"/>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="12"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="12"/>
+      <c r="K59" s="12"/>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" s="12"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="12"/>
+      <c r="K60" s="12"/>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="12"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="12"/>
+      <c r="K61" s="12"/>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="12"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="15"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12"/>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="12"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="12"/>
+      <c r="K63" s="12"/>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="12"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="15"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="12"/>
+      <c r="K64" s="12"/>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="12"/>
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="12"/>
+      <c r="K65" s="12"/>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="12"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="12"/>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" s="12"/>
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="15"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="12"/>
+      <c r="K67" s="12"/>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="12"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="12"/>
+      <c r="K68" s="12"/>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="12"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="14"/>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="12"/>
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="14"/>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="12"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="14"/>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="12"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="14"/>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="12"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="12"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="14"/>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="12"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="14"/>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="12"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="14"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A24:K68">
+    <sortCondition ref="B24:B68"/>
+    <sortCondition ref="C24:C68"/>
+    <sortCondition ref="A24:A68"/>
+  </sortState>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" xr:uid="{069B7175-BDC1-4A87-8176-6859CF68488E}"/>
     <hyperlink ref="M2" r:id="rId2" xr:uid="{CC6AA61B-4B14-4866-B2B1-44E08A6246DE}"/>
@@ -2004,7 +4483,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{514E08CF-4A2A-487B-B8DA-F4FE3F992158}">
   <dimension ref="A1:M21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="6.5234375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.41796875" bestFit="1" customWidth="1"/>
@@ -2020,50 +4499,50 @@
     <col min="12" max="12" width="5.47265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13">
       <c r="A1" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="E1" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>21</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>21</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2077,9 +4556,9 @@
       <c r="K2" s="2"/>
       <c r="L2" s="3"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:13">
       <c r="A3" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -2093,9 +4572,9 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:13">
       <c r="A4" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -2109,9 +4588,9 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:13">
       <c r="A5" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -2125,9 +4604,9 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:13">
       <c r="A6" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -2141,9 +4620,9 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:13">
       <c r="A7" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -2157,9 +4636,9 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:13">
       <c r="A8" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -2173,9 +4652,9 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:13">
       <c r="A9" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -2189,9 +4668,9 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:13">
       <c r="A10" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -2205,9 +4684,9 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:13">
       <c r="A11" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -2221,9 +4700,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:13">
       <c r="A12" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -2237,9 +4716,9 @@
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:13">
       <c r="A13" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -2253,9 +4732,9 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:13">
       <c r="A14" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -2269,9 +4748,9 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:13">
       <c r="A15" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -2285,9 +4764,9 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:13">
       <c r="A16" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -2301,9 +4780,9 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:12">
       <c r="A17" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -2317,9 +4796,9 @@
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -2333,9 +4812,9 @@
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:12">
       <c r="A19" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -2349,9 +4828,9 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -2365,9 +4844,9 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:12">
       <c r="A21" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -2389,25 +4868,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D4CA371-CE34-405E-BD66-2ABB6E4FC501}">
   <dimension ref="A1:M23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.83984375" style="1"/>
     <col min="2" max="2" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.41796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13">
       <c r="A1" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
@@ -2419,30 +4898,30 @@
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:13">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="G2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2450,30 +4929,30 @@
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:13">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -2481,21 +4960,21 @@
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:13">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -2506,24 +4985,24 @@
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:13">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -2533,27 +5012,27 @@
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:13">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -2562,30 +5041,30 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:13">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -2593,136 +5072,136 @@
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:13">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H8" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="J8" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H9" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="J9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:13">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H10" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:13">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="H11" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="3"/>
@@ -2730,360 +5209,551 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:13">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="H12" s="4" t="s">
+      <c r="I12" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="J12" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:13">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="J13" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:13">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>100</v>
-      </c>
       <c r="F14" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H14" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="J14" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:13">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="I15" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:13">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:13">
       <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:13">
       <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:13">
       <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:13">
       <c r="A20" s="4">
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:13">
       <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:13">
       <c r="B22" s="9"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:13">
       <c r="B23" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB5A8E43-7FC1-40A3-A55A-D265F6AD8118}">
+  <dimension ref="A1:A53"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.5234375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="17.399999999999999">
+      <c r="A1" s="16" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="17"/>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="18" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="17"/>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="18" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="17"/>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="18" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="17.399999999999999">
+      <c r="A11" s="16" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="17"/>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="17"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="18" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="17"/>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="18" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="17.399999999999999">
+      <c r="A21" s="16" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="17"/>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="18" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="17"/>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="18" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="17.399999999999999">
+      <c r="A31" s="16" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="17"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="18" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="17"/>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="18" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="17"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="18" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="17"/>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="18" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="17.399999999999999">
+      <c r="A43" s="16" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="17"/>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="18" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="17"/>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="18" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="17"/>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="18" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="17"/>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="18" t="s">
+        <v>309</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054153EF-38AD-48D1-AB4B-3795ED199A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12DF89F-047C-43B9-89CF-C31C510A54C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
   <sheets>
     <sheet name="Branding" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="Menu-English" sheetId="3" r:id="rId3"/>
     <sheet name="Menu-Arabic" sheetId="5" r:id="rId4"/>
     <sheet name="RelatedItems" sheetId="6" r:id="rId5"/>
-    <sheet name="Content rule" sheetId="7" r:id="rId6"/>
+    <sheet name="Inventory" sheetId="8" r:id="rId6"/>
+    <sheet name="Content rule" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="464">
   <si>
     <t>Contact</t>
   </si>
@@ -1543,6 +1544,468 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>ITM052</t>
+  </si>
+  <si>
+    <t>ITM053</t>
+  </si>
+  <si>
+    <t>ITM054</t>
+  </si>
+  <si>
+    <t>ITM055</t>
+  </si>
+  <si>
+    <t>ITM056</t>
+  </si>
+  <si>
+    <t>ITM057</t>
+  </si>
+  <si>
+    <t>ITM058</t>
+  </si>
+  <si>
+    <t>ITM059</t>
+  </si>
+  <si>
+    <t>ITM060</t>
+  </si>
+  <si>
+    <t>ITM061</t>
+  </si>
+  <si>
+    <t>ITM062</t>
+  </si>
+  <si>
+    <t>ITM063</t>
+  </si>
+  <si>
+    <t>ITM064</t>
+  </si>
+  <si>
+    <t>ITM065</t>
+  </si>
+  <si>
+    <t>ITM066</t>
+  </si>
+  <si>
+    <t>ITM067</t>
+  </si>
+  <si>
+    <t>ITM068</t>
+  </si>
+  <si>
+    <t>ITM069</t>
+  </si>
+  <si>
+    <t>ITM070</t>
+  </si>
+  <si>
+    <t>ITM071</t>
+  </si>
+  <si>
+    <t>ITM072</t>
+  </si>
+  <si>
+    <t>ITM073</t>
+  </si>
+  <si>
+    <t>ITM074</t>
+  </si>
+  <si>
+    <t>ITM075</t>
+  </si>
+  <si>
+    <t>ITM076</t>
+  </si>
+  <si>
+    <t>ITM077</t>
+  </si>
+  <si>
+    <t>ITM078</t>
+  </si>
+  <si>
+    <t>ITM079</t>
+  </si>
+  <si>
+    <t>ITM080</t>
+  </si>
+  <si>
+    <t>ITM081</t>
+  </si>
+  <si>
+    <t>ITM082</t>
+  </si>
+  <si>
+    <t>ITM083</t>
+  </si>
+  <si>
+    <t>ITM084</t>
+  </si>
+  <si>
+    <t>ITM085</t>
+  </si>
+  <si>
+    <t>ITM086</t>
+  </si>
+  <si>
+    <t>ITM087</t>
+  </si>
+  <si>
+    <t>ITM088</t>
+  </si>
+  <si>
+    <t>ITM089</t>
+  </si>
+  <si>
+    <t>ITM090</t>
+  </si>
+  <si>
+    <t>ITM091</t>
+  </si>
+  <si>
+    <t>ITM092</t>
+  </si>
+  <si>
+    <t>ITM093</t>
+  </si>
+  <si>
+    <t>ITM094</t>
+  </si>
+  <si>
+    <t>ITM095</t>
+  </si>
+  <si>
+    <t>ITM096</t>
+  </si>
+  <si>
+    <t>ITM097</t>
+  </si>
+  <si>
+    <t>ITM098</t>
+  </si>
+  <si>
+    <t>ITM099</t>
+  </si>
+  <si>
+    <t>ITM100</t>
+  </si>
+  <si>
+    <t>ITM101</t>
+  </si>
+  <si>
+    <t>ITM102</t>
+  </si>
+  <si>
+    <t>ITM103</t>
+  </si>
+  <si>
+    <t>ITM104</t>
+  </si>
+  <si>
+    <t>ITM105</t>
+  </si>
+  <si>
+    <t>ITM106</t>
+  </si>
+  <si>
+    <t>ITM107</t>
+  </si>
+  <si>
+    <t>ITM108</t>
+  </si>
+  <si>
+    <t>ITM109</t>
+  </si>
+  <si>
+    <t>ITM110</t>
+  </si>
+  <si>
+    <t>ITM111</t>
+  </si>
+  <si>
+    <t>ITM112</t>
+  </si>
+  <si>
+    <t>ITM113</t>
+  </si>
+  <si>
+    <t>ITM114</t>
+  </si>
+  <si>
+    <t>ITM115</t>
+  </si>
+  <si>
+    <t>ITM116</t>
+  </si>
+  <si>
+    <t>ITM117</t>
+  </si>
+  <si>
+    <t>ITM118</t>
+  </si>
+  <si>
+    <t>ITM119</t>
+  </si>
+  <si>
+    <t>ITM120</t>
+  </si>
+  <si>
+    <t>ITM121</t>
+  </si>
+  <si>
+    <t>ITM122</t>
+  </si>
+  <si>
+    <t>ITM123</t>
+  </si>
+  <si>
+    <t>ITM124</t>
+  </si>
+  <si>
+    <t>ITM125</t>
+  </si>
+  <si>
+    <t>ITM126</t>
+  </si>
+  <si>
+    <t>ITM127</t>
+  </si>
+  <si>
+    <t>ITM128</t>
+  </si>
+  <si>
+    <t>ITM129</t>
+  </si>
+  <si>
+    <t>ITM130</t>
+  </si>
+  <si>
+    <t>ITM131</t>
+  </si>
+  <si>
+    <t>ITM132</t>
+  </si>
+  <si>
+    <t>ITM133</t>
+  </si>
+  <si>
+    <t>ITM134</t>
+  </si>
+  <si>
+    <t>ITM135</t>
+  </si>
+  <si>
+    <t>ITM136</t>
+  </si>
+  <si>
+    <t>ITM137</t>
+  </si>
+  <si>
+    <t>ITM138</t>
+  </si>
+  <si>
+    <t>ITM139</t>
+  </si>
+  <si>
+    <t>ITM140</t>
+  </si>
+  <si>
+    <t>ITM141</t>
+  </si>
+  <si>
+    <t>ITM142</t>
+  </si>
+  <si>
+    <t>ITM143</t>
+  </si>
+  <si>
+    <t>ITM144</t>
+  </si>
+  <si>
+    <t>ITM145</t>
+  </si>
+  <si>
+    <t>ITM146</t>
+  </si>
+  <si>
+    <t>ITM147</t>
+  </si>
+  <si>
+    <t>ITM148</t>
+  </si>
+  <si>
+    <t>ITM149</t>
+  </si>
+  <si>
+    <t>ITM150</t>
+  </si>
+  <si>
+    <t>ITM151</t>
+  </si>
+  <si>
+    <t>ITM152</t>
+  </si>
+  <si>
+    <t>ITM153</t>
+  </si>
+  <si>
+    <t>ITM154</t>
+  </si>
+  <si>
+    <t>ITM155</t>
+  </si>
+  <si>
+    <t>ITM156</t>
+  </si>
+  <si>
+    <t>ITM157</t>
+  </si>
+  <si>
+    <t>ITM158</t>
+  </si>
+  <si>
+    <t>ITM159</t>
+  </si>
+  <si>
+    <t>ITM160</t>
+  </si>
+  <si>
+    <t>ITM161</t>
+  </si>
+  <si>
+    <t>ITM162</t>
+  </si>
+  <si>
+    <t>ITM163</t>
+  </si>
+  <si>
+    <t>ITM164</t>
+  </si>
+  <si>
+    <t>ITM165</t>
+  </si>
+  <si>
+    <t>ITM166</t>
+  </si>
+  <si>
+    <t>ITM167</t>
+  </si>
+  <si>
+    <t>ITM168</t>
+  </si>
+  <si>
+    <t>ITM169</t>
+  </si>
+  <si>
+    <t>ITM170</t>
+  </si>
+  <si>
+    <t>ITM171</t>
+  </si>
+  <si>
+    <t>ITM172</t>
+  </si>
+  <si>
+    <t>ITM173</t>
+  </si>
+  <si>
+    <t>ITM174</t>
+  </si>
+  <si>
+    <t>ITM175</t>
+  </si>
+  <si>
+    <t>ITM176</t>
+  </si>
+  <si>
+    <t>ITM177</t>
+  </si>
+  <si>
+    <t>ITM178</t>
+  </si>
+  <si>
+    <t>ITM179</t>
+  </si>
+  <si>
+    <t>ITM180</t>
+  </si>
+  <si>
+    <t>ITM181</t>
+  </si>
+  <si>
+    <t>ITM182</t>
+  </si>
+  <si>
+    <t>ITM183</t>
+  </si>
+  <si>
+    <t>ITM184</t>
+  </si>
+  <si>
+    <t>ITM185</t>
+  </si>
+  <si>
+    <t>ITM186</t>
+  </si>
+  <si>
+    <t>ITM187</t>
+  </si>
+  <si>
+    <t>ITM188</t>
+  </si>
+  <si>
+    <t>ITM189</t>
+  </si>
+  <si>
+    <t>ITM190</t>
+  </si>
+  <si>
+    <t>ITM191</t>
+  </si>
+  <si>
+    <t>ITM192</t>
+  </si>
+  <si>
+    <t>ITM193</t>
+  </si>
+  <si>
+    <t>ITM194</t>
+  </si>
+  <si>
+    <t>ITM195</t>
+  </si>
+  <si>
+    <t>ITM196</t>
+  </si>
+  <si>
+    <t>ITM197</t>
+  </si>
+  <si>
+    <t>ITM198</t>
+  </si>
+  <si>
+    <t>ITM199</t>
+  </si>
+  <si>
+    <t>ITM200</t>
+  </si>
+  <si>
+    <t>Restaurant-menu/images/FlashCard/</t>
+  </si>
+  <si>
+    <t>Restaurant-menu/images/ItemImages/</t>
+  </si>
+  <si>
+    <t>Restaurant-menu/images/Offer/</t>
+  </si>
+  <si>
+    <t>Restaurant-menu/images/branding/</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/banner/Banner01.jpg</t>
   </si>
 </sst>
 </file>
@@ -1665,7 +2128,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1696,6 +2159,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1717,6 +2183,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2326,14 +2793,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7BBC53C-7D22-49C5-B4EB-590F6754435F}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="2" max="2" width="32.89453125" customWidth="1"/>
     <col min="3" max="3" width="32.9453125" customWidth="1"/>
     <col min="4" max="4" width="11.3671875" customWidth="1"/>
     <col min="5" max="5" width="18.47265625" customWidth="1"/>
-    <col min="6" max="6" width="11.62890625" customWidth="1"/>
+    <col min="6" max="6" width="28.05078125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2391,7 +2858,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>79</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2428,7 +2895,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>79</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2448,10 +2915,36 @@
         <v>30</v>
       </c>
     </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="12" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="12" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="12" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="12" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="12"/>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="12"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F3" r:id="rId1" xr:uid="{A1250854-E734-4599-AFB8-95F5375F4F23}"/>
-    <hyperlink ref="F5" r:id="rId2" xr:uid="{5B6ACCA9-437B-4F9A-9CB2-C2B93F023C17}"/>
+    <hyperlink ref="F3" r:id="rId1" xr:uid="{52222A41-E790-4553-BF37-D311340B1ECC}"/>
+    <hyperlink ref="F5" r:id="rId2" xr:uid="{BA3A31D8-88B0-4E51-AC24-6C25A353933C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2523,31 +3016,32 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="15">
+      <c r="D2" s="13" t="str">
+        <f>VLOOKUP(A2,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Puttu</v>
+      </c>
+      <c r="E2" s="16">
         <v>1</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="14">
         <v>15</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="14">
         <v>225</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="15" t="s">
         <v>203</v>
       </c>
       <c r="J2" s="3"/>
@@ -2560,31 +3054,32 @@
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="15">
+      <c r="D3" s="13" t="str">
+        <f>VLOOKUP(A3,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Appam</v>
+      </c>
+      <c r="E3" s="16">
         <v>2</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="14">
         <v>20</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="14">
         <v>124</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="15" t="s">
         <v>205</v>
       </c>
       <c r="J3" s="3"/>
@@ -2594,31 +3089,32 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="E4" s="15">
+      <c r="D4" s="13" t="str">
+        <f>VLOOKUP(A4,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Kerala Porotta</v>
+      </c>
+      <c r="E4" s="16">
         <v>3</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="14">
         <v>2</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="14">
         <v>300</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="15" t="s">
         <v>108</v>
       </c>
       <c r="J4" s="3"/>
@@ -2628,31 +3124,32 @@
       <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D5" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="15">
+      <c r="D5" s="13" t="str">
+        <f>VLOOKUP(A5,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Idiyappam</v>
+      </c>
+      <c r="E5" s="16">
         <v>4</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="14">
         <v>2</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="14">
         <v>150</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="15" t="s">
         <v>112</v>
       </c>
       <c r="J5" s="3"/>
@@ -2662,31 +3159,32 @@
       <c r="L5" s="3"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" s="15">
+      <c r="D6" s="13" t="str">
+        <f>VLOOKUP(A6,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Masala Dosa</v>
+      </c>
+      <c r="E6" s="16">
         <v>1</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <v>12</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="14">
         <v>350</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="15" t="s">
         <v>125</v>
       </c>
       <c r="J6" s="3" t="s">
@@ -2698,66 +3196,68 @@
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="E7" s="15">
+      <c r="D7" s="13" t="str">
+        <f>VLOOKUP(A7,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Plain Dosa</v>
+      </c>
+      <c r="E7" s="16">
         <v>2</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="14">
         <v>8</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="14">
         <v>200</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="15" t="s">
         <v>193</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="2"/>
       <c r="L7" s="3"/>
       <c r="N7" s="2" t="s">
-        <v>79</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="E8" s="15">
+      <c r="D8" s="13" t="str">
+        <f>VLOOKUP(A8,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Kadala Curry</v>
+      </c>
+      <c r="E8" s="16">
         <v>1</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <v>8</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="14">
         <v>250</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="15" t="s">
         <v>116</v>
       </c>
       <c r="J8" s="3"/>
@@ -2765,31 +3265,32 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E9" s="15">
+      <c r="D9" s="13" t="str">
+        <f>VLOOKUP(A9,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Egg Roast</v>
+      </c>
+      <c r="E9" s="16">
         <v>2</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <v>9</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="14">
         <v>220</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="15" t="s">
         <v>120</v>
       </c>
       <c r="J9" s="3"/>
@@ -2802,31 +3303,32 @@
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="15">
+      <c r="D10" s="13" t="str">
+        <f>VLOOKUP(A10,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Kerala Rice</v>
+      </c>
+      <c r="E10" s="16">
         <v>1</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="14">
         <v>8</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="14">
         <v>521</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="15" t="s">
         <v>208</v>
       </c>
       <c r="J10" s="3"/>
@@ -2836,31 +3338,32 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="15">
+      <c r="D11" s="13" t="str">
+        <f>VLOOKUP(A11,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Baric Rice</v>
+      </c>
+      <c r="E11" s="16">
         <v>2</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <v>10</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="14">
         <v>154</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="15" t="s">
         <v>210</v>
       </c>
       <c r="J11" s="3"/>
@@ -2870,31 +3373,32 @@
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="E12" s="15">
+      <c r="D12" s="13" t="str">
+        <f>VLOOKUP(A12,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Ghee Rice (Neychoru)</v>
+      </c>
+      <c r="E12" s="16">
         <v>3</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="14">
         <v>12</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="14">
         <v>450</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="15" t="s">
         <v>129</v>
       </c>
       <c r="J12" s="3"/>
@@ -2904,31 +3408,32 @@
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="E13" s="15">
+      <c r="D13" s="13" t="str">
+        <f>VLOOKUP(A13,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Biriyani Rice</v>
+      </c>
+      <c r="E13" s="16">
         <v>1</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <v>6</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="14">
         <v>523</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="15" t="s">
         <v>213</v>
       </c>
       <c r="J13" s="3"/>
@@ -2938,31 +3443,32 @@
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="15">
+      <c r="D14" s="13" t="str">
+        <f>VLOOKUP(A14,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Chicken Biriyani</v>
+      </c>
+      <c r="E14" s="16">
         <v>2</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="14">
         <v>11</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="14">
         <v>620</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="15" t="s">
         <v>215</v>
       </c>
       <c r="J14" s="3"/>
@@ -2972,31 +3478,32 @@
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="15">
+      <c r="D15" s="13" t="str">
+        <f>VLOOKUP(A15,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Beef Biriyani</v>
+      </c>
+      <c r="E15" s="16">
         <v>3</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="14">
         <v>12</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="14">
         <v>856</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="15" t="s">
         <v>217</v>
       </c>
       <c r="J15" s="3"/>
@@ -3009,31 +3516,32 @@
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="E16" s="15">
+      <c r="D16" s="13" t="str">
+        <f>VLOOKUP(A16,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Fish Meals</v>
+      </c>
+      <c r="E16" s="16">
         <v>1</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="14">
         <v>15</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="14">
         <v>650</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="15" t="s">
         <v>197</v>
       </c>
       <c r="J16" s="3" t="s">
@@ -3048,31 +3556,32 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="E17" s="15">
+      <c r="D17" s="13" t="str">
+        <f>VLOOKUP(A17,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Pothichoru</v>
+      </c>
+      <c r="E17" s="16">
         <v>2</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="14">
         <v>18</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="14">
         <v>600</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="15" t="s">
         <v>133</v>
       </c>
       <c r="J17" s="3"/>
@@ -3082,31 +3591,32 @@
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="E18" s="15">
+      <c r="D18" s="13" t="str">
+        <f>VLOOKUP(A18,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Ayala Fish Curry</v>
+      </c>
+      <c r="E18" s="16">
         <v>1</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="14">
         <v>15</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="14">
         <v>320</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="I18" s="15" t="s">
         <v>138</v>
       </c>
       <c r="J18" s="3"/>
@@ -3116,31 +3626,32 @@
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19" s="15">
+      <c r="D19" s="13" t="str">
+        <f>VLOOKUP(A19,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Fish Pollichathu</v>
+      </c>
+      <c r="E19" s="16">
         <v>2</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="14">
         <v>25</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="14">
         <v>400</v>
       </c>
-      <c r="I19" s="14" t="s">
+      <c r="I19" s="15" t="s">
         <v>141</v>
       </c>
       <c r="J19" s="3"/>
@@ -3150,31 +3661,32 @@
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="E20" s="15">
+      <c r="D20" s="13" t="str">
+        <f>VLOOKUP(A20,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Chicken Shawarma</v>
+      </c>
+      <c r="E20" s="16">
         <v>1</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="14">
         <v>6</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="14">
         <v>450</v>
       </c>
-      <c r="I20" s="14" t="s">
+      <c r="I20" s="15" t="s">
         <v>149</v>
       </c>
       <c r="J20" s="3" t="s">
@@ -3186,31 +3698,32 @@
       <c r="L20" s="3"/>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="E21" s="15">
+      <c r="D21" s="13" t="str">
+        <f>VLOOKUP(A21,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Alfaham Chicken</v>
+      </c>
+      <c r="E21" s="16">
         <v>2</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="14">
         <v>20</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="G21" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="14">
         <v>750</v>
       </c>
-      <c r="I21" s="14" t="s">
+      <c r="I21" s="15" t="s">
         <v>145</v>
       </c>
       <c r="J21" s="3"/>
@@ -3220,1246 +3733,1277 @@
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="13" t="str">
+        <f>VLOOKUP(A22,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Broasted Chicken</v>
+      </c>
+      <c r="E22" s="16">
+        <v>3</v>
+      </c>
+      <c r="F22" s="14">
+        <v>17</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="H22" s="14">
+        <v>850</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D23" s="13" t="str">
+        <f>VLOOKUP(A23,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Mixed Grill</v>
+      </c>
+      <c r="E23" s="16">
+        <v>4</v>
+      </c>
+      <c r="F23" s="14">
+        <v>35</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="H23" s="14">
+        <v>900</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="13" t="str">
+        <f>VLOOKUP(A24,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Beef Roast (Nadan)</v>
+      </c>
+      <c r="E24" s="16">
+        <v>1</v>
+      </c>
+      <c r="F24" s="14">
+        <v>16</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H24" s="14">
+        <v>550</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="13" t="str">
+        <f>VLOOKUP(A25,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Beef Fry</v>
+      </c>
+      <c r="E25" s="16">
+        <v>2</v>
+      </c>
+      <c r="F25" s="14">
+        <v>12</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="H25" s="14">
+        <v>450</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="13" t="str">
+        <f>VLOOKUP(A26,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Mutton Curry</v>
+      </c>
+      <c r="E26" s="16">
+        <v>3</v>
+      </c>
+      <c r="F26" s="14">
+        <v>22</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="H26" s="14">
+        <v>600</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="13" t="str">
+        <f>VLOOKUP(A27,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Chicken Fry</v>
+      </c>
+      <c r="E27" s="16">
+        <v>4</v>
+      </c>
+      <c r="F27" s="14">
+        <v>10</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="H27" s="14">
+        <v>521</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" s="13" t="str">
+        <f>VLOOKUP(A28,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Butter Chicken</v>
+      </c>
+      <c r="E28" s="16">
+        <v>1</v>
+      </c>
+      <c r="F28" s="14">
+        <v>20</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="H28" s="14">
+        <v>650</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="13" t="str">
+        <f>VLOOKUP(A29,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Nadan Pathiri</v>
+      </c>
+      <c r="E29" s="16">
+        <v>1</v>
+      </c>
+      <c r="F29" s="14">
+        <v>2</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="H29" s="14">
+        <v>120</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="13" t="str">
+        <f>VLOOKUP(A30,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Normal Tea (Black)</v>
+      </c>
+      <c r="E30" s="16">
+        <v>1</v>
+      </c>
+      <c r="F30" s="14">
+        <v>2</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="H30" s="14">
+        <v>5</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="13" t="str">
+        <f>VLOOKUP(A31,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Milk Tea</v>
+      </c>
+      <c r="E31" s="16">
+        <v>2</v>
+      </c>
+      <c r="F31" s="14">
+        <v>3</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="H31" s="14">
+        <v>65</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="13" t="str">
+        <f>VLOOKUP(A32,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Sulaimani</v>
+      </c>
+      <c r="E32" s="16">
+        <v>3</v>
+      </c>
+      <c r="F32" s="14">
+        <v>2</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="H32" s="14">
+        <v>30</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="13" t="str">
+        <f>VLOOKUP(A33,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Black Coffee</v>
+      </c>
+      <c r="E33" s="16">
+        <v>1</v>
+      </c>
+      <c r="F33" s="14">
+        <v>3</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="H33" s="14">
+        <v>10</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" s="13" t="str">
+        <f>VLOOKUP(A34,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Milk Coffee</v>
+      </c>
+      <c r="E34" s="16">
+        <v>2</v>
+      </c>
+      <c r="F34" s="14">
+        <v>4</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="H34" s="14">
+        <v>85</v>
+      </c>
+      <c r="I34" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="13" t="str">
+        <f>VLOOKUP(A35,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Water Cup 250ml</v>
+      </c>
+      <c r="E35" s="16">
+        <v>1</v>
+      </c>
+      <c r="F35" s="14">
+        <v>1</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="H35" s="14">
+        <v>0</v>
+      </c>
+      <c r="I35" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="13" t="str">
+        <f>VLOOKUP(A36,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Water Bottle 500ml</v>
+      </c>
+      <c r="E36" s="16">
+        <v>2</v>
+      </c>
+      <c r="F36" s="14">
+        <v>2</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="H36" s="14">
+        <v>0</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="13" t="str">
+        <f>VLOOKUP(A37,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Water Bottle 1Ltr</v>
+      </c>
+      <c r="E37" s="16">
+        <v>3</v>
+      </c>
+      <c r="F37" s="14">
+        <v>3</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="H37" s="14">
+        <v>0</v>
+      </c>
+      <c r="I37" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="D38" s="13" t="str">
+        <f>VLOOKUP(A38,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Pepsi 330ml</v>
+      </c>
+      <c r="E38" s="16">
+        <v>1</v>
+      </c>
+      <c r="F38" s="14">
+        <v>3</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="H38" s="14">
+        <v>150</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="D39" s="13" t="str">
+        <f>VLOOKUP(A39,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Coca-Cola 330ml</v>
+      </c>
+      <c r="E39" s="16">
+        <v>2</v>
+      </c>
+      <c r="F39" s="14">
+        <v>3</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="H39" s="14">
+        <v>140</v>
+      </c>
+      <c r="I39" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="D40" s="13" t="str">
+        <f>VLOOKUP(A40,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>7 Up 330ml</v>
+      </c>
+      <c r="E40" s="16">
+        <v>3</v>
+      </c>
+      <c r="F40" s="14">
+        <v>3</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="H40" s="14">
+        <v>140</v>
+      </c>
+      <c r="I40" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="D41" s="13" t="str">
+        <f>VLOOKUP(A41,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Mirinda 330ml</v>
+      </c>
+      <c r="E41" s="16">
+        <v>4</v>
+      </c>
+      <c r="F41" s="14">
+        <v>3</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="H41" s="14">
+        <v>160</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="D42" s="13" t="str">
+        <f>VLOOKUP(A42,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Kinza Cola 330ml</v>
+      </c>
+      <c r="E42" s="16">
+        <v>5</v>
+      </c>
+      <c r="F42" s="14">
+        <v>3</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="H42" s="14">
+        <v>145</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="J42" s="13"/>
+      <c r="K42" s="13"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="D43" s="13" t="str">
+        <f>VLOOKUP(A43,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Kinza Citrus 330ml</v>
+      </c>
+      <c r="E43" s="16">
+        <v>6</v>
+      </c>
+      <c r="F43" s="14">
+        <v>3</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="H43" s="14">
+        <v>150</v>
+      </c>
+      <c r="I43" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="J43" s="13"/>
+      <c r="K43" s="13"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" s="13" t="str">
+        <f>VLOOKUP(A44,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Fresh Orange Juice</v>
+      </c>
+      <c r="E44" s="16">
+        <v>1</v>
+      </c>
+      <c r="F44" s="14">
+        <v>10</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="H44" s="14">
+        <v>135</v>
+      </c>
+      <c r="I44" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" s="13" t="str">
+        <f>VLOOKUP(A45,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Fresh Mango Juice</v>
+      </c>
+      <c r="E45" s="16">
+        <v>2</v>
+      </c>
+      <c r="F45" s="14">
+        <v>12</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="H45" s="14">
+        <v>150</v>
+      </c>
+      <c r="I45" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="J45" s="13"/>
+      <c r="K45" s="13"/>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="13" t="str">
+        <f>VLOOKUP(A46,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Fresh Lemon Mint</v>
+      </c>
+      <c r="E46" s="16">
+        <v>3</v>
+      </c>
+      <c r="F46" s="14">
+        <v>8</v>
+      </c>
+      <c r="G46" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="H46" s="14">
+        <v>110</v>
+      </c>
+      <c r="I46" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="J46" s="13"/>
+      <c r="K46" s="13"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="D47" s="13" t="str">
+        <f>VLOOKUP(A47,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Avocado Shake</v>
+      </c>
+      <c r="E47" s="16">
+        <v>1</v>
+      </c>
+      <c r="F47" s="14">
+        <v>15</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="H47" s="14">
+        <v>420</v>
+      </c>
+      <c r="I47" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="D48" s="13" t="str">
+        <f>VLOOKUP(A48,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Sharjah Shake</v>
+      </c>
+      <c r="E48" s="16">
+        <v>2</v>
+      </c>
+      <c r="F48" s="14">
+        <v>12</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H48" s="14">
+        <v>350</v>
+      </c>
+      <c r="I48" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="J48" s="13"/>
+      <c r="K48" s="13"/>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49" s="13" t="str">
+        <f>VLOOKUP(A49,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Vanilla Ice Cream</v>
+      </c>
+      <c r="E49" s="16">
+        <v>1</v>
+      </c>
+      <c r="F49" s="14">
+        <v>5</v>
+      </c>
+      <c r="G49" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="H49" s="14">
         <v>220</v>
       </c>
-      <c r="E22" s="15">
-        <v>3</v>
-      </c>
-      <c r="F22" s="13">
-        <v>17</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="H22" s="13">
-        <v>850</v>
-      </c>
-      <c r="I22" s="14" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="E23" s="15">
-        <v>4</v>
-      </c>
-      <c r="F23" s="13">
-        <v>35</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="H23" s="13">
-        <v>900</v>
-      </c>
-      <c r="I23" s="14" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E24" s="15">
+      <c r="I49" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="J49" s="13"/>
+      <c r="K49" s="13"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50" s="13" t="str">
+        <f>VLOOKUP(A50,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Strawberry Ice Cream</v>
+      </c>
+      <c r="E50" s="16">
+        <v>2</v>
+      </c>
+      <c r="F50" s="14">
+        <v>5</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="H50" s="14">
+        <v>210</v>
+      </c>
+      <c r="I50" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="D51" s="13" t="str">
+        <f>VLOOKUP(A51,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Fruit Salad w/ Ice Cream</v>
+      </c>
+      <c r="E51" s="16">
         <v>1</v>
       </c>
-      <c r="F24" s="13">
-        <v>16</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="H24" s="13">
-        <v>550</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E25" s="15">
+      <c r="F51" s="14">
+        <v>12</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="H51" s="14">
+        <v>250</v>
+      </c>
+      <c r="I51" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="D52" s="13" t="str">
+        <f>VLOOKUP(A52,Inventory!$B$2:$C$201,2,FALSE)</f>
+        <v>Royal Falooda</v>
+      </c>
+      <c r="E52" s="16">
         <v>2</v>
       </c>
-      <c r="F25" s="13">
-        <v>12</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="H25" s="13">
-        <v>450</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="E26" s="15">
-        <v>3</v>
-      </c>
-      <c r="F26" s="13">
-        <v>22</v>
-      </c>
-      <c r="G26" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="H26" s="13">
-        <v>600</v>
-      </c>
-      <c r="I26" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="15">
-        <v>4</v>
-      </c>
-      <c r="F27" s="13">
-        <v>10</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="H27" s="13">
-        <v>521</v>
-      </c>
-      <c r="I27" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="E28" s="15">
-        <v>1</v>
-      </c>
-      <c r="F28" s="13">
-        <v>20</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="H28" s="13">
-        <v>650</v>
-      </c>
-      <c r="I28" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="E29" s="15">
-        <v>1</v>
-      </c>
-      <c r="F29" s="13">
-        <v>2</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="H29" s="13">
-        <v>120</v>
-      </c>
-      <c r="I29" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E30" s="15">
-        <v>1</v>
-      </c>
-      <c r="F30" s="13">
-        <v>2</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="H30" s="13">
-        <v>5</v>
-      </c>
-      <c r="I30" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="E31" s="15">
-        <v>2</v>
-      </c>
-      <c r="F31" s="13">
-        <v>3</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="H31" s="13">
-        <v>65</v>
-      </c>
-      <c r="I31" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="E32" s="15">
-        <v>3</v>
-      </c>
-      <c r="F32" s="13">
-        <v>2</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="H32" s="13">
-        <v>30</v>
-      </c>
-      <c r="I32" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="E33" s="15">
-        <v>1</v>
-      </c>
-      <c r="F33" s="13">
-        <v>3</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="H33" s="13">
-        <v>10</v>
-      </c>
-      <c r="I33" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="E34" s="15">
-        <v>2</v>
-      </c>
-      <c r="F34" s="13">
-        <v>4</v>
-      </c>
-      <c r="G34" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="H34" s="13">
-        <v>85</v>
-      </c>
-      <c r="I34" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="E35" s="15">
-        <v>1</v>
-      </c>
-      <c r="F35" s="13">
-        <v>1</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="H35" s="13">
-        <v>0</v>
-      </c>
-      <c r="I35" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="E36" s="15">
-        <v>2</v>
-      </c>
-      <c r="F36" s="13">
-        <v>2</v>
-      </c>
-      <c r="G36" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="H36" s="13">
-        <v>0</v>
-      </c>
-      <c r="I36" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="E37" s="15">
-        <v>3</v>
-      </c>
-      <c r="F37" s="13">
-        <v>3</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="H37" s="13">
-        <v>0</v>
-      </c>
-      <c r="I37" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-    </row>
-    <row r="38" spans="1:11">
-      <c r="A38" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="E38" s="15">
-        <v>1</v>
-      </c>
-      <c r="F38" s="13">
-        <v>3</v>
-      </c>
-      <c r="G38" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="H38" s="13">
-        <v>150</v>
-      </c>
-      <c r="I38" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="J38" s="12"/>
-      <c r="K38" s="12"/>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="E39" s="15">
-        <v>2</v>
-      </c>
-      <c r="F39" s="13">
-        <v>3</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="H39" s="13">
-        <v>140</v>
-      </c>
-      <c r="I39" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
-    </row>
-    <row r="40" spans="1:11">
-      <c r="A40" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="E40" s="15">
-        <v>3</v>
-      </c>
-      <c r="F40" s="13">
-        <v>3</v>
-      </c>
-      <c r="G40" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="H40" s="13">
-        <v>140</v>
-      </c>
-      <c r="I40" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="J40" s="12"/>
-      <c r="K40" s="12"/>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="E41" s="15">
-        <v>4</v>
-      </c>
-      <c r="F41" s="13">
-        <v>3</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="H41" s="13">
-        <v>160</v>
-      </c>
-      <c r="I41" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="J41" s="12"/>
-      <c r="K41" s="12"/>
-    </row>
-    <row r="42" spans="1:11">
-      <c r="A42" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="E42" s="15">
-        <v>5</v>
-      </c>
-      <c r="F42" s="13">
-        <v>3</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="H42" s="13">
-        <v>145</v>
-      </c>
-      <c r="I42" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="J42" s="12"/>
-      <c r="K42" s="12"/>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="E43" s="15">
-        <v>6</v>
-      </c>
-      <c r="F43" s="13">
-        <v>3</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="H43" s="13">
-        <v>150</v>
-      </c>
-      <c r="I43" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="J43" s="12"/>
-      <c r="K43" s="12"/>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="E44" s="15">
-        <v>1</v>
-      </c>
-      <c r="F44" s="13">
-        <v>10</v>
-      </c>
-      <c r="G44" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="H44" s="13">
-        <v>135</v>
-      </c>
-      <c r="I44" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="A45" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="E45" s="15">
-        <v>2</v>
-      </c>
-      <c r="F45" s="13">
-        <v>12</v>
-      </c>
-      <c r="G45" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="H45" s="13">
-        <v>150</v>
-      </c>
-      <c r="I45" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="J45" s="12"/>
-      <c r="K45" s="12"/>
-    </row>
-    <row r="46" spans="1:11">
-      <c r="A46" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="E46" s="15">
-        <v>3</v>
-      </c>
-      <c r="F46" s="13">
-        <v>8</v>
-      </c>
-      <c r="G46" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="H46" s="13">
-        <v>110</v>
-      </c>
-      <c r="I46" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-    </row>
-    <row r="47" spans="1:11">
-      <c r="A47" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="E47" s="15">
-        <v>1</v>
-      </c>
-      <c r="F47" s="13">
+      <c r="F52" s="14">
         <v>15</v>
       </c>
-      <c r="G47" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="H47" s="13">
-        <v>420</v>
-      </c>
-      <c r="I47" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="J47" s="12"/>
-      <c r="K47" s="12"/>
-    </row>
-    <row r="48" spans="1:11">
-      <c r="A48" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="E48" s="15">
-        <v>2</v>
-      </c>
-      <c r="F48" s="13">
-        <v>12</v>
-      </c>
-      <c r="G48" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="H48" s="13">
-        <v>350</v>
-      </c>
-      <c r="I48" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="E49" s="15">
-        <v>1</v>
-      </c>
-      <c r="F49" s="13">
-        <v>5</v>
-      </c>
-      <c r="G49" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="H49" s="13">
-        <v>220</v>
-      </c>
-      <c r="I49" s="14" t="s">
-        <v>274</v>
-      </c>
-      <c r="J49" s="12"/>
-      <c r="K49" s="12"/>
-    </row>
-    <row r="50" spans="1:11">
-      <c r="A50" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="E50" s="15">
-        <v>2</v>
-      </c>
-      <c r="F50" s="13">
-        <v>5</v>
-      </c>
-      <c r="G50" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="H50" s="13">
-        <v>210</v>
-      </c>
-      <c r="I50" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
-    </row>
-    <row r="51" spans="1:11">
-      <c r="A51" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="E51" s="15">
-        <v>1</v>
-      </c>
-      <c r="F51" s="13">
-        <v>12</v>
-      </c>
-      <c r="G51" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="H51" s="13">
-        <v>250</v>
-      </c>
-      <c r="I51" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="J51" s="12"/>
-      <c r="K51" s="12"/>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="A52" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="E52" s="15">
-        <v>2</v>
-      </c>
-      <c r="F52" s="13">
-        <v>15</v>
-      </c>
-      <c r="G52" s="12" t="s">
+      <c r="G52" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="H52" s="13">
+      <c r="H52" s="14">
         <v>400</v>
       </c>
-      <c r="I52" s="14" t="s">
+      <c r="I52" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
+      <c r="J52" s="13"/>
+      <c r="K52" s="13"/>
     </row>
     <row r="53" spans="1:11">
-      <c r="A53" s="12"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="12"/>
-      <c r="K53" s="12"/>
+      <c r="A53" s="13"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="13"/>
+      <c r="K53" s="13"/>
     </row>
     <row r="54" spans="1:11">
-      <c r="A54" s="12"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
+      <c r="A54" s="13"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="15"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="13"/>
     </row>
     <row r="55" spans="1:11">
-      <c r="A55" s="12"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="14"/>
-      <c r="J55" s="12"/>
-      <c r="K55" s="12"/>
+      <c r="A55" s="13"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="13"/>
+      <c r="K55" s="13"/>
     </row>
     <row r="56" spans="1:11">
-      <c r="A56" s="12"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="12"/>
-      <c r="K56" s="12"/>
+      <c r="A56" s="13"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="15"/>
+      <c r="J56" s="13"/>
+      <c r="K56" s="13"/>
     </row>
     <row r="57" spans="1:11">
-      <c r="A57" s="12"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="14"/>
-      <c r="J57" s="12"/>
-      <c r="K57" s="12"/>
+      <c r="A57" s="13"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="15"/>
+      <c r="J57" s="13"/>
+      <c r="K57" s="13"/>
     </row>
     <row r="58" spans="1:11">
-      <c r="A58" s="12"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="12"/>
-      <c r="K58" s="12"/>
+      <c r="A58" s="13"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="13"/>
+      <c r="K58" s="13"/>
     </row>
     <row r="59" spans="1:11">
-      <c r="A59" s="12"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="14"/>
-      <c r="J59" s="12"/>
-      <c r="K59" s="12"/>
+      <c r="A59" s="13"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="15"/>
+      <c r="J59" s="13"/>
+      <c r="K59" s="13"/>
     </row>
     <row r="60" spans="1:11">
-      <c r="A60" s="12"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="12"/>
-      <c r="K60" s="12"/>
+      <c r="A60" s="13"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="15"/>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
     </row>
     <row r="61" spans="1:11">
-      <c r="A61" s="12"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="12"/>
-      <c r="K61" s="12"/>
+      <c r="A61" s="13"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="16"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="15"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
     </row>
     <row r="62" spans="1:11">
-      <c r="A62" s="12"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="12"/>
-      <c r="K62" s="12"/>
+      <c r="A62" s="13"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="14"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="13"/>
+      <c r="K62" s="13"/>
     </row>
     <row r="63" spans="1:11">
-      <c r="A63" s="12"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="12"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="14"/>
-      <c r="J63" s="12"/>
-      <c r="K63" s="12"/>
+      <c r="A63" s="13"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="15"/>
+      <c r="J63" s="13"/>
+      <c r="K63" s="13"/>
     </row>
     <row r="64" spans="1:11">
-      <c r="A64" s="12"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="15"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="14"/>
-      <c r="J64" s="12"/>
-      <c r="K64" s="12"/>
+      <c r="A64" s="13"/>
+      <c r="B64" s="13"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="13"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="15"/>
+      <c r="J64" s="13"/>
+      <c r="K64" s="13"/>
     </row>
     <row r="65" spans="1:11">
-      <c r="A65" s="12"/>
-      <c r="B65" s="12"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="14"/>
-      <c r="J65" s="12"/>
-      <c r="K65" s="12"/>
+      <c r="A65" s="13"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="16"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="15"/>
+      <c r="J65" s="13"/>
+      <c r="K65" s="13"/>
     </row>
     <row r="66" spans="1:11">
-      <c r="A66" s="12"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="14"/>
-      <c r="J66" s="12"/>
-      <c r="K66" s="12"/>
+      <c r="A66" s="13"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="15"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="13"/>
     </row>
     <row r="67" spans="1:11">
-      <c r="A67" s="12"/>
-      <c r="B67" s="12"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
-      <c r="E67" s="15"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="14"/>
-      <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
+      <c r="A67" s="13"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="15"/>
+      <c r="J67" s="13"/>
+      <c r="K67" s="13"/>
     </row>
     <row r="68" spans="1:11">
-      <c r="A68" s="12"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="15"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="14"/>
-      <c r="J68" s="12"/>
-      <c r="K68" s="12"/>
+      <c r="A68" s="13"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="16"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="15"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="13"/>
     </row>
     <row r="69" spans="1:11">
-      <c r="A69" s="12"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12"/>
-      <c r="E69" s="15"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="14"/>
+      <c r="A69" s="13"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="15"/>
     </row>
     <row r="70" spans="1:11">
-      <c r="A70" s="12"/>
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="14"/>
+      <c r="A70" s="13"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="15"/>
     </row>
     <row r="71" spans="1:11">
-      <c r="A71" s="12"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="12"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="14"/>
+      <c r="A71" s="13"/>
+      <c r="B71" s="13"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="15"/>
     </row>
     <row r="72" spans="1:11">
-      <c r="A72" s="12"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12"/>
-      <c r="E72" s="15"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="12"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="14"/>
+      <c r="A72" s="13"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="15"/>
     </row>
     <row r="73" spans="1:11">
-      <c r="A73" s="12"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="12"/>
-      <c r="E73" s="15"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="12"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="14"/>
+      <c r="A73" s="13"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="13"/>
+      <c r="E73" s="16"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="15"/>
     </row>
     <row r="74" spans="1:11">
-      <c r="A74" s="12"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="12"/>
-      <c r="D74" s="12"/>
-      <c r="E74" s="15"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="12"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="14"/>
+      <c r="A74" s="13"/>
+      <c r="B74" s="13"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="15"/>
     </row>
     <row r="75" spans="1:11">
-      <c r="A75" s="12"/>
-      <c r="B75" s="12"/>
-      <c r="C75" s="12"/>
-      <c r="D75" s="12"/>
-      <c r="E75" s="15"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="12"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="14"/>
+      <c r="A75" s="13"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="15"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A24:K68">
@@ -5568,6 +6112,1785 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD7D43A2-32B5-4707-8810-85425DA4CA13}">
+  <dimension ref="A1:C201"/>
+  <sheetFormatPr defaultColWidth="19.83984375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="6.5234375" customWidth="1"/>
+    <col min="2" max="2" width="9.15625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" s="13" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" s="13" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" s="13" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" s="13" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" s="13" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" s="13" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" s="13" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" s="13" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" s="13" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" s="13" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" s="13" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" s="13" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" s="13" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" s="13" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" s="13" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" s="13" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" s="13" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" s="13" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" s="13" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" s="13" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" s="13" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" s="13" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" s="13" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" s="13" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" s="13" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" s="13" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" s="13" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" s="13" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" s="13" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" s="13" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" s="13" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" s="13" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" s="13" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" s="13" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" s="13" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" s="13" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" s="13" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" s="13" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" s="13" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" s="13" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" s="13" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" s="13" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" s="13" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" s="13" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" s="13" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" s="13" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" s="13" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" s="13" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" s="13" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" s="13" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" s="13" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" s="13" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" s="13" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" s="13" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" s="13" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" s="13" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" s="13" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" s="13" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" s="13" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" s="13" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" s="13" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" s="13" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" s="13" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" s="13" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" s="13" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" s="13" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" s="13" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" s="13" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162" s="13" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163" s="13" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164" s="13" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" s="13" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166" s="13" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167" s="13" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168" s="13" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169" s="13" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170" s="13" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171" s="13" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172" s="13" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173" s="13" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174" s="13" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175" s="13" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176" s="13" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177" s="13" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178" s="13" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179" s="13" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180" s="13" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181" s="13" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182" s="13" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183" s="13" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184" s="13" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185" s="13" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186" s="13" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187" s="13" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188" s="13" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189" s="13" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190" s="13" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191" s="13" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192" s="13" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" s="13" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194" s="13" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195" s="13" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196" s="13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197" s="13" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198" s="13" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199" s="13" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200" s="13" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201" s="13" t="s">
+        <v>458</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB5A8E43-7FC1-40A3-A55A-D265F6AD8118}">
   <dimension ref="A1:A53"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5576,7 +7899,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="17.399999999999999">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>284</v>
       </c>
     </row>
@@ -5586,31 +7909,31 @@
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="17"/>
+      <c r="A4" s="18"/>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="17"/>
+      <c r="A6" s="18"/>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="17"/>
+      <c r="A8" s="18"/>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="17.399999999999999">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="17" t="s">
         <v>289</v>
       </c>
     </row>
@@ -5620,31 +7943,31 @@
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="17"/>
+      <c r="A14" s="18"/>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="19" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="17"/>
+      <c r="A16" s="18"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="19" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="17"/>
+      <c r="A18" s="18"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="19" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="17.399999999999999">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="17" t="s">
         <v>294</v>
       </c>
     </row>
@@ -5654,23 +7977,23 @@
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="17"/>
+      <c r="A24" s="18"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="19" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="17"/>
+      <c r="A26" s="18"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="19" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="17.399999999999999">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="17" t="s">
         <v>298</v>
       </c>
     </row>
@@ -5680,39 +8003,39 @@
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="17"/>
+      <c r="A34" s="18"/>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="19" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="17"/>
+      <c r="A36" s="18"/>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="18" t="s">
+      <c r="A37" s="19" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="17"/>
+      <c r="A38" s="18"/>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="19" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="17"/>
+      <c r="A40" s="18"/>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="18" t="s">
+      <c r="A41" s="19" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="17.399999999999999">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="17" t="s">
         <v>304</v>
       </c>
     </row>
@@ -5722,34 +8045,34 @@
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="17"/>
+      <c r="A46" s="18"/>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="18" t="s">
+      <c r="A47" s="19" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="17"/>
+      <c r="A48" s="18"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="18" t="s">
+      <c r="A49" s="19" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="17"/>
+      <c r="A50" s="18"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="18" t="s">
+      <c r="A51" s="19" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="17"/>
+      <c r="A52" s="18"/>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="18" t="s">
+      <c r="A53" s="19" t="s">
         <v>309</v>
       </c>
     </row>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12DF89F-047C-43B9-89CF-C31C510A54C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D40F28B-41C7-46C4-A826-5741CDEE459A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
   <sheets>
     <sheet name="Branding" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="460">
   <si>
     <t>Contact</t>
   </si>
@@ -1991,18 +1991,6 @@
   </si>
   <si>
     <t>ITM200</t>
-  </si>
-  <si>
-    <t>Restaurant-menu/images/FlashCard/</t>
-  </si>
-  <si>
-    <t>Restaurant-menu/images/ItemImages/</t>
-  </si>
-  <si>
-    <t>Restaurant-menu/images/Offer/</t>
-  </si>
-  <si>
-    <t>Restaurant-menu/images/branding/</t>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/banner/Banner01.jpg</t>
@@ -2858,7 +2846,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2895,7 +2883,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2916,24 +2904,16 @@
       </c>
     </row>
     <row r="17" spans="2:2">
-      <c r="B17" s="12" t="s">
-        <v>460</v>
-      </c>
+      <c r="B17" s="12"/>
     </row>
     <row r="18" spans="2:2">
-      <c r="B18" s="12" t="s">
-        <v>459</v>
-      </c>
+      <c r="B18" s="12"/>
     </row>
     <row r="19" spans="2:2">
-      <c r="B19" s="12" t="s">
-        <v>461</v>
-      </c>
+      <c r="B19" s="12"/>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" s="12" t="s">
-        <v>462</v>
-      </c>
+      <c r="B20" s="12"/>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="12"/>
@@ -3228,7 +3208,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="3"/>
       <c r="N7" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3512,7 +3492,7 @@
       </c>
       <c r="L15" s="3"/>
       <c r="N15" s="2" t="s">
-        <v>79</v>
+        <v>459</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -5018,7 +4998,7 @@
     <hyperlink ref="M9" r:id="rId3" xr:uid="{58671AAD-F2F2-47B6-9253-073208E89680}"/>
     <hyperlink ref="M16" r:id="rId4" xr:uid="{9936B76F-B377-4FE6-9BE3-317950F81D0C}"/>
     <hyperlink ref="N7" r:id="rId5" xr:uid="{34EB5817-7AEF-4055-973E-042FD52EDB95}"/>
-    <hyperlink ref="N15" r:id="rId6" xr:uid="{E3E1759E-257E-4884-9127-0D5E5FB4AA12}"/>
+    <hyperlink ref="N15" r:id="rId6" xr:uid="{1C256CF5-232E-4CD0-9B21-D99C0C8BE300}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D40F28B-41C7-46C4-A826-5741CDEE459A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F466E7-BD6B-4272-A12A-801048C9F77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="459">
   <si>
     <t>Contact</t>
   </si>
@@ -243,9 +243,6 @@
   </si>
   <si>
     <t>English</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/burgers/beef-burgers/5101579-1.jpg</t>
   </si>
   <si>
     <t>Banner Image</t>
@@ -2672,7 +2669,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -2696,7 +2693,7 @@
         <v>7</v>
       </c>
       <c r="J1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K1" t="s">
         <v>18</v>
@@ -2708,13 +2705,13 @@
         <v>58</v>
       </c>
       <c r="N1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -2722,7 +2719,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2">
         <v>1254653</v>
@@ -2737,16 +2734,16 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2" t="s">
         <v>70</v>
-      </c>
-      <c r="H2" t="s">
-        <v>71</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K2" t="s">
         <v>19</v>
@@ -2758,10 +2755,10 @@
         <v>15</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -2846,7 +2843,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2883,7 +2880,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2953,7 +2950,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="8" customFormat="1" ht="28.8">
       <c r="A1" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>30</v>
@@ -2962,7 +2959,7 @@
         <v>31</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>62</v>
@@ -2989,21 +2986,21 @@
         <v>63</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D2" s="13" t="str">
         <f>VLOOKUP(A2,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3016,32 +3013,30 @@
         <v>15</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H2" s="14">
         <v>225</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J2" s="3"/>
-      <c r="K2" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K2" s="2"/>
       <c r="L2" s="3"/>
       <c r="M2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D3" s="13" t="str">
         <f>VLOOKUP(A3,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3054,29 +3049,27 @@
         <v>20</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H3" s="14">
         <v>124</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J3" s="3"/>
-      <c r="K3" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K3" s="2"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D4" s="13" t="str">
         <f>VLOOKUP(A4,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3089,29 +3082,27 @@
         <v>2</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H4" s="14">
         <v>300</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K4" s="2"/>
       <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D5" s="13" t="str">
         <f>VLOOKUP(A5,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3124,29 +3115,27 @@
         <v>2</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H5" s="14">
         <v>150</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K5" s="2"/>
       <c r="L5" s="3"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D6" s="13" t="str">
         <f>VLOOKUP(A6,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3159,31 +3148,29 @@
         <v>12</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H6" s="14">
         <v>350</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K6" s="2"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D7" s="13" t="str">
         <f>VLOOKUP(A7,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3196,30 +3183,30 @@
         <v>8</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H7" s="14">
         <v>200</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="2"/>
       <c r="L7" s="3"/>
       <c r="N7" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D8" s="13" t="str">
         <f>VLOOKUP(A8,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3232,13 +3219,13 @@
         <v>8</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H8" s="14">
         <v>250</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="2"/>
@@ -3246,13 +3233,13 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D9" s="13" t="str">
         <f>VLOOKUP(A9,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3265,26 +3252,24 @@
         <v>9</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H9" s="14">
         <v>220</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J9" s="3"/>
-      <c r="K9" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K9" s="2"/>
       <c r="L9" s="3"/>
       <c r="M9" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>28</v>
@@ -3303,23 +3288,21 @@
         <v>8</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H10" s="14">
         <v>521</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J10" s="3"/>
-      <c r="K10" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K10" s="2"/>
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>28</v>
@@ -3338,23 +3321,21 @@
         <v>10</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H11" s="14">
         <v>154</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J11" s="3"/>
-      <c r="K11" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K11" s="2"/>
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>28</v>
@@ -3373,23 +3354,21 @@
         <v>12</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H12" s="14">
         <v>450</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J12" s="3"/>
-      <c r="K12" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K12" s="2"/>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>28</v>
@@ -3408,23 +3387,21 @@
         <v>6</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H13" s="14">
         <v>523</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J13" s="3"/>
-      <c r="K13" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>28</v>
@@ -3443,23 +3420,21 @@
         <v>11</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H14" s="14">
         <v>620</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J14" s="3"/>
-      <c r="K14" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K14" s="2"/>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>28</v>
@@ -3478,26 +3453,24 @@
         <v>12</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H15" s="14">
         <v>856</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J15" s="3"/>
-      <c r="K15" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K15" s="2"/>
       <c r="L15" s="3"/>
       <c r="N15" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>28</v>
@@ -3516,28 +3489,26 @@
         <v>15</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H16" s="14">
         <v>650</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K16" s="2"/>
       <c r="L16" s="3"/>
       <c r="M16" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>28</v>
@@ -3556,29 +3527,27 @@
         <v>18</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H17" s="14">
         <v>600</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J17" s="3"/>
-      <c r="K17" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K17" s="2"/>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D18" s="13" t="str">
         <f>VLOOKUP(A18,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3591,29 +3560,27 @@
         <v>15</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H18" s="14">
         <v>320</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J18" s="3"/>
-      <c r="K18" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K18" s="2"/>
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>28</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D19" s="13" t="str">
         <f>VLOOKUP(A19,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3626,29 +3593,27 @@
         <v>25</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H19" s="14">
         <v>400</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J19" s="3"/>
-      <c r="K19" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K19" s="2"/>
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D20" s="13" t="str">
         <f>VLOOKUP(A20,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3661,31 +3626,29 @@
         <v>6</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H20" s="14">
         <v>450</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K20" s="2"/>
       <c r="L20" s="3"/>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D21" s="13" t="str">
         <f>VLOOKUP(A21,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3698,29 +3661,27 @@
         <v>20</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H21" s="14">
         <v>750</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J21" s="3"/>
-      <c r="K21" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="K21" s="2"/>
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D22" s="13" t="str">
         <f>VLOOKUP(A22,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3733,24 +3694,24 @@
         <v>17</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H22" s="14">
         <v>850</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D23" s="13" t="str">
         <f>VLOOKUP(A23,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3763,18 +3724,18 @@
         <v>35</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H23" s="14">
         <v>900</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>29</v>
@@ -3793,20 +3754,20 @@
         <v>16</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H24" s="14">
         <v>550</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B25" s="13" t="s">
         <v>29</v>
@@ -3825,20 +3786,20 @@
         <v>12</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H25" s="14">
         <v>450</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J25" s="13"/>
       <c r="K25" s="13"/>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>29</v>
@@ -3857,20 +3818,20 @@
         <v>22</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H26" s="14">
         <v>600</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>29</v>
@@ -3889,26 +3850,26 @@
         <v>10</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H27" s="14">
         <v>521</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J27" s="13"/>
       <c r="K27" s="13"/>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B28" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D28" s="13" t="str">
         <f>VLOOKUP(A28,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3921,26 +3882,26 @@
         <v>20</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H28" s="14">
         <v>650</v>
       </c>
       <c r="I28" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J28" s="13"/>
       <c r="K28" s="13"/>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D29" s="13" t="str">
         <f>VLOOKUP(A29,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3953,20 +3914,20 @@
         <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H29" s="14">
         <v>120</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J29" s="13"/>
       <c r="K29" s="13"/>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>33</v>
@@ -3985,20 +3946,20 @@
         <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H30" s="14">
         <v>5</v>
       </c>
       <c r="I30" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J30" s="13"/>
       <c r="K30" s="13"/>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>33</v>
@@ -4017,20 +3978,20 @@
         <v>3</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H31" s="14">
         <v>65</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J31" s="13"/>
       <c r="K31" s="13"/>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>33</v>
@@ -4049,20 +4010,20 @@
         <v>2</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H32" s="14">
         <v>30</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J32" s="13"/>
       <c r="K32" s="13"/>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>33</v>
@@ -4081,20 +4042,20 @@
         <v>3</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H33" s="14">
         <v>10</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J33" s="13"/>
       <c r="K33" s="13"/>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>33</v>
@@ -4113,20 +4074,20 @@
         <v>4</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H34" s="14">
         <v>85</v>
       </c>
       <c r="I34" s="15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J34" s="13"/>
       <c r="K34" s="13"/>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B35" s="13" t="s">
         <v>33</v>
@@ -4145,20 +4106,20 @@
         <v>1</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H35" s="14">
         <v>0</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J35" s="13"/>
       <c r="K35" s="13"/>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B36" s="13" t="s">
         <v>33</v>
@@ -4177,20 +4138,20 @@
         <v>2</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H36" s="14">
         <v>0</v>
       </c>
       <c r="I36" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J36" s="13"/>
       <c r="K36" s="13"/>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B37" s="13" t="s">
         <v>33</v>
@@ -4209,26 +4170,26 @@
         <v>3</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H37" s="14">
         <v>0</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J37" s="13"/>
       <c r="K37" s="13"/>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B38" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D38" s="13" t="str">
         <f>VLOOKUP(A38,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4241,26 +4202,26 @@
         <v>3</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H38" s="14">
         <v>150</v>
       </c>
       <c r="I38" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J38" s="13"/>
       <c r="K38" s="13"/>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B39" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D39" s="13" t="str">
         <f>VLOOKUP(A39,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4273,26 +4234,26 @@
         <v>3</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H39" s="14">
         <v>140</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J39" s="13"/>
       <c r="K39" s="13"/>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B40" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D40" s="13" t="str">
         <f>VLOOKUP(A40,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4305,26 +4266,26 @@
         <v>3</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H40" s="14">
         <v>140</v>
       </c>
       <c r="I40" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J40" s="13"/>
       <c r="K40" s="13"/>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D41" s="13" t="str">
         <f>VLOOKUP(A41,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4337,26 +4298,26 @@
         <v>3</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H41" s="14">
         <v>160</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J41" s="13"/>
       <c r="K41" s="13"/>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D42" s="13" t="str">
         <f>VLOOKUP(A42,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4369,26 +4330,26 @@
         <v>3</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H42" s="14">
         <v>145</v>
       </c>
       <c r="I42" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J42" s="13"/>
       <c r="K42" s="13"/>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D43" s="13" t="str">
         <f>VLOOKUP(A43,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4401,20 +4362,20 @@
         <v>3</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H43" s="14">
         <v>150</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J43" s="13"/>
       <c r="K43" s="13"/>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>33</v>
@@ -4433,20 +4394,20 @@
         <v>10</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H44" s="14">
         <v>135</v>
       </c>
       <c r="I44" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J44" s="13"/>
       <c r="K44" s="13"/>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>33</v>
@@ -4465,20 +4426,20 @@
         <v>12</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H45" s="14">
         <v>150</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J45" s="13"/>
       <c r="K45" s="13"/>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B46" s="13" t="s">
         <v>33</v>
@@ -4497,26 +4458,26 @@
         <v>8</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H46" s="14">
         <v>110</v>
       </c>
       <c r="I46" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J46" s="13"/>
       <c r="K46" s="13"/>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B47" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D47" s="13" t="str">
         <f>VLOOKUP(A47,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4529,26 +4490,26 @@
         <v>15</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H47" s="14">
         <v>420</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J47" s="13"/>
       <c r="K47" s="13"/>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B48" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D48" s="13" t="str">
         <f>VLOOKUP(A48,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4561,23 +4522,23 @@
         <v>12</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H48" s="14">
         <v>350</v>
       </c>
       <c r="I48" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J48" s="13"/>
       <c r="K48" s="13"/>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>36</v>
@@ -4593,23 +4554,23 @@
         <v>5</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H49" s="14">
         <v>220</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J49" s="13"/>
       <c r="K49" s="13"/>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>36</v>
@@ -4625,26 +4586,26 @@
         <v>5</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H50" s="14">
         <v>210</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J50" s="13"/>
       <c r="K50" s="13"/>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="C51" s="13" t="s">
         <v>279</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>280</v>
       </c>
       <c r="D51" s="13" t="str">
         <f>VLOOKUP(A51,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4657,26 +4618,26 @@
         <v>12</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H51" s="14">
         <v>250</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J51" s="13"/>
       <c r="K51" s="13"/>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D52" s="13" t="str">
         <f>VLOOKUP(A52,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4689,13 +4650,13 @@
         <v>15</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H52" s="14">
         <v>400</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J52" s="13"/>
       <c r="K52" s="13"/>
@@ -4993,12 +4954,11 @@
   </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="K2" r:id="rId1" xr:uid="{069B7175-BDC1-4A87-8176-6859CF68488E}"/>
-    <hyperlink ref="M2" r:id="rId2" xr:uid="{CC6AA61B-4B14-4866-B2B1-44E08A6246DE}"/>
-    <hyperlink ref="M9" r:id="rId3" xr:uid="{58671AAD-F2F2-47B6-9253-073208E89680}"/>
-    <hyperlink ref="M16" r:id="rId4" xr:uid="{9936B76F-B377-4FE6-9BE3-317950F81D0C}"/>
-    <hyperlink ref="N7" r:id="rId5" xr:uid="{34EB5817-7AEF-4055-973E-042FD52EDB95}"/>
-    <hyperlink ref="N15" r:id="rId6" xr:uid="{1C256CF5-232E-4CD0-9B21-D99C0C8BE300}"/>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{CC6AA61B-4B14-4866-B2B1-44E08A6246DE}"/>
+    <hyperlink ref="M9" r:id="rId2" xr:uid="{58671AAD-F2F2-47B6-9253-073208E89680}"/>
+    <hyperlink ref="M16" r:id="rId3" xr:uid="{9936B76F-B377-4FE6-9BE3-317950F81D0C}"/>
+    <hyperlink ref="N7" r:id="rId4" xr:uid="{34EB5817-7AEF-4055-973E-042FD52EDB95}"/>
+    <hyperlink ref="N15" r:id="rId5" xr:uid="{1C256CF5-232E-4CD0-9B21-D99C0C8BE300}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5046,10 +5006,10 @@
         <v>63</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>60</v>
@@ -5061,12 +5021,12 @@
         <v>63</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5082,7 +5042,7 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -5098,7 +5058,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -5114,7 +5074,7 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -5130,7 +5090,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -5146,7 +5106,7 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -5162,7 +5122,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -5178,7 +5138,7 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -5194,7 +5154,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -5210,7 +5170,7 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -5226,7 +5186,7 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -5242,7 +5202,7 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -5258,7 +5218,7 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -5274,7 +5234,7 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -5290,7 +5250,7 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -5306,7 +5266,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -5322,7 +5282,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -5338,7 +5298,7 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -5354,7 +5314,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -5370,7 +5330,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -5404,13 +5364,13 @@
         <v>61</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
@@ -5430,22 +5390,22 @@
         <v>38</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -5461,22 +5421,22 @@
         <v>39</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -5492,13 +5452,13 @@
         <v>40</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -5517,16 +5477,16 @@
         <v>41</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -5544,19 +5504,19 @@
         <v>42</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="G6" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -5573,22 +5533,22 @@
         <v>45</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="G7" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -5604,37 +5564,37 @@
         <v>43</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="K8" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5645,25 +5605,25 @@
         <v>44</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="J9" s="3"/>
       <c r="L9" s="3"/>
@@ -5677,25 +5637,25 @@
         <v>50</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -5710,22 +5670,22 @@
         <v>49</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="G11" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="3"/>
@@ -5741,34 +5701,34 @@
         <v>45</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I12" s="4" t="s">
+      <c r="J12" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="K12" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M12" s="3"/>
     </row>
@@ -5780,34 +5740,34 @@
         <v>43</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E13" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I13" s="4" t="s">
+      <c r="J13" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="K13" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M13" s="3"/>
     </row>
@@ -5819,34 +5779,34 @@
         <v>44</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="H14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I14" s="4" t="s">
+      <c r="J14" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="K14" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M14" s="3"/>
     </row>
@@ -5858,25 +5818,25 @@
         <v>46</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="G15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="I15" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -5891,23 +5851,23 @@
         <v>47</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="G16" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -5922,25 +5882,25 @@
         <v>51</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="I17" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -5955,25 +5915,25 @@
         <v>52</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="H18" s="4" t="s">
+      <c r="I18" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -5988,25 +5948,25 @@
         <v>53</v>
       </c>
       <c r="C19" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -6021,25 +5981,25 @@
         <v>54</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="G20" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="I20" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
@@ -6054,25 +6014,25 @@
         <v>55</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E21" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="G21" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="I21" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
@@ -6105,10 +6065,10 @@
         <v>61</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6116,7 +6076,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>38</v>
@@ -6127,7 +6087,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>39</v>
@@ -6138,10 +6098,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6149,10 +6109,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6160,10 +6120,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6171,10 +6131,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6182,10 +6142,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6193,10 +6153,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6204,7 +6164,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>49</v>
@@ -6215,7 +6175,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>50</v>
@@ -6226,10 +6186,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6237,10 +6197,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6248,7 +6208,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>44</v>
@@ -6259,7 +6219,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>43</v>
@@ -6270,10 +6230,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6281,10 +6241,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6292,10 +6252,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6303,10 +6263,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6314,10 +6274,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6325,10 +6285,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6336,10 +6296,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6347,10 +6307,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6358,10 +6318,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6369,7 +6329,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>46</v>
@@ -6380,10 +6340,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6391,7 +6351,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>47</v>
@@ -6402,10 +6362,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6413,10 +6373,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -6424,10 +6384,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6435,10 +6395,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6446,10 +6406,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6457,10 +6417,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6468,10 +6428,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6479,10 +6439,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6490,10 +6450,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6501,10 +6461,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6512,10 +6472,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -6523,10 +6483,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -6534,10 +6494,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -6545,10 +6505,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -6556,10 +6516,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -6567,10 +6527,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -6578,10 +6538,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -6589,10 +6549,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -6600,10 +6560,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -6611,10 +6571,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -6622,10 +6582,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -6633,10 +6593,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>271</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -6644,10 +6604,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="C50" s="13" t="s">
         <v>275</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -6655,10 +6615,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -6666,10 +6626,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>282</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -6677,7 +6637,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -6685,7 +6645,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -6693,7 +6653,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -6701,7 +6661,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -6709,7 +6669,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -6717,7 +6677,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -6725,7 +6685,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -6733,7 +6693,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -6741,7 +6701,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -6749,7 +6709,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -6757,7 +6717,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -6765,7 +6725,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -6773,7 +6733,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -6781,7 +6741,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -6789,7 +6749,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -6797,7 +6757,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -6805,7 +6765,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -6813,7 +6773,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -6821,7 +6781,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -6829,7 +6789,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -6837,7 +6797,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -6845,7 +6805,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -6853,7 +6813,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -6861,7 +6821,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -6869,7 +6829,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -6877,7 +6837,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -6885,7 +6845,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -6893,7 +6853,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -6901,7 +6861,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -6909,7 +6869,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -6917,7 +6877,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -6925,7 +6885,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -6933,7 +6893,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -6941,7 +6901,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -6949,7 +6909,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -6957,7 +6917,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -6965,7 +6925,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -6973,7 +6933,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -6981,7 +6941,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -6989,7 +6949,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -6997,7 +6957,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -7005,7 +6965,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -7013,7 +6973,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -7021,7 +6981,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -7029,7 +6989,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -7037,7 +6997,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -7045,7 +7005,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -7053,7 +7013,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -7061,7 +7021,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -7069,7 +7029,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -7077,7 +7037,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -7085,7 +7045,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -7093,7 +7053,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -7101,7 +7061,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -7109,7 +7069,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -7117,7 +7077,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -7125,7 +7085,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -7133,7 +7093,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -7141,7 +7101,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="13" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -7149,7 +7109,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -7157,7 +7117,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -7165,7 +7125,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -7173,7 +7133,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -7181,7 +7141,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -7189,7 +7149,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -7197,7 +7157,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -7205,7 +7165,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -7213,7 +7173,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -7221,7 +7181,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -7229,7 +7189,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -7237,7 +7197,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -7245,7 +7205,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -7253,7 +7213,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -7261,7 +7221,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -7269,7 +7229,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -7277,7 +7237,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -7285,7 +7245,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -7293,7 +7253,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -7301,7 +7261,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="13" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -7309,7 +7269,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -7317,7 +7277,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="13" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -7325,7 +7285,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -7333,7 +7293,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -7341,7 +7301,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -7349,7 +7309,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="13" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -7357,7 +7317,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -7365,7 +7325,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -7373,7 +7333,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -7381,7 +7341,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="13" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -7389,7 +7349,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -7397,7 +7357,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -7405,7 +7365,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -7413,7 +7373,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -7421,7 +7381,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -7429,7 +7389,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -7437,7 +7397,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -7445,7 +7405,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -7453,7 +7413,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -7461,7 +7421,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -7469,7 +7429,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -7477,7 +7437,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -7485,7 +7445,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -7493,7 +7453,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -7501,7 +7461,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -7509,7 +7469,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -7517,7 +7477,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -7525,7 +7485,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -7533,7 +7493,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -7541,7 +7501,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="13" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -7549,7 +7509,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="13" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -7557,7 +7517,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="13" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -7565,7 +7525,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -7573,7 +7533,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="13" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -7581,7 +7541,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -7589,7 +7549,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="13" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -7597,7 +7557,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="13" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -7605,7 +7565,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -7613,7 +7573,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -7621,7 +7581,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -7629,7 +7589,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -7637,7 +7597,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="13" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -7645,7 +7605,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -7653,7 +7613,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -7661,7 +7621,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -7669,7 +7629,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="13" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -7677,7 +7637,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -7685,7 +7645,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -7693,7 +7653,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -7701,7 +7661,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="13" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -7709,7 +7669,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="13" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -7717,7 +7677,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -7725,7 +7685,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -7733,7 +7693,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="13" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -7741,7 +7701,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="13" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -7749,7 +7709,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="13" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -7757,7 +7717,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="13" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -7765,7 +7725,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="13" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -7773,7 +7733,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="13" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -7781,7 +7741,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="13" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -7789,7 +7749,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="13" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -7797,7 +7757,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="13" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -7805,7 +7765,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="13" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -7813,7 +7773,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="13" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -7821,7 +7781,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="13" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -7829,7 +7789,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="13" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -7837,7 +7797,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="13" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -7845,7 +7805,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="13" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -7853,7 +7813,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -7861,7 +7821,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="13" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -7880,12 +7840,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="17.399999999999999">
       <c r="A1" s="17" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -7893,7 +7853,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="19" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -7901,7 +7861,7 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -7909,17 +7869,17 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="17.399999999999999">
       <c r="A11" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -7927,7 +7887,7 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="19" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -7935,7 +7895,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="19" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -7943,17 +7903,17 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="17.399999999999999">
       <c r="A21" s="17" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -7961,7 +7921,7 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -7969,17 +7929,17 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="19" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="17.399999999999999">
       <c r="A31" s="17" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -7987,7 +7947,7 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="19" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -7995,7 +7955,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="19" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -8003,7 +7963,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -8011,17 +7971,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="17.399999999999999">
       <c r="A43" s="17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -8029,7 +7989,7 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="19" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="48" spans="1:1">
@@ -8037,7 +7997,7 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="19" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="50" spans="1:1">
@@ -8045,7 +8005,7 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="19" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -8053,7 +8013,7 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F466E7-BD6B-4272-A12A-801048C9F77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36BEC4A-3A60-429B-B5B1-6941DC8A098D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="459">
   <si>
     <t>Contact</t>
   </si>
@@ -279,9 +279,6 @@
   </si>
   <si>
     <t>Game</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/branding/Banner.jpeg</t>
   </si>
   <si>
     <t>ITM001</t>
@@ -1991,6 +1988,9 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/banner/Banner01.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg</t>
   </si>
 </sst>
 </file>
@@ -2758,7 +2758,7 @@
         <v>76</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2880,7 +2880,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2950,7 +2950,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="8" customFormat="1" ht="28.8">
       <c r="A1" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>30</v>
@@ -2986,21 +2986,21 @@
         <v>63</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D2" s="13" t="str">
         <f>VLOOKUP(A2,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3013,13 +3013,13 @@
         <v>15</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H2" s="14">
         <v>225</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="2"/>
@@ -3030,13 +3030,13 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D3" s="13" t="str">
         <f>VLOOKUP(A3,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3049,27 +3049,29 @@
         <v>20</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H3" s="14">
         <v>124</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J3" s="3"/>
-      <c r="K3" s="2"/>
+      <c r="K3" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D4" s="13" t="str">
         <f>VLOOKUP(A4,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3082,27 +3084,29 @@
         <v>2</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H4" s="14">
         <v>300</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="2"/>
+      <c r="K4" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D5" s="13" t="str">
         <f>VLOOKUP(A5,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3115,27 +3119,29 @@
         <v>2</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H5" s="14">
         <v>150</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="2"/>
+      <c r="K5" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L5" s="3"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" s="13" t="str">
         <f>VLOOKUP(A6,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3148,29 +3154,31 @@
         <v>12</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H6" s="14">
         <v>350</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K6" s="2"/>
+      <c r="K6" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D7" s="13" t="str">
         <f>VLOOKUP(A7,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3183,30 +3191,32 @@
         <v>8</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H7" s="14">
         <v>200</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J7" s="3"/>
-      <c r="K7" s="2"/>
+      <c r="K7" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L7" s="3"/>
       <c r="N7" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D8" s="13" t="str">
         <f>VLOOKUP(A8,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3219,27 +3229,29 @@
         <v>8</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H8" s="14">
         <v>250</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J8" s="3"/>
-      <c r="K8" s="2"/>
+      <c r="K8" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D9" s="13" t="str">
         <f>VLOOKUP(A9,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3252,16 +3264,18 @@
         <v>9</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H9" s="14">
         <v>220</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J9" s="3"/>
-      <c r="K9" s="2"/>
+      <c r="K9" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L9" s="3"/>
       <c r="M9" s="2" t="s">
         <v>75</v>
@@ -3269,7 +3283,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>28</v>
@@ -3288,21 +3302,23 @@
         <v>8</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H10" s="14">
         <v>521</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J10" s="3"/>
-      <c r="K10" s="2"/>
+      <c r="K10" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>28</v>
@@ -3321,21 +3337,23 @@
         <v>10</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H11" s="14">
         <v>154</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J11" s="3"/>
-      <c r="K11" s="2"/>
+      <c r="K11" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>28</v>
@@ -3354,21 +3372,23 @@
         <v>12</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H12" s="14">
         <v>450</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J12" s="3"/>
-      <c r="K12" s="2"/>
+      <c r="K12" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>28</v>
@@ -3387,21 +3407,23 @@
         <v>6</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H13" s="14">
         <v>523</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J13" s="3"/>
-      <c r="K13" s="2"/>
+      <c r="K13" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>28</v>
@@ -3420,21 +3442,23 @@
         <v>11</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H14" s="14">
         <v>620</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J14" s="3"/>
-      <c r="K14" s="2"/>
+      <c r="K14" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>28</v>
@@ -3453,24 +3477,26 @@
         <v>12</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H15" s="14">
         <v>856</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J15" s="3"/>
-      <c r="K15" s="2"/>
+      <c r="K15" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L15" s="3"/>
       <c r="N15" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>28</v>
@@ -3489,18 +3515,20 @@
         <v>15</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H16" s="14">
         <v>650</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K16" s="2"/>
+      <c r="K16" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L16" s="3"/>
       <c r="M16" s="2" t="s">
         <v>75</v>
@@ -3508,7 +3536,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>28</v>
@@ -3527,27 +3555,29 @@
         <v>18</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H17" s="14">
         <v>600</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3"/>
-      <c r="K17" s="2"/>
+      <c r="K17" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D18" s="13" t="str">
         <f>VLOOKUP(A18,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3560,27 +3590,29 @@
         <v>15</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H18" s="14">
         <v>320</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J18" s="3"/>
-      <c r="K18" s="2"/>
+      <c r="K18" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>28</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D19" s="13" t="str">
         <f>VLOOKUP(A19,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3593,27 +3625,29 @@
         <v>25</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H19" s="14">
         <v>400</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3"/>
-      <c r="K19" s="2"/>
+      <c r="K19" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D20" s="13" t="str">
         <f>VLOOKUP(A20,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3626,29 +3660,31 @@
         <v>6</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H20" s="14">
         <v>450</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K20" s="2"/>
+      <c r="K20" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L20" s="3"/>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D21" s="13" t="str">
         <f>VLOOKUP(A21,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3661,27 +3697,29 @@
         <v>20</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H21" s="14">
         <v>750</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J21" s="3"/>
-      <c r="K21" s="2"/>
+      <c r="K21" s="2" t="s">
+        <v>458</v>
+      </c>
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D22" s="13" t="str">
         <f>VLOOKUP(A22,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3694,24 +3732,27 @@
         <v>17</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H22" s="14">
         <v>850</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D23" s="13" t="str">
         <f>VLOOKUP(A23,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3724,18 +3765,21 @@
         <v>35</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H23" s="14">
         <v>900</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>29</v>
@@ -3754,20 +3798,22 @@
         <v>16</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H24" s="14">
         <v>550</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
+      <c r="K24" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B25" s="13" t="s">
         <v>29</v>
@@ -3786,20 +3832,22 @@
         <v>12</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H25" s="14">
         <v>450</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
+      <c r="K25" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>29</v>
@@ -3818,20 +3866,22 @@
         <v>22</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H26" s="14">
         <v>600</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
+      <c r="K26" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>29</v>
@@ -3850,26 +3900,28 @@
         <v>10</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H27" s="14">
         <v>521</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
+      <c r="K27" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B28" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D28" s="13" t="str">
         <f>VLOOKUP(A28,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3882,26 +3934,28 @@
         <v>20</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H28" s="14">
         <v>650</v>
       </c>
       <c r="I28" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
+      <c r="K28" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D29" s="13" t="str">
         <f>VLOOKUP(A29,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3914,20 +3968,22 @@
         <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H29" s="14">
         <v>120</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
+      <c r="K29" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>33</v>
@@ -3946,20 +4002,22 @@
         <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H30" s="14">
         <v>5</v>
       </c>
       <c r="I30" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
+      <c r="K30" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>33</v>
@@ -3978,20 +4036,22 @@
         <v>3</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H31" s="14">
         <v>65</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
+      <c r="K31" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>33</v>
@@ -4010,20 +4070,22 @@
         <v>2</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H32" s="14">
         <v>30</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
+      <c r="K32" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>33</v>
@@ -4042,20 +4104,22 @@
         <v>3</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H33" s="14">
         <v>10</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
+      <c r="K33" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>33</v>
@@ -4074,20 +4138,22 @@
         <v>4</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H34" s="14">
         <v>85</v>
       </c>
       <c r="I34" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
+      <c r="K34" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B35" s="13" t="s">
         <v>33</v>
@@ -4106,20 +4172,22 @@
         <v>1</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H35" s="14">
         <v>0</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
+      <c r="K35" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B36" s="13" t="s">
         <v>33</v>
@@ -4138,20 +4206,22 @@
         <v>2</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H36" s="14">
         <v>0</v>
       </c>
       <c r="I36" s="15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
+      <c r="K36" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B37" s="13" t="s">
         <v>33</v>
@@ -4170,26 +4240,28 @@
         <v>3</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H37" s="14">
         <v>0</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
+      <c r="K37" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B38" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D38" s="13" t="str">
         <f>VLOOKUP(A38,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4202,26 +4274,28 @@
         <v>3</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H38" s="14">
         <v>150</v>
       </c>
       <c r="I38" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
+      <c r="K38" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B39" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D39" s="13" t="str">
         <f>VLOOKUP(A39,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4234,26 +4308,28 @@
         <v>3</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H39" s="14">
         <v>140</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
+      <c r="K39" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B40" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D40" s="13" t="str">
         <f>VLOOKUP(A40,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4266,26 +4342,28 @@
         <v>3</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H40" s="14">
         <v>140</v>
       </c>
       <c r="I40" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J40" s="13"/>
-      <c r="K40" s="13"/>
+      <c r="K40" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D41" s="13" t="str">
         <f>VLOOKUP(A41,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4298,26 +4376,28 @@
         <v>3</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H41" s="14">
         <v>160</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
+      <c r="K41" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D42" s="13" t="str">
         <f>VLOOKUP(A42,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4330,26 +4410,28 @@
         <v>3</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H42" s="14">
         <v>145</v>
       </c>
       <c r="I42" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J42" s="13"/>
-      <c r="K42" s="13"/>
+      <c r="K42" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D43" s="13" t="str">
         <f>VLOOKUP(A43,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4362,20 +4444,22 @@
         <v>3</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H43" s="14">
         <v>150</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J43" s="13"/>
-      <c r="K43" s="13"/>
+      <c r="K43" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>33</v>
@@ -4394,20 +4478,22 @@
         <v>10</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H44" s="14">
         <v>135</v>
       </c>
       <c r="I44" s="15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J44" s="13"/>
-      <c r="K44" s="13"/>
+      <c r="K44" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>33</v>
@@ -4426,20 +4512,22 @@
         <v>12</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H45" s="14">
         <v>150</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J45" s="13"/>
-      <c r="K45" s="13"/>
+      <c r="K45" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B46" s="13" t="s">
         <v>33</v>
@@ -4458,26 +4546,28 @@
         <v>8</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H46" s="14">
         <v>110</v>
       </c>
       <c r="I46" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J46" s="13"/>
-      <c r="K46" s="13"/>
+      <c r="K46" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B47" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D47" s="13" t="str">
         <f>VLOOKUP(A47,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4490,26 +4580,28 @@
         <v>15</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H47" s="14">
         <v>420</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J47" s="13"/>
-      <c r="K47" s="13"/>
+      <c r="K47" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B48" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D48" s="13" t="str">
         <f>VLOOKUP(A48,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4522,23 +4614,25 @@
         <v>12</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H48" s="14">
         <v>350</v>
       </c>
       <c r="I48" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
+      <c r="K48" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>36</v>
@@ -4554,23 +4648,25 @@
         <v>5</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H49" s="14">
         <v>220</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J49" s="13"/>
-      <c r="K49" s="13"/>
+      <c r="K49" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>36</v>
@@ -4586,26 +4682,28 @@
         <v>5</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H50" s="14">
         <v>210</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
+      <c r="K50" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C51" s="13" t="s">
         <v>278</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>279</v>
       </c>
       <c r="D51" s="13" t="str">
         <f>VLOOKUP(A51,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4618,26 +4716,28 @@
         <v>12</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H51" s="14">
         <v>250</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J51" s="13"/>
-      <c r="K51" s="13"/>
+      <c r="K51" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D52" s="13" t="str">
         <f>VLOOKUP(A52,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4650,16 +4750,18 @@
         <v>15</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H52" s="14">
         <v>400</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J52" s="13"/>
-      <c r="K52" s="13"/>
+      <c r="K52" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="13"/>
@@ -4959,6 +5061,8 @@
     <hyperlink ref="M16" r:id="rId3" xr:uid="{9936B76F-B377-4FE6-9BE3-317950F81D0C}"/>
     <hyperlink ref="N7" r:id="rId4" xr:uid="{34EB5817-7AEF-4055-973E-042FD52EDB95}"/>
     <hyperlink ref="N15" r:id="rId5" xr:uid="{1C256CF5-232E-4CD0-9B21-D99C0C8BE300}"/>
+    <hyperlink ref="K3" r:id="rId6" xr:uid="{9D55401A-734C-478F-B8D1-3EA1DBF1054B}"/>
+    <hyperlink ref="K4:K52" r:id="rId7" display="https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg" xr:uid="{8E971F40-C5D2-424B-9856-D1E1EB7CA3BD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5009,7 +5113,7 @@
         <v>74</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>60</v>
@@ -5026,7 +5130,7 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5042,7 +5146,7 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -5058,7 +5162,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -5074,7 +5178,7 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -5090,7 +5194,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -5106,7 +5210,7 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -5122,7 +5226,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -5138,7 +5242,7 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -5154,7 +5258,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -5170,7 +5274,7 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -5186,7 +5290,7 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -5202,7 +5306,7 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -5218,7 +5322,7 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -5234,7 +5338,7 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -5250,7 +5354,7 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -5266,7 +5370,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -5282,7 +5386,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -5298,7 +5402,7 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -5314,7 +5418,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -5330,7 +5434,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -5367,10 +5471,10 @@
         <v>72</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
@@ -5390,22 +5494,22 @@
         <v>38</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -5421,22 +5525,22 @@
         <v>39</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -5452,13 +5556,13 @@
         <v>40</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -5477,16 +5581,16 @@
         <v>41</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -5504,19 +5608,19 @@
         <v>42</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>83</v>
-      </c>
       <c r="G6" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -5533,22 +5637,22 @@
         <v>45</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="G7" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -5564,37 +5668,37 @@
         <v>43</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>98</v>
-      </c>
       <c r="K8" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5605,25 +5709,25 @@
         <v>44</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="J9" s="3"/>
       <c r="L9" s="3"/>
@@ -5637,25 +5741,25 @@
         <v>50</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -5670,22 +5774,22 @@
         <v>49</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E11" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="G11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="3"/>
@@ -5701,34 +5805,34 @@
         <v>45</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I12" s="4" t="s">
+      <c r="J12" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>98</v>
-      </c>
       <c r="K12" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M12" s="3"/>
     </row>
@@ -5740,34 +5844,34 @@
         <v>43</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I13" s="4" t="s">
+      <c r="J13" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>98</v>
-      </c>
       <c r="K13" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M13" s="3"/>
     </row>
@@ -5779,34 +5883,34 @@
         <v>44</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="H14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I14" s="4" t="s">
+      <c r="J14" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>98</v>
-      </c>
       <c r="K14" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M14" s="3"/>
     </row>
@@ -5818,25 +5922,25 @@
         <v>46</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="G15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="I15" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -5851,23 +5955,23 @@
         <v>47</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="G16" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -5882,25 +5986,25 @@
         <v>51</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="I17" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -5915,25 +6019,25 @@
         <v>52</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="H18" s="4" t="s">
+      <c r="I18" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -5948,25 +6052,25 @@
         <v>53</v>
       </c>
       <c r="C19" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -5981,25 +6085,25 @@
         <v>54</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="G20" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="I20" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
@@ -6014,25 +6118,25 @@
         <v>55</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E21" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="G21" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="I21" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
@@ -6065,7 +6169,7 @@
         <v>61</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>72</v>
@@ -6076,7 +6180,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>38</v>
@@ -6087,7 +6191,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>39</v>
@@ -6098,10 +6202,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6109,10 +6213,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6120,10 +6224,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6131,10 +6235,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6142,10 +6246,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6153,10 +6257,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6164,7 +6268,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>49</v>
@@ -6175,7 +6279,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>50</v>
@@ -6186,10 +6290,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6197,10 +6301,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6208,7 +6312,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>44</v>
@@ -6219,7 +6323,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>43</v>
@@ -6230,10 +6334,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6241,10 +6345,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6252,10 +6356,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6263,10 +6367,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6274,10 +6378,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6285,10 +6389,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6296,10 +6400,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6307,10 +6411,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6318,10 +6422,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6329,7 +6433,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>46</v>
@@ -6340,10 +6444,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6351,7 +6455,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>47</v>
@@ -6362,10 +6466,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6373,10 +6477,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -6384,10 +6488,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6395,10 +6499,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6406,10 +6510,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6417,10 +6521,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6428,10 +6532,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6439,10 +6543,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6450,10 +6554,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6461,10 +6565,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6472,10 +6576,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -6483,10 +6587,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -6494,10 +6598,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -6505,10 +6609,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -6516,10 +6620,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -6527,10 +6631,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -6538,10 +6642,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -6549,10 +6653,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -6560,10 +6664,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -6571,10 +6675,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -6582,10 +6686,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -6593,10 +6697,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>270</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -6604,10 +6708,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="C50" s="13" t="s">
         <v>274</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -6615,10 +6719,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -6626,10 +6730,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>281</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -6637,7 +6741,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -6645,7 +6749,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -6653,7 +6757,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -6661,7 +6765,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -6669,7 +6773,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -6677,7 +6781,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -6685,7 +6789,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -6693,7 +6797,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -6701,7 +6805,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -6709,7 +6813,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -6717,7 +6821,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -6725,7 +6829,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -6733,7 +6837,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -6741,7 +6845,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -6749,7 +6853,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -6757,7 +6861,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -6765,7 +6869,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -6773,7 +6877,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -6781,7 +6885,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -6789,7 +6893,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -6797,7 +6901,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -6805,7 +6909,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -6813,7 +6917,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -6821,7 +6925,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -6829,7 +6933,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -6837,7 +6941,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -6845,7 +6949,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -6853,7 +6957,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -6861,7 +6965,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -6869,7 +6973,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -6877,7 +6981,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -6885,7 +6989,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -6893,7 +6997,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -6901,7 +7005,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -6909,7 +7013,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -6917,7 +7021,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -6925,7 +7029,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -6933,7 +7037,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -6941,7 +7045,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -6949,7 +7053,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -6957,7 +7061,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -6965,7 +7069,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -6973,7 +7077,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -6981,7 +7085,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -6989,7 +7093,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -6997,7 +7101,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -7005,7 +7109,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -7013,7 +7117,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -7021,7 +7125,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -7029,7 +7133,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -7037,7 +7141,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -7045,7 +7149,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -7053,7 +7157,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -7061,7 +7165,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -7069,7 +7173,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -7077,7 +7181,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -7085,7 +7189,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -7093,7 +7197,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -7101,7 +7205,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="13" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -7109,7 +7213,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -7117,7 +7221,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -7125,7 +7229,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -7133,7 +7237,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -7141,7 +7245,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -7149,7 +7253,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -7157,7 +7261,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -7165,7 +7269,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -7173,7 +7277,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -7181,7 +7285,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -7189,7 +7293,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -7197,7 +7301,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -7205,7 +7309,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -7213,7 +7317,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -7221,7 +7325,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -7229,7 +7333,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -7237,7 +7341,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -7245,7 +7349,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -7253,7 +7357,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -7261,7 +7365,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -7269,7 +7373,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -7277,7 +7381,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="13" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -7285,7 +7389,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -7293,7 +7397,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -7301,7 +7405,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -7309,7 +7413,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="13" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -7317,7 +7421,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -7325,7 +7429,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -7333,7 +7437,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -7341,7 +7445,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="13" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -7349,7 +7453,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -7357,7 +7461,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -7365,7 +7469,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -7373,7 +7477,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -7381,7 +7485,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -7389,7 +7493,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -7397,7 +7501,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -7405,7 +7509,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="13" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -7413,7 +7517,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -7421,7 +7525,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -7429,7 +7533,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -7437,7 +7541,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -7445,7 +7549,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -7453,7 +7557,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -7461,7 +7565,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -7469,7 +7573,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -7477,7 +7581,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -7485,7 +7589,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="13" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -7493,7 +7597,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -7501,7 +7605,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="13" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -7509,7 +7613,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="13" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -7517,7 +7621,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="13" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -7525,7 +7629,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -7533,7 +7637,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -7541,7 +7645,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -7549,7 +7653,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="13" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -7557,7 +7661,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="13" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -7565,7 +7669,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="13" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -7573,7 +7677,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -7581,7 +7685,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="13" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -7589,7 +7693,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -7597,7 +7701,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -7605,7 +7709,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -7613,7 +7717,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="13" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -7621,7 +7725,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -7629,7 +7733,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="13" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -7637,7 +7741,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -7645,7 +7749,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="13" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -7653,7 +7757,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -7661,7 +7765,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="13" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -7669,7 +7773,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="13" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -7677,7 +7781,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="13" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -7685,7 +7789,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -7693,7 +7797,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -7701,7 +7805,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="13" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -7709,7 +7813,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="13" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -7717,7 +7821,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="13" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -7725,7 +7829,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="13" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -7733,7 +7837,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="13" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -7741,7 +7845,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="13" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -7749,7 +7853,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="13" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -7757,7 +7861,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="13" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -7765,7 +7869,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="13" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -7773,7 +7877,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="13" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -7781,7 +7885,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="13" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -7789,7 +7893,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="13" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -7797,7 +7901,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="13" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -7805,7 +7909,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="13" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -7813,7 +7917,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="13" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -7821,7 +7925,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -7840,12 +7944,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="17.399999999999999">
       <c r="A1" s="17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -7853,7 +7957,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -7861,7 +7965,7 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="19" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -7869,17 +7973,17 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="17.399999999999999">
       <c r="A11" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -7887,7 +7991,7 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="19" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -7895,7 +7999,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="19" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -7903,17 +8007,17 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="19" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="17.399999999999999">
       <c r="A21" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -7921,7 +8025,7 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="19" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -7929,17 +8033,17 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="17.399999999999999">
       <c r="A31" s="17" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -7947,7 +8051,7 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="19" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -7955,7 +8059,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="19" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -7963,7 +8067,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="19" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -7971,17 +8075,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="17.399999999999999">
       <c r="A43" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -7989,7 +8093,7 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="48" spans="1:1">
@@ -7997,7 +8101,7 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="19" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="50" spans="1:1">
@@ -8005,7 +8109,7 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="19" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -8013,7 +8117,7 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="19" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36BEC4A-3A60-429B-B5B1-6941DC8A098D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEDD4345-F32D-4142-8FE4-F39BAAFEE081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="460">
   <si>
     <t>Contact</t>
   </si>
@@ -1991,6 +1991,9 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg</t>
   </si>
 </sst>
 </file>
@@ -3059,7 +3062,7 @@
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L3" s="3"/>
     </row>
@@ -5061,7 +5064,7 @@
     <hyperlink ref="M16" r:id="rId3" xr:uid="{9936B76F-B377-4FE6-9BE3-317950F81D0C}"/>
     <hyperlink ref="N7" r:id="rId4" xr:uid="{34EB5817-7AEF-4055-973E-042FD52EDB95}"/>
     <hyperlink ref="N15" r:id="rId5" xr:uid="{1C256CF5-232E-4CD0-9B21-D99C0C8BE300}"/>
-    <hyperlink ref="K3" r:id="rId6" xr:uid="{9D55401A-734C-478F-B8D1-3EA1DBF1054B}"/>
+    <hyperlink ref="K3" r:id="rId6" display="https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg" xr:uid="{9D55401A-734C-478F-B8D1-3EA1DBF1054B}"/>
     <hyperlink ref="K4:K52" r:id="rId7" display="https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg" xr:uid="{8E971F40-C5D2-424B-9856-D1E1EB7CA3BD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEDD4345-F32D-4142-8FE4-F39BAAFEE081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03A6002-5FBA-49AB-A387-47D991987031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
   <sheets>
     <sheet name="Branding" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="536">
   <si>
     <t>Contact</t>
   </si>
@@ -260,9 +260,6 @@
     <t>Falcon,1253.Adas,India,54652</t>
   </si>
   <si>
-    <t xml:space="preserve">E: other number optional, </t>
-  </si>
-  <si>
     <t>Items Name</t>
   </si>
   <si>
@@ -273,9 +270,6 @@
   </si>
   <si>
     <t>https://www.instagram.com,https://maps.app.goo.gl/AHQsZChqfBk3TTuV8</t>
-  </si>
-  <si>
-    <t>https://lh3.googleusercontent.com/ogw/AF2bZyhKqj5qfYsu30Iy9LeElT13L-xk7R2DVTSw7TqahGtd=s32-c-mo</t>
   </si>
   <si>
     <t>Game</t>
@@ -1995,12 +1989,403 @@
   <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg</t>
   </si>
+  <si>
+    <t>Current File</t>
+  </si>
+  <si>
+    <t>Sounds Like</t>
+  </si>
+  <si>
+    <t>Suggested Original/Library Name</t>
+  </si>
+  <si>
+    <t>SFX06.mp3</t>
+  </si>
+  <si>
+    <t>Short digital impact with a soft electronic pulse; good as a UI confirmation or logo hit.</t>
+  </si>
+  <si>
+    <t>SFX07.mp3</t>
+  </si>
+  <si>
+    <t>Long futuristic energy sweep with rising motion and a cinematic sci-fi feel. Suitable for transitions or reveals.</t>
+  </si>
+  <si>
+    <t>SFX08.mp3</t>
+  </si>
+  <si>
+    <t>Fast electronic whoosh with a clean finish; ideal for motion graphics or object movement.</t>
+  </si>
+  <si>
+    <t>SFX09.mp3</t>
+  </si>
+  <si>
+    <t>Mechanical/electronic movement with a subtle impact at the end. Feels like a device activating or interface animation.</t>
+  </si>
+  <si>
+    <t>SFX10.mp3</t>
+  </si>
+  <si>
+    <t>Bright sparkle/chime with a magical or premium notification feeling.</t>
+  </si>
+  <si>
+    <t>SFX12.mp3</t>
+  </si>
+  <si>
+    <t>Short cinematic hit with a low electronic punch. Great for emphasis or logo animations.</t>
+  </si>
+  <si>
+    <t>UI_Click_Impact, Digital_Pop_Hit, Electronic_Tap</t>
+  </si>
+  <si>
+    <t>SciFi_Riser, Energy_Sweep, Whoosh_Rise_Long, Future_Transition</t>
+  </si>
+  <si>
+    <t>Whoosh_Fast, Digital_Swish, Air_Sweep, Transition_Whoosh</t>
+  </si>
+  <si>
+    <t>Tech_Move, Mechanical_Servo, UI_Transform, Digital_Movement</t>
+  </si>
+  <si>
+    <t>Magic_Chime, Success_Ding, Sparkle, Notification_Positive</t>
+  </si>
+  <si>
+    <t>Logo_Hit, Impact_Short, Trailer_Hit_Light, Cinematic_Punch</t>
+  </si>
+  <si>
+    <t>Female voice saying "Delicious!" with an energetic, positive tone. Great for food games or reward feedback.</t>
+  </si>
+  <si>
+    <t>VO_Female_Delicious, Female_Delicious_01, Voice_Delicious, Announcer_Delicious</t>
+  </si>
+  <si>
+    <t>Rapid score counting/tally sound with ascending UI ticks. Common after completing a level or counting points.</t>
+  </si>
+  <si>
+    <t>Score_Tally, Points_Count, Score_Count_Up, Tally_Count, Arcade_Score</t>
+  </si>
+  <si>
+    <t>Cartoon-style explosion/impact with a punchy finish. More playful than realistic.</t>
+  </si>
+  <si>
+    <t>Cartoon_Blast, Explosion_Light, Impact_Blast, Arcade_Explosion</t>
+  </si>
+  <si>
+    <t>Short success sound indicating a match or completed action. Bright and satisfying.</t>
+  </si>
+  <si>
+    <t>Match_Success, Puzzle_Match, Success_Plop, Correct_Match</t>
+  </si>
+  <si>
+    <t>Clean UI button click with a soft electronic confirmation.</t>
+  </si>
+  <si>
+    <t>UI_Click, Button_Click, Interface_Click, Menu_Select</t>
+  </si>
+  <si>
+    <t>Female voice saying "Moonstruck!" in a cheerful, game-show style. Likely a reward or themed announcement.</t>
+  </si>
+  <si>
+    <t>VO_Female_Moonstruck, Female_Moonstruck, Voice_Moonstruck, Announcer_Moonstruck</t>
+  </si>
+  <si>
+    <t>SFX05.mp3</t>
+  </si>
+  <si>
+    <t>SFX11.mp3</t>
+  </si>
+  <si>
+    <t>SFX04.mp3</t>
+  </si>
+  <si>
+    <t>SFX03.mp3</t>
+  </si>
+  <si>
+    <t>SFX02.mp3</t>
+  </si>
+  <si>
+    <t>SFX01.mp3</t>
+  </si>
+  <si>
+    <t>Image Type</t>
+  </si>
+  <si>
+    <t>Excel Column / Location</t>
+  </si>
+  <si>
+    <t>Aspect Ratio</t>
+  </si>
+  <si>
+    <t>AI Prompt Tag</t>
+  </si>
+  <si>
+    <t>Recommended Resolution</t>
+  </si>
+  <si>
+    <t>Max File Size</t>
+  </si>
+  <si>
+    <t>Brand Logo</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Branding Sheet: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Column N</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1:1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Square)</t>
+    </r>
+  </si>
+  <si>
+    <t>--ar 1:1</t>
+  </si>
+  <si>
+    <t>512 x 512 px</t>
+  </si>
+  <si>
+    <t>&lt; 100 KB</t>
+  </si>
+  <si>
+    <t>Menu Items (Main)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Menu Sheets: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Column K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>ItemImages</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4:3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Standard Photo)</t>
+    </r>
+  </si>
+  <si>
+    <t>--ar 4:3</t>
+  </si>
+  <si>
+    <t>800 x 600 px</t>
+  </si>
+  <si>
+    <t>&lt; 150 KB</t>
+  </si>
+  <si>
+    <t>Offer Carousel Backgrounds</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Offers Sheet: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Column F</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>16:9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Widescreen)</t>
+    </r>
+  </si>
+  <si>
+    <t>--ar 16:9</t>
+  </si>
+  <si>
+    <t>800 x 450 px</t>
+  </si>
+  <si>
+    <t>Inline Category Banner</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Branding Sheet: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Column O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>21:9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Ultra-Wide)</t>
+    </r>
+  </si>
+  <si>
+    <t>--ar 21:9</t>
+  </si>
+  <si>
+    <t>1200 x 400 px</t>
+  </si>
+  <si>
+    <t>&lt; 200 KB</t>
+  </si>
+  <si>
+    <t>Screensaver Flashcards</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Menu Sheets: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Column N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="5"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>FlashCard</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>9:16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Mobile Vertical)</t>
+    </r>
+  </si>
+  <si>
+    <t>--ar 9:16</t>
+  </si>
+  <si>
+    <t>1080 x 1920 px</t>
+  </si>
+  <si>
+    <t>&lt; 300 KB</t>
+  </si>
+  <si>
+    <t>PWA App Icon</t>
+  </si>
+  <si>
+    <r>
+      <t>logo.png</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Root Folder)</t>
+    </r>
+  </si>
+  <si>
+    <t>Brand name</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/logo.png</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="10">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2071,6 +2456,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="5"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2116,7 +2526,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2172,6 +2582,19 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2672,7 +3095,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>71</v>
+        <v>534</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -2696,7 +3119,7 @@
         <v>7</v>
       </c>
       <c r="J1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K1" t="s">
         <v>18</v>
@@ -2714,7 +3137,7 @@
         <v>66</v>
       </c>
       <c r="P1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -2746,7 +3169,7 @@
         <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K2" t="s">
         <v>19</v>
@@ -2758,10 +3181,10 @@
         <v>15</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>76</v>
+        <v>535</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -2772,8 +3195,8 @@
     <hyperlink ref="F2" r:id="rId1" xr:uid="{2F801368-BE40-40B3-A874-EF23D36AFEF8}"/>
     <hyperlink ref="I2" r:id="rId2" xr:uid="{1FEE94DC-E760-44CD-B2C1-6BC052C20F3D}"/>
     <hyperlink ref="J2" r:id="rId3" xr:uid="{E1AD14C0-21E3-4C09-A07A-B1FA633CDCCB}"/>
-    <hyperlink ref="N2" r:id="rId4" xr:uid="{DE44FFED-6D3D-4D02-BCFB-34B09E80FC50}"/>
-    <hyperlink ref="O2" r:id="rId5" xr:uid="{81AFF1C3-240D-468E-995A-5B6703C1D34C}"/>
+    <hyperlink ref="O2" r:id="rId4" xr:uid="{81AFF1C3-240D-468E-995A-5B6703C1D34C}"/>
+    <hyperlink ref="N2" r:id="rId5" xr:uid="{A1FB07C3-B8F2-49A0-A23A-B1A95E6708A3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2846,7 +3269,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2883,7 +3306,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2953,7 +3376,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="8" customFormat="1" ht="28.8">
       <c r="A1" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>30</v>
@@ -2962,7 +3385,7 @@
         <v>31</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>62</v>
@@ -2989,21 +3412,21 @@
         <v>63</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D2" s="13" t="str">
         <f>VLOOKUP(A2,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3016,30 +3439,30 @@
         <v>15</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H2" s="14">
         <v>225</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="2"/>
       <c r="L2" s="3"/>
       <c r="M2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D3" s="13" t="str">
         <f>VLOOKUP(A3,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3052,29 +3475,29 @@
         <v>20</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H3" s="14">
         <v>124</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D4" s="13" t="str">
         <f>VLOOKUP(A4,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3087,29 +3510,29 @@
         <v>2</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H4" s="14">
         <v>300</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D5" s="13" t="str">
         <f>VLOOKUP(A5,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3122,29 +3545,29 @@
         <v>2</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H5" s="14">
         <v>150</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L5" s="3"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D6" s="13" t="str">
         <f>VLOOKUP(A6,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3157,31 +3580,31 @@
         <v>12</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H6" s="14">
         <v>350</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>60</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D7" s="13" t="str">
         <f>VLOOKUP(A7,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3194,32 +3617,32 @@
         <v>8</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H7" s="14">
         <v>200</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L7" s="3"/>
       <c r="N7" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D8" s="13" t="str">
         <f>VLOOKUP(A8,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3232,29 +3655,29 @@
         <v>8</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H8" s="14">
         <v>250</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D9" s="13" t="str">
         <f>VLOOKUP(A9,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3267,26 +3690,26 @@
         <v>9</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H9" s="14">
         <v>220</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>28</v>
@@ -3305,23 +3728,23 @@
         <v>8</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H10" s="14">
         <v>521</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>28</v>
@@ -3340,23 +3763,23 @@
         <v>10</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H11" s="14">
         <v>154</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>28</v>
@@ -3375,23 +3798,23 @@
         <v>12</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H12" s="14">
         <v>450</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>28</v>
@@ -3410,23 +3833,23 @@
         <v>6</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H13" s="14">
         <v>523</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>28</v>
@@ -3445,23 +3868,23 @@
         <v>11</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H14" s="14">
         <v>620</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>28</v>
@@ -3480,26 +3903,26 @@
         <v>12</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H15" s="14">
         <v>856</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L15" s="3"/>
       <c r="N15" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>28</v>
@@ -3518,28 +3941,28 @@
         <v>15</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H16" s="14">
         <v>650</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>60</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>28</v>
@@ -3558,29 +3981,29 @@
         <v>18</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H17" s="14">
         <v>600</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D18" s="13" t="str">
         <f>VLOOKUP(A18,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3593,29 +4016,29 @@
         <v>15</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H18" s="14">
         <v>320</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>28</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D19" s="13" t="str">
         <f>VLOOKUP(A19,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3628,29 +4051,29 @@
         <v>25</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H19" s="14">
         <v>400</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D20" s="13" t="str">
         <f>VLOOKUP(A20,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3663,31 +4086,31 @@
         <v>6</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H20" s="14">
         <v>450</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>60</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L20" s="3"/>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D21" s="13" t="str">
         <f>VLOOKUP(A21,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3700,29 +4123,29 @@
         <v>20</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H21" s="14">
         <v>750</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D22" s="13" t="str">
         <f>VLOOKUP(A22,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3735,27 +4158,27 @@
         <v>17</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H22" s="14">
         <v>850</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D23" s="13" t="str">
         <f>VLOOKUP(A23,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3768,21 +4191,21 @@
         <v>35</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H23" s="14">
         <v>900</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>29</v>
@@ -3801,22 +4224,22 @@
         <v>16</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H24" s="14">
         <v>550</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J24" s="13"/>
       <c r="K24" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B25" s="13" t="s">
         <v>29</v>
@@ -3835,22 +4258,22 @@
         <v>12</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H25" s="14">
         <v>450</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J25" s="13"/>
       <c r="K25" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>29</v>
@@ -3869,22 +4292,22 @@
         <v>22</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H26" s="14">
         <v>600</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J26" s="13"/>
       <c r="K26" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>29</v>
@@ -3903,28 +4326,28 @@
         <v>10</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H27" s="14">
         <v>521</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J27" s="13"/>
       <c r="K27" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="13" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B28" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D28" s="13" t="str">
         <f>VLOOKUP(A28,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3937,28 +4360,28 @@
         <v>20</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H28" s="14">
         <v>650</v>
       </c>
       <c r="I28" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J28" s="13"/>
       <c r="K28" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D29" s="13" t="str">
         <f>VLOOKUP(A29,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3971,22 +4394,22 @@
         <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H29" s="14">
         <v>120</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J29" s="13"/>
       <c r="K29" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>33</v>
@@ -4005,22 +4428,22 @@
         <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H30" s="14">
         <v>5</v>
       </c>
       <c r="I30" s="15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J30" s="13"/>
       <c r="K30" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>33</v>
@@ -4039,22 +4462,22 @@
         <v>3</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H31" s="14">
         <v>65</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J31" s="13"/>
       <c r="K31" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>33</v>
@@ -4073,22 +4496,22 @@
         <v>2</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H32" s="14">
         <v>30</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J32" s="13"/>
       <c r="K32" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>33</v>
@@ -4107,22 +4530,22 @@
         <v>3</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H33" s="14">
         <v>10</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J33" s="13"/>
       <c r="K33" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="13" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>33</v>
@@ -4141,22 +4564,22 @@
         <v>4</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H34" s="14">
         <v>85</v>
       </c>
       <c r="I34" s="15" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J34" s="13"/>
       <c r="K34" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B35" s="13" t="s">
         <v>33</v>
@@ -4175,22 +4598,22 @@
         <v>1</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H35" s="14">
         <v>0</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J35" s="13"/>
       <c r="K35" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="13" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B36" s="13" t="s">
         <v>33</v>
@@ -4209,22 +4632,22 @@
         <v>2</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H36" s="14">
         <v>0</v>
       </c>
       <c r="I36" s="15" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J36" s="13"/>
       <c r="K36" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B37" s="13" t="s">
         <v>33</v>
@@ -4243,28 +4666,28 @@
         <v>3</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H37" s="14">
         <v>0</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J37" s="13"/>
       <c r="K37" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B38" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D38" s="13" t="str">
         <f>VLOOKUP(A38,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4277,28 +4700,28 @@
         <v>3</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H38" s="14">
         <v>150</v>
       </c>
       <c r="I38" s="15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J38" s="13"/>
       <c r="K38" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B39" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D39" s="13" t="str">
         <f>VLOOKUP(A39,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4311,28 +4734,28 @@
         <v>3</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H39" s="14">
         <v>140</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J39" s="13"/>
       <c r="K39" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="13" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B40" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D40" s="13" t="str">
         <f>VLOOKUP(A40,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4345,28 +4768,28 @@
         <v>3</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H40" s="14">
         <v>140</v>
       </c>
       <c r="I40" s="15" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J40" s="13"/>
       <c r="K40" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D41" s="13" t="str">
         <f>VLOOKUP(A41,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4379,28 +4802,28 @@
         <v>3</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H41" s="14">
         <v>160</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J41" s="13"/>
       <c r="K41" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D42" s="13" t="str">
         <f>VLOOKUP(A42,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4413,28 +4836,28 @@
         <v>3</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H42" s="14">
         <v>145</v>
       </c>
       <c r="I42" s="15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J42" s="13"/>
       <c r="K42" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="13" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D43" s="13" t="str">
         <f>VLOOKUP(A43,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4447,22 +4870,22 @@
         <v>3</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H43" s="14">
         <v>150</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J43" s="13"/>
       <c r="K43" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>33</v>
@@ -4481,22 +4904,22 @@
         <v>10</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H44" s="14">
         <v>135</v>
       </c>
       <c r="I44" s="15" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="J44" s="13"/>
       <c r="K44" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>33</v>
@@ -4515,22 +4938,22 @@
         <v>12</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H45" s="14">
         <v>150</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="J45" s="13"/>
       <c r="K45" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B46" s="13" t="s">
         <v>33</v>
@@ -4549,28 +4972,28 @@
         <v>8</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H46" s="14">
         <v>110</v>
       </c>
       <c r="I46" s="15" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J46" s="13"/>
       <c r="K46" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="13" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B47" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D47" s="13" t="str">
         <f>VLOOKUP(A47,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4583,28 +5006,28 @@
         <v>15</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H47" s="14">
         <v>420</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J47" s="13"/>
       <c r="K47" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="13" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B48" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D48" s="13" t="str">
         <f>VLOOKUP(A48,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4617,25 +5040,25 @@
         <v>12</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H48" s="14">
         <v>350</v>
       </c>
       <c r="I48" s="15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J48" s="13"/>
       <c r="K48" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="13" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>36</v>
@@ -4651,25 +5074,25 @@
         <v>5</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H49" s="14">
         <v>220</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="J49" s="13"/>
       <c r="K49" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="13" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>36</v>
@@ -4685,28 +5108,28 @@
         <v>5</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H50" s="14">
         <v>210</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="J50" s="13"/>
       <c r="K50" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D51" s="13" t="str">
         <f>VLOOKUP(A51,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4719,28 +5142,28 @@
         <v>12</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H51" s="14">
         <v>250</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J51" s="13"/>
       <c r="K51" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="13" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D52" s="13" t="str">
         <f>VLOOKUP(A52,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4753,17 +5176,17 @@
         <v>15</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H52" s="14">
         <v>400</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J52" s="13"/>
       <c r="K52" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5113,10 +5536,10 @@
         <v>63</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>60</v>
@@ -5128,12 +5551,12 @@
         <v>63</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5149,7 +5572,7 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -5165,7 +5588,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -5181,7 +5604,7 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -5197,7 +5620,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -5213,7 +5636,7 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -5229,7 +5652,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -5245,7 +5668,7 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -5261,7 +5684,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -5277,7 +5700,7 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -5293,7 +5716,7 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -5309,7 +5732,7 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -5325,7 +5748,7 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -5341,7 +5764,7 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -5357,7 +5780,7 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -5373,7 +5796,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -5389,7 +5812,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -5405,7 +5828,7 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -5421,7 +5844,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -5437,7 +5860,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -5471,13 +5894,13 @@
         <v>61</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
@@ -5497,22 +5920,22 @@
         <v>38</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -5528,22 +5951,22 @@
         <v>39</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -5559,13 +5982,13 @@
         <v>40</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -5584,16 +6007,16 @@
         <v>41</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -5611,19 +6034,19 @@
         <v>42</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -5640,22 +6063,22 @@
         <v>45</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -5671,37 +6094,37 @@
         <v>43</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="K8" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="M8" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5712,25 +6135,25 @@
         <v>44</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="J9" s="3"/>
       <c r="L9" s="3"/>
@@ -5744,25 +6167,25 @@
         <v>50</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -5777,22 +6200,22 @@
         <v>49</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="3"/>
@@ -5808,34 +6231,34 @@
         <v>45</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="J12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="K12" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M12" s="3"/>
     </row>
@@ -5847,34 +6270,34 @@
         <v>43</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="H13" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="J13" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="K13" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M13" s="3"/>
     </row>
@@ -5886,34 +6309,34 @@
         <v>44</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E14" s="4" t="s">
+      <c r="I14" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="J14" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>97</v>
-      </c>
       <c r="K14" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M14" s="3"/>
     </row>
@@ -5925,25 +6348,25 @@
         <v>46</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G15" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -5958,23 +6381,23 @@
         <v>47</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -5989,25 +6412,25 @@
         <v>51</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="I17" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -6022,25 +6445,25 @@
         <v>52</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -6055,25 +6478,25 @@
         <v>53</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G19" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -6088,25 +6511,25 @@
         <v>54</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G20" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
@@ -6121,25 +6544,25 @@
         <v>55</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G21" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
@@ -6172,10 +6595,10 @@
         <v>61</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6183,7 +6606,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>38</v>
@@ -6194,7 +6617,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>39</v>
@@ -6205,10 +6628,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6216,10 +6639,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6227,10 +6650,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6238,10 +6661,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6249,10 +6672,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6260,10 +6683,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6271,7 +6694,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>49</v>
@@ -6282,7 +6705,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>50</v>
@@ -6293,10 +6716,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6304,10 +6727,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6315,7 +6738,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>44</v>
@@ -6326,7 +6749,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>43</v>
@@ -6337,10 +6760,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6348,10 +6771,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6359,10 +6782,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6370,10 +6793,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6381,10 +6804,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6392,10 +6815,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6403,10 +6826,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6414,10 +6837,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6425,10 +6848,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6436,7 +6859,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>46</v>
@@ -6447,10 +6870,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6458,7 +6881,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>47</v>
@@ -6469,10 +6892,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6480,10 +6903,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -6491,10 +6914,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6502,10 +6925,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6513,10 +6936,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6524,10 +6947,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6535,10 +6958,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6546,10 +6969,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6557,10 +6980,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6568,10 +6991,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6579,10 +7002,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -6590,10 +7013,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -6601,10 +7024,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -6612,10 +7035,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -6623,10 +7046,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -6634,10 +7057,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -6645,10 +7068,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -6656,10 +7079,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -6667,10 +7090,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -6678,10 +7101,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -6689,10 +7112,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -6700,10 +7123,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -6711,10 +7134,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -6722,10 +7145,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C51" s="13" t="s">
         <v>277</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -6733,10 +7156,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -6744,7 +7167,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -6752,7 +7175,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -6760,7 +7183,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -6768,7 +7191,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -6776,7 +7199,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -6784,7 +7207,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -6792,7 +7215,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -6800,7 +7223,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -6808,7 +7231,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -6816,7 +7239,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -6824,7 +7247,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -6832,7 +7255,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -6840,7 +7263,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -6848,7 +7271,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -6856,7 +7279,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -6864,7 +7287,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -6872,7 +7295,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -6880,7 +7303,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -6888,7 +7311,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -6896,7 +7319,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -6904,7 +7327,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -6912,7 +7335,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -6920,7 +7343,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -6928,7 +7351,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -6936,7 +7359,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -6944,7 +7367,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -6952,7 +7375,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -6960,7 +7383,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -6968,7 +7391,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -6976,7 +7399,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -6984,7 +7407,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -6992,7 +7415,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -7000,7 +7423,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -7008,7 +7431,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -7016,7 +7439,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -7024,7 +7447,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -7032,7 +7455,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -7040,7 +7463,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -7048,7 +7471,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -7056,7 +7479,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -7064,7 +7487,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -7072,7 +7495,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -7080,7 +7503,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -7088,7 +7511,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -7096,7 +7519,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -7104,7 +7527,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -7112,7 +7535,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -7120,7 +7543,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -7128,7 +7551,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -7136,7 +7559,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -7144,7 +7567,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -7152,7 +7575,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -7160,7 +7583,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -7168,7 +7591,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -7176,7 +7599,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -7184,7 +7607,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -7192,7 +7615,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -7200,7 +7623,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -7208,7 +7631,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="13" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -7216,7 +7639,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -7224,7 +7647,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -7232,7 +7655,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -7240,7 +7663,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -7248,7 +7671,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -7256,7 +7679,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -7264,7 +7687,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -7272,7 +7695,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -7280,7 +7703,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -7288,7 +7711,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -7296,7 +7719,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -7304,7 +7727,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -7312,7 +7735,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -7320,7 +7743,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -7328,7 +7751,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -7336,7 +7759,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -7344,7 +7767,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -7352,7 +7775,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -7360,7 +7783,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -7368,7 +7791,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="13" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -7376,7 +7799,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -7384,7 +7807,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="13" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -7392,7 +7815,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -7400,7 +7823,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -7408,7 +7831,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -7416,7 +7839,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="13" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -7424,7 +7847,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -7432,7 +7855,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -7440,7 +7863,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -7448,7 +7871,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="13" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -7456,7 +7879,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -7464,7 +7887,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -7472,7 +7895,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -7480,7 +7903,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -7488,7 +7911,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -7496,7 +7919,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -7504,7 +7927,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -7512,7 +7935,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="13" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -7520,7 +7943,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -7528,7 +7951,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -7536,7 +7959,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -7544,7 +7967,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -7552,7 +7975,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -7560,7 +7983,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -7568,7 +7991,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -7576,7 +7999,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -7584,7 +8007,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -7592,7 +8015,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="13" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -7600,7 +8023,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -7608,7 +8031,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="13" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -7616,7 +8039,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="13" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -7624,7 +8047,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="13" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -7632,7 +8055,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -7640,7 +8063,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="13" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -7648,7 +8071,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -7656,7 +8079,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="13" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -7664,7 +8087,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="13" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -7672,7 +8095,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="13" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -7680,7 +8103,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -7688,7 +8111,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="13" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -7696,7 +8119,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -7704,7 +8127,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="13" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -7712,7 +8135,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -7720,7 +8143,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="13" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -7728,7 +8151,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -7736,7 +8159,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="13" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -7744,7 +8167,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -7752,7 +8175,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="13" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -7760,7 +8183,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -7768,7 +8191,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="13" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -7776,7 +8199,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="13" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -7784,7 +8207,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="13" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -7792,7 +8215,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="13" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -7800,7 +8223,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="13" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -7808,7 +8231,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="13" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -7816,7 +8239,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="13" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -7824,7 +8247,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="13" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -7832,7 +8255,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="13" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -7840,7 +8263,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="13" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -7848,7 +8271,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="13" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -7856,7 +8279,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="13" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -7864,7 +8287,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="13" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -7872,7 +8295,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="13" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -7880,7 +8303,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="13" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -7888,7 +8311,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="13" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -7896,7 +8319,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="13" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -7904,7 +8327,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="13" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -7912,7 +8335,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="13" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -7920,7 +8343,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="13" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -7928,7 +8351,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="13" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -7939,70 +8362,199 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB5A8E43-7FC1-40A3-A55A-D265F6AD8118}">
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="39.5234375" customWidth="1"/>
+    <col min="2" max="2" width="60.5234375" customWidth="1"/>
+    <col min="3" max="3" width="17.41796875" customWidth="1"/>
+    <col min="5" max="5" width="16.3671875" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="98.47265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="54.7890625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="17.399999999999999">
+    <row r="1" spans="1:11" ht="17.399999999999999">
       <c r="A1" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1" t="s">
+        <v>458</v>
+      </c>
+      <c r="J1" t="s">
+        <v>459</v>
+      </c>
+      <c r="K1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="I2" t="s">
+        <v>461</v>
+      </c>
+      <c r="J2" t="s">
+        <v>462</v>
+      </c>
+      <c r="K2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>281</v>
+      </c>
+      <c r="I3" t="s">
+        <v>463</v>
+      </c>
+      <c r="J3" t="s">
+        <v>464</v>
+      </c>
+      <c r="K3" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="18"/>
+      <c r="I4" t="s">
+        <v>465</v>
+      </c>
+      <c r="J4" t="s">
+        <v>466</v>
+      </c>
+      <c r="K4" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="19" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
+      <c r="I5" t="s">
+        <v>467</v>
+      </c>
+      <c r="J5" t="s">
+        <v>468</v>
+      </c>
+      <c r="K5" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="18"/>
+      <c r="I6" t="s">
+        <v>469</v>
+      </c>
+      <c r="J6" t="s">
+        <v>470</v>
+      </c>
+      <c r="K6" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="19" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="18"/>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="19" t="s">
+      <c r="I7" t="s">
+        <v>471</v>
+      </c>
+      <c r="J7" t="s">
+        <v>472</v>
+      </c>
+      <c r="K7" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="18"/>
+      <c r="I8" t="s">
+        <v>491</v>
+      </c>
+      <c r="J8" t="s">
+        <v>479</v>
+      </c>
+      <c r="K8" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="19" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="18"/>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="19" t="s">
+      <c r="I9" t="s">
+        <v>493</v>
+      </c>
+      <c r="J9" t="s">
+        <v>481</v>
+      </c>
+      <c r="K9" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="I10" t="s">
+        <v>494</v>
+      </c>
+      <c r="J10" t="s">
+        <v>483</v>
+      </c>
+      <c r="K10" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="17.399999999999999">
+      <c r="A11" s="17" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="18"/>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="19" t="s">
+      <c r="I11" t="s">
+        <v>495</v>
+      </c>
+      <c r="J11" t="s">
+        <v>485</v>
+      </c>
+      <c r="K11" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="I12" t="s">
+        <v>496</v>
+      </c>
+      <c r="J12" t="s">
+        <v>487</v>
+      </c>
+      <c r="K12" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" ht="17.399999999999999">
-      <c r="A11" s="17" t="s">
+      <c r="I13" t="s">
+        <v>492</v>
+      </c>
+      <c r="J13" t="s">
+        <v>489</v>
+      </c>
+      <c r="K13" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="18"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="19" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="18"/>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="19" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:11">
       <c r="A16" s="18"/>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="19" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -8010,17 +8562,17 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="19" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="17.399999999999999">
       <c r="A21" s="17" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -8028,7 +8580,7 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="19" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -8036,17 +8588,17 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="19" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="17.399999999999999">
       <c r="A31" s="17" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -8054,7 +8606,7 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="19" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -8062,7 +8614,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="19" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -8070,7 +8622,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="19" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -8078,17 +8630,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="17.399999999999999">
       <c r="A43" s="17" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -8096,34 +8648,250 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="19" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="18"/>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:6">
       <c r="A49" s="19" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="18"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="19" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="18"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="19" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="18"/>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="19" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="18"/>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="19" t="s">
-        <v>307</v>
-      </c>
+    <row r="59" spans="1:6" ht="42.3">
+      <c r="A59" s="22" t="s">
+        <v>497</v>
+      </c>
+      <c r="B59" s="22" t="s">
+        <v>498</v>
+      </c>
+      <c r="C59" s="22" t="s">
+        <v>499</v>
+      </c>
+      <c r="D59" s="22" t="s">
+        <v>500</v>
+      </c>
+      <c r="E59" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="F59" s="22" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="27.6">
+      <c r="A60" s="22" t="s">
+        <v>503</v>
+      </c>
+      <c r="B60" s="23" t="s">
+        <v>504</v>
+      </c>
+      <c r="C60" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="D60" s="25" t="s">
+        <v>506</v>
+      </c>
+      <c r="E60" s="23" t="s">
+        <v>507</v>
+      </c>
+      <c r="F60" s="23" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="27.9">
+      <c r="A61" s="22" t="s">
+        <v>509</v>
+      </c>
+      <c r="B61" s="23" t="s">
+        <v>510</v>
+      </c>
+      <c r="C61" s="22" t="s">
+        <v>511</v>
+      </c>
+      <c r="D61" s="25" t="s">
+        <v>512</v>
+      </c>
+      <c r="E61" s="23" t="s">
+        <v>513</v>
+      </c>
+      <c r="F61" s="23" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="27.6">
+      <c r="A62" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>516</v>
+      </c>
+      <c r="C62" s="22" t="s">
+        <v>517</v>
+      </c>
+      <c r="D62" s="25" t="s">
+        <v>518</v>
+      </c>
+      <c r="E62" s="23" t="s">
+        <v>519</v>
+      </c>
+      <c r="F62" s="23" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="27.6">
+      <c r="A63" s="22" t="s">
+        <v>520</v>
+      </c>
+      <c r="B63" s="23" t="s">
+        <v>521</v>
+      </c>
+      <c r="C63" s="22" t="s">
+        <v>522</v>
+      </c>
+      <c r="D63" s="25" t="s">
+        <v>523</v>
+      </c>
+      <c r="E63" s="23" t="s">
+        <v>524</v>
+      </c>
+      <c r="F63" s="23" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="27.9">
+      <c r="A64" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="B64" s="23" t="s">
+        <v>527</v>
+      </c>
+      <c r="C64" s="22" t="s">
+        <v>528</v>
+      </c>
+      <c r="D64" s="25" t="s">
+        <v>529</v>
+      </c>
+      <c r="E64" s="23" t="s">
+        <v>530</v>
+      </c>
+      <c r="F64" s="23" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="27.6">
+      <c r="A65" s="22" t="s">
+        <v>532</v>
+      </c>
+      <c r="B65" s="24" t="s">
+        <v>533</v>
+      </c>
+      <c r="C65" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="D65" s="25" t="s">
+        <v>506</v>
+      </c>
+      <c r="E65" s="23" t="s">
+        <v>507</v>
+      </c>
+      <c r="F65" s="23" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="B66" s="18"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="18"/>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="18"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="18"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="18"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="B71" s="18"/>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="B72" s="18"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="18"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="18"/>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="B76" s="21"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="18"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="B78" s="18"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="B79" s="18"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="B80" s="18"/>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="18"/>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="18"/>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="18"/>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="18"/>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" s="21"/>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" s="18"/>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88" s="18"/>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89" s="18"/>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90" s="18"/>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91" s="18"/>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92" s="18"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03A6002-5FBA-49AB-A387-47D991987031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD65488A-54BD-47AD-9B3B-2BD53D28FEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="537">
   <si>
     <t>Contact</t>
   </si>
@@ -2379,6 +2379,9 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/logo.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/banner/Banner01.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/banner/Banner01.jpg</t>
   </si>
 </sst>
 </file>
@@ -3184,7 +3187,7 @@
         <v>535</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>455</v>
+        <v>536</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD65488A-54BD-47AD-9B3B-2BD53D28FEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958BAFEE-E686-4440-8842-113262E713C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
   <sheets>
     <sheet name="Branding" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="537">
   <si>
     <t>Contact</t>
   </si>
@@ -5086,9 +5086,7 @@
         <v>270</v>
       </c>
       <c r="J49" s="13"/>
-      <c r="K49" s="2" t="s">
-        <v>456</v>
-      </c>
+      <c r="K49" s="2"/>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="13" t="s">
@@ -5120,9 +5118,7 @@
         <v>274</v>
       </c>
       <c r="J50" s="13"/>
-      <c r="K50" s="2" t="s">
-        <v>456</v>
-      </c>
+      <c r="K50" s="2"/>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="13" t="s">
@@ -5154,9 +5150,7 @@
         <v>174</v>
       </c>
       <c r="J51" s="13"/>
-      <c r="K51" s="2" t="s">
-        <v>456</v>
-      </c>
+      <c r="K51" s="2"/>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="13" t="s">
@@ -5188,9 +5182,7 @@
         <v>177</v>
       </c>
       <c r="J52" s="13"/>
-      <c r="K52" s="2" t="s">
-        <v>456</v>
-      </c>
+      <c r="K52" s="2"/>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="13"/>
@@ -5491,7 +5483,7 @@
     <hyperlink ref="N7" r:id="rId4" xr:uid="{34EB5817-7AEF-4055-973E-042FD52EDB95}"/>
     <hyperlink ref="N15" r:id="rId5" xr:uid="{1C256CF5-232E-4CD0-9B21-D99C0C8BE300}"/>
     <hyperlink ref="K3" r:id="rId6" display="https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg" xr:uid="{9D55401A-734C-478F-B8D1-3EA1DBF1054B}"/>
-    <hyperlink ref="K4:K52" r:id="rId7" display="https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg" xr:uid="{8E971F40-C5D2-424B-9856-D1E1EB7CA3BD}"/>
+    <hyperlink ref="K6" r:id="rId7" xr:uid="{AB762D55-2876-46AD-BD09-CF7CECA0AC70}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958BAFEE-E686-4440-8842-113262E713C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80AB708B-5ABF-4AC4-8A12-84C25C3B4DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
   <sheets>
     <sheet name="Branding" sheetId="1" r:id="rId1"/>
@@ -242,9 +242,6 @@
     <t>Language</t>
   </si>
   <si>
-    <t>English</t>
-  </si>
-  <si>
     <t>Banner Image</t>
   </si>
   <si>
@@ -2382,6 +2379,9 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/banner/Banner01.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/banner/Banner01.jpg</t>
+  </si>
+  <si>
+    <t>English&amp;Arabic</t>
   </si>
 </sst>
 </file>
@@ -3098,7 +3098,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -3122,7 +3122,7 @@
         <v>7</v>
       </c>
       <c r="J1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K1" t="s">
         <v>18</v>
@@ -3134,13 +3134,13 @@
         <v>58</v>
       </c>
       <c r="N1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -3148,7 +3148,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2">
         <v>1254653</v>
@@ -3163,31 +3163,31 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" t="s">
         <v>69</v>
-      </c>
-      <c r="H2" t="s">
-        <v>70</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K2" t="s">
         <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>65</v>
+        <v>536</v>
       </c>
       <c r="M2">
         <v>15</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>536</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -3272,7 +3272,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3309,7 +3309,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3379,7 +3379,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="8" customFormat="1" ht="28.8">
       <c r="A1" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>30</v>
@@ -3388,7 +3388,7 @@
         <v>31</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>62</v>
@@ -3415,21 +3415,21 @@
         <v>63</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D2" s="13" t="str">
         <f>VLOOKUP(A2,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3442,30 +3442,30 @@
         <v>15</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H2" s="14">
         <v>225</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="2"/>
       <c r="L2" s="3"/>
       <c r="M2" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D3" s="13" t="str">
         <f>VLOOKUP(A3,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3478,29 +3478,29 @@
         <v>20</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H3" s="14">
         <v>124</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" s="13" t="str">
         <f>VLOOKUP(A4,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3513,29 +3513,29 @@
         <v>2</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H4" s="14">
         <v>300</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D5" s="13" t="str">
         <f>VLOOKUP(A5,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3548,29 +3548,29 @@
         <v>2</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H5" s="14">
         <v>150</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L5" s="3"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D6" s="13" t="str">
         <f>VLOOKUP(A6,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3583,31 +3583,31 @@
         <v>12</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H6" s="14">
         <v>350</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>60</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D7" s="13" t="str">
         <f>VLOOKUP(A7,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3620,32 +3620,32 @@
         <v>8</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H7" s="14">
         <v>200</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L7" s="3"/>
       <c r="N7" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D8" s="13" t="str">
         <f>VLOOKUP(A8,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3658,29 +3658,29 @@
         <v>8</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H8" s="14">
         <v>250</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D9" s="13" t="str">
         <f>VLOOKUP(A9,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -3693,26 +3693,26 @@
         <v>9</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H9" s="14">
         <v>220</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>28</v>
@@ -3731,23 +3731,23 @@
         <v>8</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H10" s="14">
         <v>521</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>28</v>
@@ -3766,23 +3766,23 @@
         <v>10</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H11" s="14">
         <v>154</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>28</v>
@@ -3801,23 +3801,23 @@
         <v>12</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H12" s="14">
         <v>450</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>28</v>
@@ -3836,23 +3836,23 @@
         <v>6</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H13" s="14">
         <v>523</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>28</v>
@@ -3871,23 +3871,23 @@
         <v>11</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H14" s="14">
         <v>620</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>28</v>
@@ -3906,26 +3906,26 @@
         <v>12</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H15" s="14">
         <v>856</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L15" s="3"/>
       <c r="N15" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>28</v>
@@ -3944,28 +3944,28 @@
         <v>15</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H16" s="14">
         <v>650</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>60</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>28</v>
@@ -3984,29 +3984,29 @@
         <v>18</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H17" s="14">
         <v>600</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D18" s="13" t="str">
         <f>VLOOKUP(A18,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4019,29 +4019,29 @@
         <v>15</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H18" s="14">
         <v>320</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>28</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D19" s="13" t="str">
         <f>VLOOKUP(A19,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4054,29 +4054,29 @@
         <v>25</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H19" s="14">
         <v>400</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D20" s="13" t="str">
         <f>VLOOKUP(A20,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4089,31 +4089,31 @@
         <v>6</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H20" s="14">
         <v>450</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>60</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L20" s="3"/>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D21" s="13" t="str">
         <f>VLOOKUP(A21,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4126,29 +4126,29 @@
         <v>20</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H21" s="14">
         <v>750</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D22" s="13" t="str">
         <f>VLOOKUP(A22,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4161,27 +4161,27 @@
         <v>17</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H22" s="14">
         <v>850</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D23" s="13" t="str">
         <f>VLOOKUP(A23,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4194,21 +4194,21 @@
         <v>35</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H23" s="14">
         <v>900</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>29</v>
@@ -4227,22 +4227,22 @@
         <v>16</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H24" s="14">
         <v>550</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J24" s="13"/>
       <c r="K24" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B25" s="13" t="s">
         <v>29</v>
@@ -4261,22 +4261,22 @@
         <v>12</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H25" s="14">
         <v>450</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J25" s="13"/>
       <c r="K25" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>29</v>
@@ -4295,22 +4295,22 @@
         <v>22</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H26" s="14">
         <v>600</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J26" s="13"/>
       <c r="K26" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>29</v>
@@ -4329,28 +4329,28 @@
         <v>10</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H27" s="14">
         <v>521</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J27" s="13"/>
       <c r="K27" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B28" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D28" s="13" t="str">
         <f>VLOOKUP(A28,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4363,28 +4363,28 @@
         <v>20</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H28" s="14">
         <v>650</v>
       </c>
       <c r="I28" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J28" s="13"/>
       <c r="K28" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D29" s="13" t="str">
         <f>VLOOKUP(A29,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4397,22 +4397,22 @@
         <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H29" s="14">
         <v>120</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J29" s="13"/>
       <c r="K29" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>33</v>
@@ -4431,22 +4431,22 @@
         <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H30" s="14">
         <v>5</v>
       </c>
       <c r="I30" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J30" s="13"/>
       <c r="K30" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>33</v>
@@ -4465,22 +4465,22 @@
         <v>3</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H31" s="14">
         <v>65</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J31" s="13"/>
       <c r="K31" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>33</v>
@@ -4499,22 +4499,22 @@
         <v>2</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H32" s="14">
         <v>30</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J32" s="13"/>
       <c r="K32" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>33</v>
@@ -4533,22 +4533,22 @@
         <v>3</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H33" s="14">
         <v>10</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J33" s="13"/>
       <c r="K33" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>33</v>
@@ -4567,22 +4567,22 @@
         <v>4</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H34" s="14">
         <v>85</v>
       </c>
       <c r="I34" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J34" s="13"/>
       <c r="K34" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B35" s="13" t="s">
         <v>33</v>
@@ -4601,22 +4601,22 @@
         <v>1</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H35" s="14">
         <v>0</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J35" s="13"/>
       <c r="K35" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B36" s="13" t="s">
         <v>33</v>
@@ -4635,22 +4635,22 @@
         <v>2</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H36" s="14">
         <v>0</v>
       </c>
       <c r="I36" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J36" s="13"/>
       <c r="K36" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B37" s="13" t="s">
         <v>33</v>
@@ -4669,28 +4669,28 @@
         <v>3</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H37" s="14">
         <v>0</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J37" s="13"/>
       <c r="K37" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B38" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D38" s="13" t="str">
         <f>VLOOKUP(A38,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4703,28 +4703,28 @@
         <v>3</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H38" s="14">
         <v>150</v>
       </c>
       <c r="I38" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J38" s="13"/>
       <c r="K38" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B39" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D39" s="13" t="str">
         <f>VLOOKUP(A39,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4737,28 +4737,28 @@
         <v>3</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H39" s="14">
         <v>140</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J39" s="13"/>
       <c r="K39" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B40" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D40" s="13" t="str">
         <f>VLOOKUP(A40,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4771,28 +4771,28 @@
         <v>3</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H40" s="14">
         <v>140</v>
       </c>
       <c r="I40" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J40" s="13"/>
       <c r="K40" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D41" s="13" t="str">
         <f>VLOOKUP(A41,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4805,28 +4805,28 @@
         <v>3</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H41" s="14">
         <v>160</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J41" s="13"/>
       <c r="K41" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D42" s="13" t="str">
         <f>VLOOKUP(A42,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4839,28 +4839,28 @@
         <v>3</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H42" s="14">
         <v>145</v>
       </c>
       <c r="I42" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J42" s="13"/>
       <c r="K42" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D43" s="13" t="str">
         <f>VLOOKUP(A43,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4873,22 +4873,22 @@
         <v>3</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H43" s="14">
         <v>150</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J43" s="13"/>
       <c r="K43" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>33</v>
@@ -4907,22 +4907,22 @@
         <v>10</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H44" s="14">
         <v>135</v>
       </c>
       <c r="I44" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J44" s="13"/>
       <c r="K44" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>33</v>
@@ -4941,22 +4941,22 @@
         <v>12</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H45" s="14">
         <v>150</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J45" s="13"/>
       <c r="K45" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B46" s="13" t="s">
         <v>33</v>
@@ -4975,28 +4975,28 @@
         <v>8</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H46" s="14">
         <v>110</v>
       </c>
       <c r="I46" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J46" s="13"/>
       <c r="K46" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B47" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D47" s="13" t="str">
         <f>VLOOKUP(A47,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -5009,28 +5009,28 @@
         <v>15</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H47" s="14">
         <v>420</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J47" s="13"/>
       <c r="K47" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B48" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D48" s="13" t="str">
         <f>VLOOKUP(A48,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -5043,25 +5043,25 @@
         <v>12</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H48" s="14">
         <v>350</v>
       </c>
       <c r="I48" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J48" s="13"/>
       <c r="K48" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>36</v>
@@ -5077,23 +5077,23 @@
         <v>5</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H49" s="14">
         <v>220</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J49" s="13"/>
       <c r="K49" s="2"/>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>36</v>
@@ -5109,26 +5109,26 @@
         <v>5</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H50" s="14">
         <v>210</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J50" s="13"/>
       <c r="K50" s="2"/>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="C51" s="13" t="s">
         <v>275</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>276</v>
       </c>
       <c r="D51" s="13" t="str">
         <f>VLOOKUP(A51,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -5141,26 +5141,26 @@
         <v>12</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H51" s="14">
         <v>250</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J51" s="13"/>
       <c r="K51" s="2"/>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D52" s="13" t="str">
         <f>VLOOKUP(A52,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -5173,13 +5173,13 @@
         <v>15</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H52" s="14">
         <v>400</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J52" s="13"/>
       <c r="K52" s="2"/>
@@ -5531,10 +5531,10 @@
         <v>63</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>60</v>
@@ -5546,12 +5546,12 @@
         <v>63</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5567,7 +5567,7 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -5583,7 +5583,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -5599,7 +5599,7 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -5615,7 +5615,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -5631,7 +5631,7 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -5647,7 +5647,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -5679,7 +5679,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -5695,7 +5695,7 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -5711,7 +5711,7 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -5727,7 +5727,7 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -5743,7 +5743,7 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -5759,7 +5759,7 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -5775,7 +5775,7 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -5791,7 +5791,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -5807,7 +5807,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -5823,7 +5823,7 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -5855,7 +5855,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -5889,13 +5889,13 @@
         <v>61</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
@@ -5915,22 +5915,22 @@
         <v>38</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -5946,22 +5946,22 @@
         <v>39</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -5977,13 +5977,13 @@
         <v>40</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -6002,16 +6002,16 @@
         <v>41</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -6029,19 +6029,19 @@
         <v>42</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="G6" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -6058,22 +6058,22 @@
         <v>45</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="G7" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -6089,37 +6089,37 @@
         <v>43</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="K8" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -6130,25 +6130,25 @@
         <v>44</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="J9" s="3"/>
       <c r="L9" s="3"/>
@@ -6162,25 +6162,25 @@
         <v>50</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -6195,22 +6195,22 @@
         <v>49</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="G11" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="3"/>
@@ -6226,34 +6226,34 @@
         <v>45</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="I12" s="4" t="s">
+      <c r="J12" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="K12" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M12" s="3"/>
     </row>
@@ -6265,34 +6265,34 @@
         <v>43</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="I13" s="4" t="s">
+      <c r="J13" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="K13" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M13" s="3"/>
     </row>
@@ -6304,34 +6304,34 @@
         <v>44</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="H14" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="I14" s="4" t="s">
+      <c r="J14" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="K14" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M14" s="3"/>
     </row>
@@ -6343,25 +6343,25 @@
         <v>46</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>77</v>
-      </c>
       <c r="G15" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="I15" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -6376,23 +6376,23 @@
         <v>47</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>77</v>
-      </c>
       <c r="G16" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -6407,25 +6407,25 @@
         <v>51</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="I17" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -6440,25 +6440,25 @@
         <v>52</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H18" s="4" t="s">
+      <c r="I18" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -6473,25 +6473,25 @@
         <v>53</v>
       </c>
       <c r="C19" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -6506,25 +6506,25 @@
         <v>54</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>77</v>
-      </c>
       <c r="G20" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="I20" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
@@ -6539,25 +6539,25 @@
         <v>55</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>77</v>
-      </c>
       <c r="G21" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="I21" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
@@ -6590,10 +6590,10 @@
         <v>61</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6601,7 +6601,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>38</v>
@@ -6612,7 +6612,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>39</v>
@@ -6623,10 +6623,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6634,10 +6634,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6645,10 +6645,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6656,10 +6656,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6667,10 +6667,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6678,10 +6678,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6689,7 +6689,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>49</v>
@@ -6700,7 +6700,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>50</v>
@@ -6711,10 +6711,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6722,10 +6722,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6733,7 +6733,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>44</v>
@@ -6744,7 +6744,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>43</v>
@@ -6755,10 +6755,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6766,10 +6766,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6777,10 +6777,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6788,10 +6788,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6799,10 +6799,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6810,10 +6810,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6821,10 +6821,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6832,10 +6832,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6843,10 +6843,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6854,7 +6854,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>46</v>
@@ -6865,10 +6865,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6876,7 +6876,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>47</v>
@@ -6887,10 +6887,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6898,10 +6898,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -6909,10 +6909,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6920,10 +6920,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6931,10 +6931,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6942,10 +6942,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6953,10 +6953,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6964,10 +6964,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6975,10 +6975,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6986,10 +6986,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6997,10 +6997,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -7008,10 +7008,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -7019,10 +7019,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -7030,10 +7030,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7041,10 +7041,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -7052,10 +7052,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -7063,10 +7063,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -7074,10 +7074,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -7085,10 +7085,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -7096,10 +7096,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -7107,10 +7107,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -7118,10 +7118,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>267</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -7129,10 +7129,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="C50" s="13" t="s">
         <v>271</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -7140,10 +7140,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -7151,10 +7151,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>278</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -7162,7 +7162,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -7170,7 +7170,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -7178,7 +7178,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -7186,7 +7186,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -7194,7 +7194,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -7202,7 +7202,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -7210,7 +7210,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -7218,7 +7218,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -7226,7 +7226,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -7234,7 +7234,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -7242,7 +7242,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -7250,7 +7250,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -7258,7 +7258,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -7266,7 +7266,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -7274,7 +7274,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -7282,7 +7282,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -7290,7 +7290,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -7298,7 +7298,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -7306,7 +7306,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -7314,7 +7314,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -7322,7 +7322,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -7330,7 +7330,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -7338,7 +7338,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -7346,7 +7346,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -7354,7 +7354,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -7362,7 +7362,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -7370,7 +7370,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -7378,7 +7378,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -7386,7 +7386,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -7394,7 +7394,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -7402,7 +7402,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -7410,7 +7410,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -7418,7 +7418,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -7426,7 +7426,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -7434,7 +7434,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -7442,7 +7442,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -7450,7 +7450,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -7458,7 +7458,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -7466,7 +7466,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -7474,7 +7474,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -7482,7 +7482,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -7490,7 +7490,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -7498,7 +7498,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -7506,7 +7506,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -7514,7 +7514,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -7522,7 +7522,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -7530,7 +7530,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -7538,7 +7538,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -7546,7 +7546,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -7554,7 +7554,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -7562,7 +7562,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -7570,7 +7570,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -7578,7 +7578,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -7586,7 +7586,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -7594,7 +7594,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -7602,7 +7602,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -7610,7 +7610,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -7618,7 +7618,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -7626,7 +7626,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="13" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -7634,7 +7634,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -7642,7 +7642,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -7650,7 +7650,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -7658,7 +7658,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -7666,7 +7666,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -7674,7 +7674,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -7682,7 +7682,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -7690,7 +7690,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -7698,7 +7698,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -7706,7 +7706,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -7714,7 +7714,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -7722,7 +7722,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -7730,7 +7730,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -7738,7 +7738,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -7746,7 +7746,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -7754,7 +7754,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -7762,7 +7762,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -7770,7 +7770,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -7778,7 +7778,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -7786,7 +7786,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -7794,7 +7794,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -7802,7 +7802,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="13" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -7810,7 +7810,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -7818,7 +7818,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -7826,7 +7826,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -7834,7 +7834,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="13" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -7842,7 +7842,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -7850,7 +7850,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -7858,7 +7858,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -7866,7 +7866,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="13" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -7874,7 +7874,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -7882,7 +7882,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -7890,7 +7890,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -7898,7 +7898,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -7906,7 +7906,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -7914,7 +7914,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -7922,7 +7922,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -7930,7 +7930,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -7938,7 +7938,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -7946,7 +7946,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -7954,7 +7954,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -7962,7 +7962,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -7970,7 +7970,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -7978,7 +7978,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -7986,7 +7986,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -7994,7 +7994,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -8002,7 +8002,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -8010,7 +8010,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="13" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -8018,7 +8018,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -8026,7 +8026,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="13" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -8034,7 +8034,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="13" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -8042,7 +8042,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -8050,7 +8050,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -8058,7 +8058,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="13" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -8066,7 +8066,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -8074,7 +8074,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="13" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -8082,7 +8082,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -8090,7 +8090,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="13" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -8098,7 +8098,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -8106,7 +8106,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="13" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -8114,7 +8114,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -8122,7 +8122,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -8130,7 +8130,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -8138,7 +8138,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -8146,7 +8146,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -8154,7 +8154,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="13" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -8162,7 +8162,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -8170,7 +8170,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -8178,7 +8178,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -8186,7 +8186,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="13" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -8194,7 +8194,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="13" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -8202,7 +8202,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -8210,7 +8210,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="13" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -8218,7 +8218,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="13" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -8226,7 +8226,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="13" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -8234,7 +8234,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -8242,7 +8242,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -8250,7 +8250,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="13" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -8258,7 +8258,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="13" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -8266,7 +8266,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="13" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -8274,7 +8274,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="13" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -8282,7 +8282,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="13" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -8290,7 +8290,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="13" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -8298,7 +8298,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="13" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -8306,7 +8306,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="13" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -8314,7 +8314,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="13" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -8322,7 +8322,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="13" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -8330,7 +8330,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="13" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -8338,7 +8338,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="13" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -8346,7 +8346,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="13" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -8371,169 +8371,169 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999">
       <c r="A1" s="17" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I1" t="s">
+        <v>457</v>
+      </c>
+      <c r="J1" t="s">
         <v>458</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>459</v>
-      </c>
-      <c r="K1" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="I2" t="s">
+        <v>460</v>
+      </c>
+      <c r="J2" t="s">
         <v>461</v>
       </c>
-      <c r="J2" t="s">
-        <v>462</v>
-      </c>
       <c r="K2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I3" t="s">
+        <v>462</v>
+      </c>
+      <c r="J3" t="s">
         <v>463</v>
       </c>
-      <c r="J3" t="s">
-        <v>464</v>
-      </c>
       <c r="K3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="18"/>
       <c r="I4" t="s">
+        <v>464</v>
+      </c>
+      <c r="J4" t="s">
         <v>465</v>
       </c>
-      <c r="J4" t="s">
-        <v>466</v>
-      </c>
       <c r="K4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I5" t="s">
+        <v>466</v>
+      </c>
+      <c r="J5" t="s">
         <v>467</v>
       </c>
-      <c r="J5" t="s">
-        <v>468</v>
-      </c>
       <c r="K5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="18"/>
       <c r="I6" t="s">
+        <v>468</v>
+      </c>
+      <c r="J6" t="s">
         <v>469</v>
       </c>
-      <c r="J6" t="s">
-        <v>470</v>
-      </c>
       <c r="K6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I7" t="s">
+        <v>470</v>
+      </c>
+      <c r="J7" t="s">
         <v>471</v>
       </c>
-      <c r="J7" t="s">
-        <v>472</v>
-      </c>
       <c r="K7" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="18"/>
       <c r="I8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J8" t="s">
+        <v>478</v>
+      </c>
+      <c r="K8" t="s">
         <v>479</v>
-      </c>
-      <c r="K8" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I9" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="J9" t="s">
+        <v>480</v>
+      </c>
+      <c r="K9" t="s">
         <v>481</v>
-      </c>
-      <c r="K9" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="I10" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="J10" t="s">
+        <v>482</v>
+      </c>
+      <c r="K10" t="s">
         <v>483</v>
-      </c>
-      <c r="K10" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="17.399999999999999">
       <c r="A11" s="17" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I11" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J11" t="s">
+        <v>484</v>
+      </c>
+      <c r="K11" t="s">
         <v>485</v>
-      </c>
-      <c r="K11" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="I12" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="J12" t="s">
+        <v>486</v>
+      </c>
+      <c r="K12" t="s">
         <v>487</v>
-      </c>
-      <c r="K12" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I13" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="J13" t="s">
+        <v>488</v>
+      </c>
+      <c r="K13" t="s">
         <v>489</v>
-      </c>
-      <c r="K13" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -8541,7 +8541,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -8549,7 +8549,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -8557,17 +8557,17 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="17.399999999999999">
       <c r="A21" s="17" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -8575,7 +8575,7 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="19" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -8583,17 +8583,17 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="17.399999999999999">
       <c r="A31" s="17" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -8601,7 +8601,7 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -8609,7 +8609,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="19" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -8617,7 +8617,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -8625,17 +8625,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="19" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="17.399999999999999">
       <c r="A43" s="17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -8643,7 +8643,7 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="48" spans="1:1">
@@ -8651,7 +8651,7 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -8659,7 +8659,7 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="19" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -8667,147 +8667,147 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="42.3">
       <c r="A59" s="22" t="s">
+        <v>496</v>
+      </c>
+      <c r="B59" s="22" t="s">
         <v>497</v>
       </c>
-      <c r="B59" s="22" t="s">
+      <c r="C59" s="22" t="s">
         <v>498</v>
       </c>
-      <c r="C59" s="22" t="s">
+      <c r="D59" s="22" t="s">
         <v>499</v>
       </c>
-      <c r="D59" s="22" t="s">
+      <c r="E59" s="22" t="s">
         <v>500</v>
       </c>
-      <c r="E59" s="22" t="s">
+      <c r="F59" s="22" t="s">
         <v>501</v>
-      </c>
-      <c r="F59" s="22" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="27.6">
       <c r="A60" s="22" t="s">
+        <v>502</v>
+      </c>
+      <c r="B60" s="23" t="s">
         <v>503</v>
       </c>
-      <c r="B60" s="23" t="s">
+      <c r="C60" s="22" t="s">
         <v>504</v>
       </c>
-      <c r="C60" s="22" t="s">
+      <c r="D60" s="25" t="s">
         <v>505</v>
       </c>
-      <c r="D60" s="25" t="s">
+      <c r="E60" s="23" t="s">
         <v>506</v>
       </c>
-      <c r="E60" s="23" t="s">
+      <c r="F60" s="23" t="s">
         <v>507</v>
-      </c>
-      <c r="F60" s="23" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="27.9">
       <c r="A61" s="22" t="s">
+        <v>508</v>
+      </c>
+      <c r="B61" s="23" t="s">
         <v>509</v>
       </c>
-      <c r="B61" s="23" t="s">
+      <c r="C61" s="22" t="s">
         <v>510</v>
       </c>
-      <c r="C61" s="22" t="s">
+      <c r="D61" s="25" t="s">
         <v>511</v>
       </c>
-      <c r="D61" s="25" t="s">
+      <c r="E61" s="23" t="s">
         <v>512</v>
       </c>
-      <c r="E61" s="23" t="s">
+      <c r="F61" s="23" t="s">
         <v>513</v>
-      </c>
-      <c r="F61" s="23" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="27.6">
       <c r="A62" s="22" t="s">
+        <v>514</v>
+      </c>
+      <c r="B62" s="23" t="s">
         <v>515</v>
       </c>
-      <c r="B62" s="23" t="s">
+      <c r="C62" s="22" t="s">
         <v>516</v>
       </c>
-      <c r="C62" s="22" t="s">
+      <c r="D62" s="25" t="s">
         <v>517</v>
       </c>
-      <c r="D62" s="25" t="s">
+      <c r="E62" s="23" t="s">
         <v>518</v>
       </c>
-      <c r="E62" s="23" t="s">
-        <v>519</v>
-      </c>
       <c r="F62" s="23" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="27.6">
       <c r="A63" s="22" t="s">
+        <v>519</v>
+      </c>
+      <c r="B63" s="23" t="s">
         <v>520</v>
       </c>
-      <c r="B63" s="23" t="s">
+      <c r="C63" s="22" t="s">
         <v>521</v>
       </c>
-      <c r="C63" s="22" t="s">
+      <c r="D63" s="25" t="s">
         <v>522</v>
       </c>
-      <c r="D63" s="25" t="s">
+      <c r="E63" s="23" t="s">
         <v>523</v>
       </c>
-      <c r="E63" s="23" t="s">
+      <c r="F63" s="23" t="s">
         <v>524</v>
-      </c>
-      <c r="F63" s="23" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="27.9">
       <c r="A64" s="22" t="s">
+        <v>525</v>
+      </c>
+      <c r="B64" s="23" t="s">
         <v>526</v>
       </c>
-      <c r="B64" s="23" t="s">
+      <c r="C64" s="22" t="s">
         <v>527</v>
       </c>
-      <c r="C64" s="22" t="s">
+      <c r="D64" s="25" t="s">
         <v>528</v>
       </c>
-      <c r="D64" s="25" t="s">
+      <c r="E64" s="23" t="s">
         <v>529</v>
       </c>
-      <c r="E64" s="23" t="s">
+      <c r="F64" s="23" t="s">
         <v>530</v>
-      </c>
-      <c r="F64" s="23" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="27.6">
       <c r="A65" s="22" t="s">
+        <v>531</v>
+      </c>
+      <c r="B65" s="24" t="s">
         <v>532</v>
       </c>
-      <c r="B65" s="24" t="s">
-        <v>533</v>
-      </c>
       <c r="C65" s="22" t="s">
+        <v>504</v>
+      </c>
+      <c r="D65" s="25" t="s">
         <v>505</v>
       </c>
-      <c r="D65" s="25" t="s">
+      <c r="E65" s="23" t="s">
         <v>506</v>
       </c>
-      <c r="E65" s="23" t="s">
+      <c r="F65" s="23" t="s">
         <v>507</v>
-      </c>
-      <c r="F65" s="23" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="66" spans="1:6">

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80AB708B-5ABF-4AC4-8A12-84C25C3B4DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E53D9DB-AEE0-4F14-8D05-868E09599CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="542">
   <si>
     <t>Contact</t>
   </si>
@@ -1978,9 +1978,6 @@
     <t>ITM200</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/banner/Banner01.jpg</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg</t>
   </si>
   <si>
@@ -2378,10 +2375,28 @@
     <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/logo.png</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/banner/Banner01.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/banner/Banner01.jpg</t>
-  </si>
-  <si>
     <t>English&amp;Arabic</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/FlashCard/FlashCard.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/FlashCard/FlashCard02.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/Offer/Offer01.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/Offer/Offer02.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/FlashCard/FlashCard04.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/FlashCard/FlashCard03.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/banner/Banner01.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/banner/Banner02.jpg</t>
   </si>
 </sst>
 </file>
@@ -3098,7 +3113,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -3178,16 +3193,16 @@
         <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="M2">
         <v>15</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -3272,7 +3287,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>454</v>
+        <v>537</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3309,7 +3324,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>454</v>
+        <v>538</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3456,6 +3471,9 @@
       <c r="M2" s="2" t="s">
         <v>73</v>
       </c>
+      <c r="N2" s="2" t="s">
+        <v>539</v>
+      </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="13" t="s">
@@ -3488,7 +3506,7 @@
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L3" s="3"/>
     </row>
@@ -3523,7 +3541,7 @@
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L4" s="3"/>
     </row>
@@ -3558,7 +3576,7 @@
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L5" s="3"/>
     </row>
@@ -3595,9 +3613,12 @@
         <v>60</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L6" s="3"/>
+      <c r="N6" s="2" t="s">
+        <v>540</v>
+      </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="13" t="s">
@@ -3630,11 +3651,11 @@
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L7" s="3"/>
       <c r="N7" s="2" t="s">
-        <v>454</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3668,7 +3689,7 @@
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L8" s="3"/>
     </row>
@@ -3703,7 +3724,7 @@
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="2" t="s">
@@ -3741,7 +3762,7 @@
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L10" s="3"/>
     </row>
@@ -3776,7 +3797,7 @@
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L11" s="3"/>
     </row>
@@ -3811,7 +3832,7 @@
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L12" s="3"/>
     </row>
@@ -3846,7 +3867,7 @@
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L13" s="3"/>
     </row>
@@ -3881,7 +3902,7 @@
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L14" s="3"/>
     </row>
@@ -3916,11 +3937,11 @@
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L15" s="3"/>
       <c r="N15" s="2" t="s">
-        <v>454</v>
+        <v>536</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -3956,7 +3977,7 @@
         <v>60</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="2" t="s">
@@ -3994,7 +4015,7 @@
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L17" s="3"/>
     </row>
@@ -4029,7 +4050,7 @@
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L18" s="3"/>
     </row>
@@ -4064,7 +4085,7 @@
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L19" s="3"/>
     </row>
@@ -4101,7 +4122,7 @@
         <v>60</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L20" s="3"/>
     </row>
@@ -4136,7 +4157,7 @@
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L21" s="3"/>
     </row>
@@ -4170,7 +4191,7 @@
         <v>146</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -4203,7 +4224,7 @@
         <v>180</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -4237,7 +4258,7 @@
       </c>
       <c r="J24" s="13"/>
       <c r="K24" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -4271,7 +4292,7 @@
       </c>
       <c r="J25" s="13"/>
       <c r="K25" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -4305,7 +4326,7 @@
       </c>
       <c r="J26" s="13"/>
       <c r="K26" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -4339,7 +4360,7 @@
       </c>
       <c r="J27" s="13"/>
       <c r="K27" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -4373,7 +4394,7 @@
       </c>
       <c r="J28" s="13"/>
       <c r="K28" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -4407,7 +4428,7 @@
       </c>
       <c r="J29" s="13"/>
       <c r="K29" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -4441,7 +4462,7 @@
       </c>
       <c r="J30" s="13"/>
       <c r="K30" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -4475,7 +4496,7 @@
       </c>
       <c r="J31" s="13"/>
       <c r="K31" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -4509,7 +4530,7 @@
       </c>
       <c r="J32" s="13"/>
       <c r="K32" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4543,7 +4564,7 @@
       </c>
       <c r="J33" s="13"/>
       <c r="K33" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4577,7 +4598,7 @@
       </c>
       <c r="J34" s="13"/>
       <c r="K34" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4611,7 +4632,7 @@
       </c>
       <c r="J35" s="13"/>
       <c r="K35" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -4645,7 +4666,7 @@
       </c>
       <c r="J36" s="13"/>
       <c r="K36" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4679,7 +4700,7 @@
       </c>
       <c r="J37" s="13"/>
       <c r="K37" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -4713,7 +4734,7 @@
       </c>
       <c r="J38" s="13"/>
       <c r="K38" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -4747,7 +4768,7 @@
       </c>
       <c r="J39" s="13"/>
       <c r="K39" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -4781,7 +4802,7 @@
       </c>
       <c r="J40" s="13"/>
       <c r="K40" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -4815,7 +4836,7 @@
       </c>
       <c r="J41" s="13"/>
       <c r="K41" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -4849,7 +4870,7 @@
       </c>
       <c r="J42" s="13"/>
       <c r="K42" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -4883,7 +4904,7 @@
       </c>
       <c r="J43" s="13"/>
       <c r="K43" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -4917,7 +4938,7 @@
       </c>
       <c r="J44" s="13"/>
       <c r="K44" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -4951,7 +4972,7 @@
       </c>
       <c r="J45" s="13"/>
       <c r="K45" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -4985,7 +5006,7 @@
       </c>
       <c r="J46" s="13"/>
       <c r="K46" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -5019,7 +5040,7 @@
       </c>
       <c r="J47" s="13"/>
       <c r="K47" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -5053,7 +5074,7 @@
       </c>
       <c r="J48" s="13"/>
       <c r="K48" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -5481,9 +5502,11 @@
     <hyperlink ref="M9" r:id="rId2" xr:uid="{58671AAD-F2F2-47B6-9253-073208E89680}"/>
     <hyperlink ref="M16" r:id="rId3" xr:uid="{9936B76F-B377-4FE6-9BE3-317950F81D0C}"/>
     <hyperlink ref="N7" r:id="rId4" xr:uid="{34EB5817-7AEF-4055-973E-042FD52EDB95}"/>
-    <hyperlink ref="N15" r:id="rId5" xr:uid="{1C256CF5-232E-4CD0-9B21-D99C0C8BE300}"/>
-    <hyperlink ref="K3" r:id="rId6" display="https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg" xr:uid="{9D55401A-734C-478F-B8D1-3EA1DBF1054B}"/>
-    <hyperlink ref="K6" r:id="rId7" xr:uid="{AB762D55-2876-46AD-BD09-CF7CECA0AC70}"/>
+    <hyperlink ref="K3" r:id="rId5" display="https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg" xr:uid="{9D55401A-734C-478F-B8D1-3EA1DBF1054B}"/>
+    <hyperlink ref="K6" r:id="rId6" xr:uid="{AB762D55-2876-46AD-BD09-CF7CECA0AC70}"/>
+    <hyperlink ref="N15" r:id="rId7" xr:uid="{367C55C2-5B31-4F6C-8B5B-778B591A5594}"/>
+    <hyperlink ref="N2" r:id="rId8" xr:uid="{92E7935C-C54F-4FA7-AD23-121F6D1B83AE}"/>
+    <hyperlink ref="N6" r:id="rId9" xr:uid="{E50CEE3F-8265-4EFB-B2C2-60689A7334BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8374,24 +8397,24 @@
         <v>279</v>
       </c>
       <c r="I1" t="s">
+        <v>456</v>
+      </c>
+      <c r="J1" t="s">
         <v>457</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>458</v>
-      </c>
-      <c r="K1" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="I2" t="s">
+        <v>459</v>
+      </c>
+      <c r="J2" t="s">
         <v>460</v>
       </c>
-      <c r="J2" t="s">
-        <v>461</v>
-      </c>
       <c r="K2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -8399,25 +8422,25 @@
         <v>280</v>
       </c>
       <c r="I3" t="s">
+        <v>461</v>
+      </c>
+      <c r="J3" t="s">
         <v>462</v>
       </c>
-      <c r="J3" t="s">
-        <v>463</v>
-      </c>
       <c r="K3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="18"/>
       <c r="I4" t="s">
+        <v>463</v>
+      </c>
+      <c r="J4" t="s">
         <v>464</v>
       </c>
-      <c r="J4" t="s">
-        <v>465</v>
-      </c>
       <c r="K4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -8425,25 +8448,25 @@
         <v>281</v>
       </c>
       <c r="I5" t="s">
+        <v>465</v>
+      </c>
+      <c r="J5" t="s">
         <v>466</v>
       </c>
-      <c r="J5" t="s">
-        <v>467</v>
-      </c>
       <c r="K5" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="18"/>
       <c r="I6" t="s">
+        <v>467</v>
+      </c>
+      <c r="J6" t="s">
         <v>468</v>
       </c>
-      <c r="J6" t="s">
-        <v>469</v>
-      </c>
       <c r="K6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -8451,25 +8474,25 @@
         <v>282</v>
       </c>
       <c r="I7" t="s">
+        <v>469</v>
+      </c>
+      <c r="J7" t="s">
         <v>470</v>
       </c>
-      <c r="J7" t="s">
-        <v>471</v>
-      </c>
       <c r="K7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="18"/>
       <c r="I8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J8" t="s">
+        <v>477</v>
+      </c>
+      <c r="K8" t="s">
         <v>478</v>
-      </c>
-      <c r="K8" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -8477,24 +8500,24 @@
         <v>283</v>
       </c>
       <c r="I9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="J9" t="s">
+        <v>479</v>
+      </c>
+      <c r="K9" t="s">
         <v>480</v>
-      </c>
-      <c r="K9" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="I10" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="J10" t="s">
+        <v>481</v>
+      </c>
+      <c r="K10" t="s">
         <v>482</v>
-      </c>
-      <c r="K10" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="17.399999999999999">
@@ -8502,24 +8525,24 @@
         <v>284</v>
       </c>
       <c r="I11" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="J11" t="s">
+        <v>483</v>
+      </c>
+      <c r="K11" t="s">
         <v>484</v>
-      </c>
-      <c r="K11" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="I12" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J12" t="s">
+        <v>485</v>
+      </c>
+      <c r="K12" t="s">
         <v>486</v>
-      </c>
-      <c r="K12" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -8527,13 +8550,13 @@
         <v>285</v>
       </c>
       <c r="I13" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J13" t="s">
+        <v>487</v>
+      </c>
+      <c r="K13" t="s">
         <v>488</v>
-      </c>
-      <c r="K13" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -8672,142 +8695,142 @@
     </row>
     <row r="59" spans="1:6" ht="42.3">
       <c r="A59" s="22" t="s">
+        <v>495</v>
+      </c>
+      <c r="B59" s="22" t="s">
         <v>496</v>
       </c>
-      <c r="B59" s="22" t="s">
+      <c r="C59" s="22" t="s">
         <v>497</v>
       </c>
-      <c r="C59" s="22" t="s">
+      <c r="D59" s="22" t="s">
         <v>498</v>
       </c>
-      <c r="D59" s="22" t="s">
+      <c r="E59" s="22" t="s">
         <v>499</v>
       </c>
-      <c r="E59" s="22" t="s">
+      <c r="F59" s="22" t="s">
         <v>500</v>
-      </c>
-      <c r="F59" s="22" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="27.6">
       <c r="A60" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="B60" s="23" t="s">
         <v>502</v>
       </c>
-      <c r="B60" s="23" t="s">
+      <c r="C60" s="22" t="s">
         <v>503</v>
       </c>
-      <c r="C60" s="22" t="s">
+      <c r="D60" s="25" t="s">
         <v>504</v>
       </c>
-      <c r="D60" s="25" t="s">
+      <c r="E60" s="23" t="s">
         <v>505</v>
       </c>
-      <c r="E60" s="23" t="s">
+      <c r="F60" s="23" t="s">
         <v>506</v>
-      </c>
-      <c r="F60" s="23" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="27.9">
       <c r="A61" s="22" t="s">
+        <v>507</v>
+      </c>
+      <c r="B61" s="23" t="s">
         <v>508</v>
       </c>
-      <c r="B61" s="23" t="s">
+      <c r="C61" s="22" t="s">
         <v>509</v>
       </c>
-      <c r="C61" s="22" t="s">
+      <c r="D61" s="25" t="s">
         <v>510</v>
       </c>
-      <c r="D61" s="25" t="s">
+      <c r="E61" s="23" t="s">
         <v>511</v>
       </c>
-      <c r="E61" s="23" t="s">
+      <c r="F61" s="23" t="s">
         <v>512</v>
-      </c>
-      <c r="F61" s="23" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="27.6">
       <c r="A62" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="B62" s="23" t="s">
         <v>514</v>
       </c>
-      <c r="B62" s="23" t="s">
+      <c r="C62" s="22" t="s">
         <v>515</v>
       </c>
-      <c r="C62" s="22" t="s">
+      <c r="D62" s="25" t="s">
         <v>516</v>
       </c>
-      <c r="D62" s="25" t="s">
+      <c r="E62" s="23" t="s">
         <v>517</v>
       </c>
-      <c r="E62" s="23" t="s">
-        <v>518</v>
-      </c>
       <c r="F62" s="23" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="27.6">
       <c r="A63" s="22" t="s">
+        <v>518</v>
+      </c>
+      <c r="B63" s="23" t="s">
         <v>519</v>
       </c>
-      <c r="B63" s="23" t="s">
+      <c r="C63" s="22" t="s">
         <v>520</v>
       </c>
-      <c r="C63" s="22" t="s">
+      <c r="D63" s="25" t="s">
         <v>521</v>
       </c>
-      <c r="D63" s="25" t="s">
+      <c r="E63" s="23" t="s">
         <v>522</v>
       </c>
-      <c r="E63" s="23" t="s">
+      <c r="F63" s="23" t="s">
         <v>523</v>
-      </c>
-      <c r="F63" s="23" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="27.9">
       <c r="A64" s="22" t="s">
+        <v>524</v>
+      </c>
+      <c r="B64" s="23" t="s">
         <v>525</v>
       </c>
-      <c r="B64" s="23" t="s">
+      <c r="C64" s="22" t="s">
         <v>526</v>
       </c>
-      <c r="C64" s="22" t="s">
+      <c r="D64" s="25" t="s">
         <v>527</v>
       </c>
-      <c r="D64" s="25" t="s">
+      <c r="E64" s="23" t="s">
         <v>528</v>
       </c>
-      <c r="E64" s="23" t="s">
+      <c r="F64" s="23" t="s">
         <v>529</v>
-      </c>
-      <c r="F64" s="23" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="27.6">
       <c r="A65" s="22" t="s">
+        <v>530</v>
+      </c>
+      <c r="B65" s="24" t="s">
         <v>531</v>
       </c>
-      <c r="B65" s="24" t="s">
-        <v>532</v>
-      </c>
       <c r="C65" s="22" t="s">
+        <v>503</v>
+      </c>
+      <c r="D65" s="25" t="s">
         <v>504</v>
       </c>
-      <c r="D65" s="25" t="s">
+      <c r="E65" s="23" t="s">
         <v>505</v>
       </c>
-      <c r="E65" s="23" t="s">
+      <c r="F65" s="23" t="s">
         <v>506</v>
-      </c>
-      <c r="F65" s="23" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="66" spans="1:6">

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E53D9DB-AEE0-4F14-8D05-868E09599CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964B2CC4-0B5C-4C80-AB54-A021DE5E5972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
   <sheets>
     <sheet name="Branding" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="541">
   <si>
     <t>Contact</t>
   </si>
@@ -1978,12 +1978,6 @@
     <t>ITM200</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg</t>
-  </si>
-  <si>
     <t>Current File</t>
   </si>
   <si>
@@ -2397,6 +2391,9 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/banner/Banner01.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/banner/Banner02.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM002.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM002.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg</t>
   </si>
 </sst>
 </file>
@@ -3113,7 +3110,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -3193,16 +3190,16 @@
         <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="M2">
         <v>15</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -3287,7 +3284,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3324,7 +3321,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3472,7 +3469,7 @@
         <v>73</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -3506,7 +3503,7 @@
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="2" t="s">
-        <v>455</v>
+        <v>540</v>
       </c>
       <c r="L3" s="3"/>
     </row>
@@ -3540,9 +3537,7 @@
         <v>103</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K4" s="2"/>
       <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:14">
@@ -3575,9 +3570,7 @@
         <v>107</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K5" s="2"/>
       <c r="L5" s="3"/>
     </row>
     <row r="6" spans="1:14">
@@ -3612,12 +3605,10 @@
       <c r="J6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K6" s="2"/>
       <c r="L6" s="3"/>
       <c r="N6" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -3650,12 +3641,10 @@
         <v>188</v>
       </c>
       <c r="J7" s="3"/>
-      <c r="K7" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K7" s="2"/>
       <c r="L7" s="3"/>
       <c r="N7" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3688,9 +3677,7 @@
         <v>111</v>
       </c>
       <c r="J8" s="3"/>
-      <c r="K8" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K8" s="2"/>
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="1:14">
@@ -3723,9 +3710,7 @@
         <v>115</v>
       </c>
       <c r="J9" s="3"/>
-      <c r="K9" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K9" s="2"/>
       <c r="L9" s="3"/>
       <c r="M9" s="2" t="s">
         <v>73</v>
@@ -3761,9 +3746,7 @@
         <v>203</v>
       </c>
       <c r="J10" s="3"/>
-      <c r="K10" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K10" s="2"/>
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:14">
@@ -3796,9 +3779,7 @@
         <v>205</v>
       </c>
       <c r="J11" s="3"/>
-      <c r="K11" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K11" s="2"/>
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:14">
@@ -3831,9 +3812,7 @@
         <v>124</v>
       </c>
       <c r="J12" s="3"/>
-      <c r="K12" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K12" s="2"/>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="1:14">
@@ -3866,9 +3845,7 @@
         <v>208</v>
       </c>
       <c r="J13" s="3"/>
-      <c r="K13" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="1:14">
@@ -3901,9 +3878,7 @@
         <v>210</v>
       </c>
       <c r="J14" s="3"/>
-      <c r="K14" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K14" s="2"/>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:14">
@@ -3936,12 +3911,10 @@
         <v>212</v>
       </c>
       <c r="J15" s="3"/>
-      <c r="K15" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K15" s="2"/>
       <c r="L15" s="3"/>
       <c r="N15" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -3976,9 +3949,7 @@
       <c r="J16" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K16" s="2"/>
       <c r="L16" s="3"/>
       <c r="M16" s="2" t="s">
         <v>73</v>
@@ -4014,9 +3985,7 @@
         <v>128</v>
       </c>
       <c r="J17" s="3"/>
-      <c r="K17" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K17" s="2"/>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="1:12">
@@ -4049,9 +4018,7 @@
         <v>133</v>
       </c>
       <c r="J18" s="3"/>
-      <c r="K18" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K18" s="2"/>
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="1:12">
@@ -4084,9 +4051,7 @@
         <v>136</v>
       </c>
       <c r="J19" s="3"/>
-      <c r="K19" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K19" s="2"/>
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="1:12">
@@ -4121,9 +4086,7 @@
       <c r="J20" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K20" s="2"/>
       <c r="L20" s="3"/>
     </row>
     <row r="21" spans="1:12">
@@ -4156,9 +4119,7 @@
         <v>140</v>
       </c>
       <c r="J21" s="3"/>
-      <c r="K21" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K21" s="2"/>
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="1:12">
@@ -4190,9 +4151,7 @@
       <c r="I22" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K22" s="2"/>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="13" t="s">
@@ -4223,9 +4182,7 @@
       <c r="I23" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="K23" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K23" s="2"/>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="13" t="s">
@@ -4257,9 +4214,7 @@
         <v>150</v>
       </c>
       <c r="J24" s="13"/>
-      <c r="K24" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K24" s="2"/>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="13" t="s">
@@ -4291,9 +4246,7 @@
         <v>218</v>
       </c>
       <c r="J25" s="13"/>
-      <c r="K25" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K25" s="2"/>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="13" t="s">
@@ -4325,9 +4278,7 @@
         <v>153</v>
       </c>
       <c r="J26" s="13"/>
-      <c r="K26" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K26" s="2"/>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="13" t="s">
@@ -4359,9 +4310,7 @@
         <v>221</v>
       </c>
       <c r="J27" s="13"/>
-      <c r="K27" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K27" s="2"/>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="13" t="s">
@@ -4393,9 +4342,7 @@
         <v>184</v>
       </c>
       <c r="J28" s="13"/>
-      <c r="K28" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K28" s="2"/>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="13" t="s">
@@ -4427,9 +4374,7 @@
         <v>157</v>
       </c>
       <c r="J29" s="13"/>
-      <c r="K29" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K29" s="2"/>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="13" t="s">
@@ -4461,9 +4406,7 @@
         <v>224</v>
       </c>
       <c r="J30" s="13"/>
-      <c r="K30" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K30" s="2"/>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="13" t="s">
@@ -4495,9 +4438,7 @@
         <v>227</v>
       </c>
       <c r="J31" s="13"/>
-      <c r="K31" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K31" s="2"/>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="13" t="s">
@@ -4529,9 +4470,7 @@
         <v>228</v>
       </c>
       <c r="J32" s="13"/>
-      <c r="K32" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K32" s="2"/>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="13" t="s">
@@ -4563,9 +4502,7 @@
         <v>231</v>
       </c>
       <c r="J33" s="13"/>
-      <c r="K33" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K33" s="2"/>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="13" t="s">
@@ -4597,9 +4534,7 @@
         <v>234</v>
       </c>
       <c r="J34" s="13"/>
-      <c r="K34" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K34" s="2"/>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="13" t="s">
@@ -4631,9 +4566,7 @@
         <v>237</v>
       </c>
       <c r="J35" s="13"/>
-      <c r="K35" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K35" s="2"/>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="13" t="s">
@@ -4665,9 +4598,7 @@
         <v>237</v>
       </c>
       <c r="J36" s="13"/>
-      <c r="K36" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K36" s="2"/>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="13" t="s">
@@ -4699,9 +4630,7 @@
         <v>237</v>
       </c>
       <c r="J37" s="13"/>
-      <c r="K37" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K37" s="2"/>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="13" t="s">
@@ -4733,9 +4662,7 @@
         <v>245</v>
       </c>
       <c r="J38" s="13"/>
-      <c r="K38" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K38" s="2"/>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="13" t="s">
@@ -4767,9 +4694,7 @@
         <v>245</v>
       </c>
       <c r="J39" s="13"/>
-      <c r="K39" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K39" s="2"/>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="13" t="s">
@@ -4801,9 +4726,7 @@
         <v>249</v>
       </c>
       <c r="J40" s="13"/>
-      <c r="K40" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K40" s="2"/>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="13" t="s">
@@ -4835,9 +4758,7 @@
         <v>252</v>
       </c>
       <c r="J41" s="13"/>
-      <c r="K41" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K41" s="2"/>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="13" t="s">
@@ -4869,9 +4790,7 @@
         <v>245</v>
       </c>
       <c r="J42" s="13"/>
-      <c r="K42" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K42" s="2"/>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="13" t="s">
@@ -4903,9 +4822,7 @@
         <v>257</v>
       </c>
       <c r="J43" s="13"/>
-      <c r="K43" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K43" s="2"/>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="13" t="s">
@@ -4937,9 +4854,7 @@
         <v>260</v>
       </c>
       <c r="J44" s="13"/>
-      <c r="K44" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K44" s="2"/>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="13" t="s">
@@ -4971,9 +4886,7 @@
         <v>263</v>
       </c>
       <c r="J45" s="13"/>
-      <c r="K45" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K45" s="2"/>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="13" t="s">
@@ -5005,9 +4918,7 @@
         <v>161</v>
       </c>
       <c r="J46" s="13"/>
-      <c r="K46" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K46" s="2"/>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="13" t="s">
@@ -5039,9 +4950,7 @@
         <v>196</v>
       </c>
       <c r="J47" s="13"/>
-      <c r="K47" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K47" s="2"/>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="13" t="s">
@@ -5073,9 +4982,7 @@
         <v>166</v>
       </c>
       <c r="J48" s="13"/>
-      <c r="K48" s="2" t="s">
-        <v>454</v>
-      </c>
+      <c r="K48" s="2"/>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="13" t="s">
@@ -5502,11 +5409,10 @@
     <hyperlink ref="M9" r:id="rId2" xr:uid="{58671AAD-F2F2-47B6-9253-073208E89680}"/>
     <hyperlink ref="M16" r:id="rId3" xr:uid="{9936B76F-B377-4FE6-9BE3-317950F81D0C}"/>
     <hyperlink ref="N7" r:id="rId4" xr:uid="{34EB5817-7AEF-4055-973E-042FD52EDB95}"/>
-    <hyperlink ref="K3" r:id="rId5" display="https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg" xr:uid="{9D55401A-734C-478F-B8D1-3EA1DBF1054B}"/>
-    <hyperlink ref="K6" r:id="rId6" xr:uid="{AB762D55-2876-46AD-BD09-CF7CECA0AC70}"/>
-    <hyperlink ref="N15" r:id="rId7" xr:uid="{367C55C2-5B31-4F6C-8B5B-778B591A5594}"/>
-    <hyperlink ref="N2" r:id="rId8" xr:uid="{92E7935C-C54F-4FA7-AD23-121F6D1B83AE}"/>
-    <hyperlink ref="N6" r:id="rId9" xr:uid="{E50CEE3F-8265-4EFB-B2C2-60689A7334BB}"/>
+    <hyperlink ref="K3" r:id="rId5" display="https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM002.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM002.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg" xr:uid="{9D55401A-734C-478F-B8D1-3EA1DBF1054B}"/>
+    <hyperlink ref="N15" r:id="rId6" xr:uid="{367C55C2-5B31-4F6C-8B5B-778B591A5594}"/>
+    <hyperlink ref="N2" r:id="rId7" xr:uid="{92E7935C-C54F-4FA7-AD23-121F6D1B83AE}"/>
+    <hyperlink ref="N6" r:id="rId8" xr:uid="{E50CEE3F-8265-4EFB-B2C2-60689A7334BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8397,24 +8303,24 @@
         <v>279</v>
       </c>
       <c r="I1" t="s">
+        <v>454</v>
+      </c>
+      <c r="J1" t="s">
+        <v>455</v>
+      </c>
+      <c r="K1" t="s">
         <v>456</v>
-      </c>
-      <c r="J1" t="s">
-        <v>457</v>
-      </c>
-      <c r="K1" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="I2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="J2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -8422,25 +8328,25 @@
         <v>280</v>
       </c>
       <c r="I3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="18"/>
       <c r="I4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="K4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -8448,25 +8354,25 @@
         <v>281</v>
       </c>
       <c r="I5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="J5" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="18"/>
       <c r="I6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="J6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -8474,25 +8380,25 @@
         <v>282</v>
       </c>
       <c r="I7" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="J7" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K7" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="18"/>
       <c r="I8" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="J8" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="K8" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -8500,24 +8406,24 @@
         <v>283</v>
       </c>
       <c r="I9" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="J9" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="K9" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="I10" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J10" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="K10" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="17.399999999999999">
@@ -8525,24 +8431,24 @@
         <v>284</v>
       </c>
       <c r="I11" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="J11" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="K11" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="I12" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="J12" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="K12" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -8550,13 +8456,13 @@
         <v>285</v>
       </c>
       <c r="I13" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J13" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K13" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -8695,142 +8601,142 @@
     </row>
     <row r="59" spans="1:6" ht="42.3">
       <c r="A59" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="B59" s="22" t="s">
+        <v>494</v>
+      </c>
+      <c r="C59" s="22" t="s">
         <v>495</v>
       </c>
-      <c r="B59" s="22" t="s">
+      <c r="D59" s="22" t="s">
         <v>496</v>
       </c>
-      <c r="C59" s="22" t="s">
+      <c r="E59" s="22" t="s">
         <v>497</v>
       </c>
-      <c r="D59" s="22" t="s">
+      <c r="F59" s="22" t="s">
         <v>498</v>
-      </c>
-      <c r="E59" s="22" t="s">
-        <v>499</v>
-      </c>
-      <c r="F59" s="22" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="27.6">
       <c r="A60" s="22" t="s">
+        <v>499</v>
+      </c>
+      <c r="B60" s="23" t="s">
+        <v>500</v>
+      </c>
+      <c r="C60" s="22" t="s">
         <v>501</v>
       </c>
-      <c r="B60" s="23" t="s">
+      <c r="D60" s="25" t="s">
         <v>502</v>
       </c>
-      <c r="C60" s="22" t="s">
+      <c r="E60" s="23" t="s">
         <v>503</v>
       </c>
-      <c r="D60" s="25" t="s">
+      <c r="F60" s="23" t="s">
         <v>504</v>
-      </c>
-      <c r="E60" s="23" t="s">
-        <v>505</v>
-      </c>
-      <c r="F60" s="23" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="27.9">
       <c r="A61" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="B61" s="23" t="s">
+        <v>506</v>
+      </c>
+      <c r="C61" s="22" t="s">
         <v>507</v>
       </c>
-      <c r="B61" s="23" t="s">
+      <c r="D61" s="25" t="s">
         <v>508</v>
       </c>
-      <c r="C61" s="22" t="s">
+      <c r="E61" s="23" t="s">
         <v>509</v>
       </c>
-      <c r="D61" s="25" t="s">
+      <c r="F61" s="23" t="s">
         <v>510</v>
-      </c>
-      <c r="E61" s="23" t="s">
-        <v>511</v>
-      </c>
-      <c r="F61" s="23" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="27.6">
       <c r="A62" s="22" t="s">
+        <v>511</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>512</v>
+      </c>
+      <c r="C62" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="B62" s="23" t="s">
+      <c r="D62" s="25" t="s">
         <v>514</v>
       </c>
-      <c r="C62" s="22" t="s">
+      <c r="E62" s="23" t="s">
         <v>515</v>
       </c>
-      <c r="D62" s="25" t="s">
-        <v>516</v>
-      </c>
-      <c r="E62" s="23" t="s">
-        <v>517</v>
-      </c>
       <c r="F62" s="23" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="27.6">
       <c r="A63" s="22" t="s">
+        <v>516</v>
+      </c>
+      <c r="B63" s="23" t="s">
+        <v>517</v>
+      </c>
+      <c r="C63" s="22" t="s">
         <v>518</v>
       </c>
-      <c r="B63" s="23" t="s">
+      <c r="D63" s="25" t="s">
         <v>519</v>
       </c>
-      <c r="C63" s="22" t="s">
+      <c r="E63" s="23" t="s">
         <v>520</v>
       </c>
-      <c r="D63" s="25" t="s">
+      <c r="F63" s="23" t="s">
         <v>521</v>
-      </c>
-      <c r="E63" s="23" t="s">
-        <v>522</v>
-      </c>
-      <c r="F63" s="23" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="27.9">
       <c r="A64" s="22" t="s">
+        <v>522</v>
+      </c>
+      <c r="B64" s="23" t="s">
+        <v>523</v>
+      </c>
+      <c r="C64" s="22" t="s">
         <v>524</v>
       </c>
-      <c r="B64" s="23" t="s">
+      <c r="D64" s="25" t="s">
         <v>525</v>
       </c>
-      <c r="C64" s="22" t="s">
+      <c r="E64" s="23" t="s">
         <v>526</v>
       </c>
-      <c r="D64" s="25" t="s">
+      <c r="F64" s="23" t="s">
         <v>527</v>
-      </c>
-      <c r="E64" s="23" t="s">
-        <v>528</v>
-      </c>
-      <c r="F64" s="23" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="27.6">
       <c r="A65" s="22" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B65" s="24" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C65" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="D65" s="25" t="s">
+        <v>502</v>
+      </c>
+      <c r="E65" s="23" t="s">
         <v>503</v>
       </c>
-      <c r="D65" s="25" t="s">
+      <c r="F65" s="23" t="s">
         <v>504</v>
-      </c>
-      <c r="E65" s="23" t="s">
-        <v>505</v>
-      </c>
-      <c r="F65" s="23" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="66" spans="1:6">

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964B2CC4-0B5C-4C80-AB54-A021DE5E5972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EEFFA9A-DBB0-449E-8E51-ED748B2E6E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="542">
   <si>
     <t>Contact</t>
   </si>
@@ -642,9 +642,6 @@
   </si>
   <si>
     <t>Rice flour 500g, Coconut 100g, Water, Salt</t>
-  </si>
-  <si>
-    <t>Soft, lace-edged fermented rice pancake</t>
   </si>
   <si>
     <t>Rice 500g, Coconut milk 200ml, Yeast, Sugar</t>
@@ -2394,6 +2391,12 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM002.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM002.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM002.jpg</t>
+  </si>
+  <si>
+    <t>Soft, lace-edged fermented rice pancake . Kerala Appam (or Palappam) is a traditional South Indian fermented pancake made with ground rice, coconut, and coconut milk . It is characterized by its fluffy, spongy center and ultra-crispy, lacy edges. Cooked in a specialized curved pan called an appachatti, it is famously served with meat or vegetable stew, egg roast, or sweetened coconut milk .</t>
   </si>
 </sst>
 </file>
@@ -3110,7 +3113,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -3190,16 +3193,16 @@
         <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="M2">
         <v>15</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -3284,7 +3287,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3321,7 +3324,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3469,10 +3472,10 @@
         <v>73</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="31.8" customHeight="1">
       <c r="A3" s="13" t="s">
         <v>76</v>
       </c>
@@ -3493,17 +3496,17 @@
         <v>20</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>199</v>
+        <v>541</v>
       </c>
       <c r="H3" s="14">
         <v>124</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="L3" s="3"/>
     </row>
@@ -3528,7 +3531,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H4" s="14">
         <v>300</v>
@@ -3608,7 +3611,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="3"/>
       <c r="N6" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -3644,7 +3647,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="3"/>
       <c r="N7" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3737,13 +3740,13 @@
         <v>8</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H10" s="14">
         <v>521</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="2"/>
@@ -3770,13 +3773,13 @@
         <v>10</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H11" s="14">
         <v>154</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="2"/>
@@ -3836,13 +3839,13 @@
         <v>6</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H13" s="14">
         <v>523</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="2"/>
@@ -3869,13 +3872,13 @@
         <v>11</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H14" s="14">
         <v>620</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="2"/>
@@ -3902,19 +3905,19 @@
         <v>12</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H15" s="14">
         <v>856</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="2"/>
       <c r="L15" s="3"/>
       <c r="N15" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -4042,7 +4045,7 @@
         <v>25</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H19" s="14">
         <v>400</v>
@@ -4143,7 +4146,7 @@
         <v>17</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H22" s="14">
         <v>850</v>
@@ -4237,13 +4240,13 @@
         <v>12</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H25" s="14">
         <v>450</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J25" s="13"/>
       <c r="K25" s="2"/>
@@ -4269,7 +4272,7 @@
         <v>22</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H26" s="14">
         <v>600</v>
@@ -4277,7 +4280,9 @@
       <c r="I26" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="J26" s="13"/>
+      <c r="J26" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="K26" s="2"/>
     </row>
     <row r="27" spans="1:12">
@@ -4301,13 +4306,13 @@
         <v>10</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H27" s="14">
         <v>521</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J27" s="13"/>
       <c r="K27" s="2"/>
@@ -4397,15 +4402,17 @@
         <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H30" s="14">
         <v>5</v>
       </c>
       <c r="I30" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="J30" s="13"/>
+        <v>223</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="K30" s="2"/>
     </row>
     <row r="31" spans="1:12">
@@ -4429,13 +4436,13 @@
         <v>3</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H31" s="14">
         <v>65</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J31" s="13"/>
       <c r="K31" s="2"/>
@@ -4467,7 +4474,7 @@
         <v>30</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J32" s="13"/>
       <c r="K32" s="2"/>
@@ -4493,13 +4500,13 @@
         <v>3</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H33" s="14">
         <v>10</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J33" s="13"/>
       <c r="K33" s="2"/>
@@ -4525,13 +4532,13 @@
         <v>4</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H34" s="14">
         <v>85</v>
       </c>
       <c r="I34" s="15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J34" s="13"/>
       <c r="K34" s="2"/>
@@ -4557,13 +4564,13 @@
         <v>1</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H35" s="14">
         <v>0</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J35" s="13"/>
       <c r="K35" s="2"/>
@@ -4589,13 +4596,13 @@
         <v>2</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H36" s="14">
         <v>0</v>
       </c>
       <c r="I36" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J36" s="13"/>
       <c r="K36" s="2"/>
@@ -4621,13 +4628,13 @@
         <v>3</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H37" s="14">
         <v>0</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J37" s="13"/>
       <c r="K37" s="2"/>
@@ -4640,7 +4647,7 @@
         <v>33</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D38" s="13" t="str">
         <f>VLOOKUP(A38,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4653,15 +4660,17 @@
         <v>3</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H38" s="14">
         <v>150</v>
       </c>
       <c r="I38" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="J38" s="13"/>
+        <v>244</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="K38" s="2"/>
     </row>
     <row r="39" spans="1:11">
@@ -4672,7 +4681,7 @@
         <v>33</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D39" s="13" t="str">
         <f>VLOOKUP(A39,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4685,13 +4694,13 @@
         <v>3</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H39" s="14">
         <v>140</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J39" s="13"/>
       <c r="K39" s="2"/>
@@ -4704,7 +4713,7 @@
         <v>33</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D40" s="13" t="str">
         <f>VLOOKUP(A40,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4717,13 +4726,13 @@
         <v>3</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H40" s="14">
         <v>140</v>
       </c>
       <c r="I40" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J40" s="13"/>
       <c r="K40" s="2"/>
@@ -4736,7 +4745,7 @@
         <v>33</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D41" s="13" t="str">
         <f>VLOOKUP(A41,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4749,13 +4758,13 @@
         <v>3</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H41" s="14">
         <v>160</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J41" s="13"/>
       <c r="K41" s="2"/>
@@ -4768,7 +4777,7 @@
         <v>33</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D42" s="13" t="str">
         <f>VLOOKUP(A42,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4781,13 +4790,13 @@
         <v>3</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H42" s="14">
         <v>145</v>
       </c>
       <c r="I42" s="15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J42" s="13"/>
       <c r="K42" s="2"/>
@@ -4800,7 +4809,7 @@
         <v>33</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D43" s="13" t="str">
         <f>VLOOKUP(A43,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4813,15 +4822,17 @@
         <v>3</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H43" s="14">
         <v>150</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="J43" s="13"/>
+        <v>256</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="K43" s="2"/>
     </row>
     <row r="44" spans="1:11">
@@ -4845,13 +4856,13 @@
         <v>10</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H44" s="14">
         <v>135</v>
       </c>
       <c r="I44" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J44" s="13"/>
       <c r="K44" s="2"/>
@@ -4877,16 +4888,18 @@
         <v>12</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H45" s="14">
         <v>150</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J45" s="13"/>
-      <c r="K45" s="2"/>
+      <c r="K45" s="2" t="s">
+        <v>540</v>
+      </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="13" t="s">
@@ -4922,7 +4935,7 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B47" s="13" t="s">
         <v>33</v>
@@ -4954,7 +4967,7 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B48" s="13" t="s">
         <v>33</v>
@@ -4986,7 +4999,7 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B49" s="13" t="s">
         <v>171</v>
@@ -5005,20 +5018,22 @@
         <v>5</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H49" s="14">
         <v>220</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="J49" s="13"/>
+        <v>268</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="K49" s="2"/>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B50" s="13" t="s">
         <v>171</v>
@@ -5037,26 +5052,26 @@
         <v>5</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H50" s="14">
         <v>210</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J50" s="13"/>
       <c r="K50" s="2"/>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B51" s="13" t="s">
         <v>171</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D51" s="13" t="str">
         <f>VLOOKUP(A51,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -5082,13 +5097,13 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B52" s="13" t="s">
         <v>171</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D52" s="13" t="str">
         <f>VLOOKUP(A52,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -5109,7 +5124,9 @@
       <c r="I52" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="J52" s="13"/>
+      <c r="J52" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="K52" s="2"/>
     </row>
     <row r="53" spans="1:11">
@@ -5413,6 +5430,7 @@
     <hyperlink ref="N15" r:id="rId6" xr:uid="{367C55C2-5B31-4F6C-8B5B-778B591A5594}"/>
     <hyperlink ref="N2" r:id="rId7" xr:uid="{92E7935C-C54F-4FA7-AD23-121F6D1B83AE}"/>
     <hyperlink ref="N6" r:id="rId8" xr:uid="{E50CEE3F-8265-4EFB-B2C2-60689A7334BB}"/>
+    <hyperlink ref="K45" r:id="rId9" xr:uid="{07973ECC-8B08-45D3-A1FD-3F4FF3612009}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6654,7 +6672,7 @@
         <v>86</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6742,7 +6760,7 @@
         <v>94</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6753,7 +6771,7 @@
         <v>100</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6841,7 +6859,7 @@
         <v>134</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6852,7 +6870,7 @@
         <v>137</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6874,7 +6892,7 @@
         <v>145</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6885,7 +6903,7 @@
         <v>147</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6896,7 +6914,7 @@
         <v>151</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6907,7 +6925,7 @@
         <v>154</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6918,7 +6936,7 @@
         <v>158</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6929,7 +6947,7 @@
         <v>162</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -6940,7 +6958,7 @@
         <v>167</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -6951,7 +6969,7 @@
         <v>170</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -6962,7 +6980,7 @@
         <v>174</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -6973,7 +6991,7 @@
         <v>177</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -6984,7 +7002,7 @@
         <v>181</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -6995,7 +7013,7 @@
         <v>185</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -7006,7 +7024,7 @@
         <v>189</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -7025,7 +7043,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C47" s="13" t="s">
         <v>194</v>
@@ -7036,7 +7054,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C48" s="13" t="s">
         <v>164</v>
@@ -7047,10 +7065,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>266</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -7058,10 +7076,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="C50" s="13" t="s">
         <v>270</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -7069,10 +7087,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -7080,10 +7098,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>277</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -7091,7 +7109,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -7099,7 +7117,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -7107,7 +7125,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -7115,7 +7133,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -7123,7 +7141,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -7131,7 +7149,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -7139,7 +7157,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -7147,7 +7165,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -7155,7 +7173,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -7163,7 +7181,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -7171,7 +7189,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -7179,7 +7197,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -7187,7 +7205,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -7195,7 +7213,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -7203,7 +7221,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -7211,7 +7229,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -7219,7 +7237,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -7227,7 +7245,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -7235,7 +7253,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -7243,7 +7261,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -7251,7 +7269,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -7259,7 +7277,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -7267,7 +7285,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -7275,7 +7293,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -7283,7 +7301,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -7291,7 +7309,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -7299,7 +7317,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -7307,7 +7325,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -7315,7 +7333,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -7323,7 +7341,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -7331,7 +7349,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -7339,7 +7357,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -7347,7 +7365,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -7355,7 +7373,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -7363,7 +7381,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -7371,7 +7389,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -7379,7 +7397,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -7387,7 +7405,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -7395,7 +7413,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -7403,7 +7421,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -7411,7 +7429,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -7419,7 +7437,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -7427,7 +7445,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -7435,7 +7453,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -7443,7 +7461,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -7451,7 +7469,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -7459,7 +7477,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -7467,7 +7485,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -7475,7 +7493,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -7483,7 +7501,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -7491,7 +7509,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -7499,7 +7517,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -7507,7 +7525,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -7515,7 +7533,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -7523,7 +7541,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -7531,7 +7549,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -7539,7 +7557,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="13" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -7547,7 +7565,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -7555,7 +7573,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="13" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -7563,7 +7581,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -7571,7 +7589,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -7579,7 +7597,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -7587,7 +7605,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -7595,7 +7613,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -7603,7 +7621,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -7611,7 +7629,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -7619,7 +7637,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -7627,7 +7645,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -7635,7 +7653,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -7643,7 +7661,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -7651,7 +7669,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -7659,7 +7677,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -7667,7 +7685,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -7675,7 +7693,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -7683,7 +7701,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -7691,7 +7709,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -7699,7 +7717,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -7707,7 +7725,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -7715,7 +7733,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="13" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -7723,7 +7741,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -7731,7 +7749,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -7739,7 +7757,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -7747,7 +7765,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -7755,7 +7773,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -7763,7 +7781,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="13" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -7771,7 +7789,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -7779,7 +7797,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -7787,7 +7805,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -7795,7 +7813,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="13" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -7803,7 +7821,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -7811,7 +7829,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -7819,7 +7837,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -7827,7 +7845,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -7835,7 +7853,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -7843,7 +7861,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -7851,7 +7869,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -7859,7 +7877,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="13" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -7867,7 +7885,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -7875,7 +7893,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -7883,7 +7901,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -7891,7 +7909,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -7899,7 +7917,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -7907,7 +7925,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -7915,7 +7933,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -7923,7 +7941,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -7931,7 +7949,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -7939,7 +7957,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -7947,7 +7965,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -7955,7 +7973,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="13" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -7963,7 +7981,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="13" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -7971,7 +7989,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="13" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -7979,7 +7997,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -7987,7 +8005,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="13" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -7995,7 +8013,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -8003,7 +8021,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="13" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -8011,7 +8029,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="13" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -8019,7 +8037,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -8027,7 +8045,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -8035,7 +8053,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="13" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -8043,7 +8061,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -8051,7 +8069,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="13" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -8059,7 +8077,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -8067,7 +8085,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="13" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -8075,7 +8093,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -8083,7 +8101,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -8091,7 +8109,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -8099,7 +8117,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="13" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -8107,7 +8125,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -8115,7 +8133,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="13" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -8123,7 +8141,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="13" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -8131,7 +8149,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="13" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -8139,7 +8157,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -8147,7 +8165,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="13" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -8155,7 +8173,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="13" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -8163,7 +8181,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="13" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -8171,7 +8189,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -8179,7 +8197,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -8187,7 +8205,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="13" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -8195,7 +8213,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="13" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -8203,7 +8221,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="13" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -8211,7 +8229,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="13" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -8219,7 +8237,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="13" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -8227,7 +8245,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="13" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -8235,7 +8253,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="13" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -8243,7 +8261,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="13" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -8251,7 +8269,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="13" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -8259,7 +8277,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="13" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -8267,7 +8285,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="13" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -8275,7 +8293,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="13" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -8300,169 +8318,169 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999">
       <c r="A1" s="17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I1" t="s">
+        <v>453</v>
+      </c>
+      <c r="J1" t="s">
         <v>454</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>455</v>
-      </c>
-      <c r="K1" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="I2" t="s">
+        <v>456</v>
+      </c>
+      <c r="J2" t="s">
         <v>457</v>
       </c>
-      <c r="J2" t="s">
-        <v>458</v>
-      </c>
       <c r="K2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I3" t="s">
+        <v>458</v>
+      </c>
+      <c r="J3" t="s">
         <v>459</v>
       </c>
-      <c r="J3" t="s">
-        <v>460</v>
-      </c>
       <c r="K3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="18"/>
       <c r="I4" t="s">
+        <v>460</v>
+      </c>
+      <c r="J4" t="s">
         <v>461</v>
       </c>
-      <c r="J4" t="s">
-        <v>462</v>
-      </c>
       <c r="K4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I5" t="s">
+        <v>462</v>
+      </c>
+      <c r="J5" t="s">
         <v>463</v>
       </c>
-      <c r="J5" t="s">
-        <v>464</v>
-      </c>
       <c r="K5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="18"/>
       <c r="I6" t="s">
+        <v>464</v>
+      </c>
+      <c r="J6" t="s">
         <v>465</v>
       </c>
-      <c r="J6" t="s">
-        <v>466</v>
-      </c>
       <c r="K6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I7" t="s">
+        <v>466</v>
+      </c>
+      <c r="J7" t="s">
         <v>467</v>
       </c>
-      <c r="J7" t="s">
-        <v>468</v>
-      </c>
       <c r="K7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="18"/>
       <c r="I8" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="J8" t="s">
+        <v>474</v>
+      </c>
+      <c r="K8" t="s">
         <v>475</v>
-      </c>
-      <c r="K8" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I9" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J9" t="s">
+        <v>476</v>
+      </c>
+      <c r="K9" t="s">
         <v>477</v>
-      </c>
-      <c r="K9" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="I10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J10" t="s">
+        <v>478</v>
+      </c>
+      <c r="K10" t="s">
         <v>479</v>
-      </c>
-      <c r="K10" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="17.399999999999999">
       <c r="A11" s="17" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J11" t="s">
+        <v>480</v>
+      </c>
+      <c r="K11" t="s">
         <v>481</v>
-      </c>
-      <c r="K11" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="I12" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="J12" t="s">
+        <v>482</v>
+      </c>
+      <c r="K12" t="s">
         <v>483</v>
-      </c>
-      <c r="K12" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I13" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J13" t="s">
+        <v>484</v>
+      </c>
+      <c r="K13" t="s">
         <v>485</v>
-      </c>
-      <c r="K13" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -8470,7 +8488,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="19" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -8478,7 +8496,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -8486,17 +8504,17 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="17.399999999999999">
       <c r="A21" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -8504,7 +8522,7 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="19" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -8512,17 +8530,17 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="19" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="17.399999999999999">
       <c r="A31" s="17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -8530,7 +8548,7 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="19" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -8538,7 +8556,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -8546,7 +8564,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="19" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -8554,17 +8572,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="17.399999999999999">
       <c r="A43" s="17" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -8572,7 +8590,7 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="19" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="48" spans="1:1">
@@ -8580,7 +8598,7 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -8588,7 +8606,7 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -8596,147 +8614,147 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="19" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="42.3">
       <c r="A59" s="22" t="s">
+        <v>492</v>
+      </c>
+      <c r="B59" s="22" t="s">
         <v>493</v>
       </c>
-      <c r="B59" s="22" t="s">
+      <c r="C59" s="22" t="s">
         <v>494</v>
       </c>
-      <c r="C59" s="22" t="s">
+      <c r="D59" s="22" t="s">
         <v>495</v>
       </c>
-      <c r="D59" s="22" t="s">
+      <c r="E59" s="22" t="s">
         <v>496</v>
       </c>
-      <c r="E59" s="22" t="s">
+      <c r="F59" s="22" t="s">
         <v>497</v>
-      </c>
-      <c r="F59" s="22" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="27.6">
       <c r="A60" s="22" t="s">
+        <v>498</v>
+      </c>
+      <c r="B60" s="23" t="s">
         <v>499</v>
       </c>
-      <c r="B60" s="23" t="s">
+      <c r="C60" s="22" t="s">
         <v>500</v>
       </c>
-      <c r="C60" s="22" t="s">
+      <c r="D60" s="25" t="s">
         <v>501</v>
       </c>
-      <c r="D60" s="25" t="s">
+      <c r="E60" s="23" t="s">
         <v>502</v>
       </c>
-      <c r="E60" s="23" t="s">
+      <c r="F60" s="23" t="s">
         <v>503</v>
-      </c>
-      <c r="F60" s="23" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="27.9">
       <c r="A61" s="22" t="s">
+        <v>504</v>
+      </c>
+      <c r="B61" s="23" t="s">
         <v>505</v>
       </c>
-      <c r="B61" s="23" t="s">
+      <c r="C61" s="22" t="s">
         <v>506</v>
       </c>
-      <c r="C61" s="22" t="s">
+      <c r="D61" s="25" t="s">
         <v>507</v>
       </c>
-      <c r="D61" s="25" t="s">
+      <c r="E61" s="23" t="s">
         <v>508</v>
       </c>
-      <c r="E61" s="23" t="s">
+      <c r="F61" s="23" t="s">
         <v>509</v>
-      </c>
-      <c r="F61" s="23" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="27.6">
       <c r="A62" s="22" t="s">
+        <v>510</v>
+      </c>
+      <c r="B62" s="23" t="s">
         <v>511</v>
       </c>
-      <c r="B62" s="23" t="s">
+      <c r="C62" s="22" t="s">
         <v>512</v>
       </c>
-      <c r="C62" s="22" t="s">
+      <c r="D62" s="25" t="s">
         <v>513</v>
       </c>
-      <c r="D62" s="25" t="s">
+      <c r="E62" s="23" t="s">
         <v>514</v>
       </c>
-      <c r="E62" s="23" t="s">
-        <v>515</v>
-      </c>
       <c r="F62" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="27.6">
       <c r="A63" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="B63" s="23" t="s">
         <v>516</v>
       </c>
-      <c r="B63" s="23" t="s">
+      <c r="C63" s="22" t="s">
         <v>517</v>
       </c>
-      <c r="C63" s="22" t="s">
+      <c r="D63" s="25" t="s">
         <v>518</v>
       </c>
-      <c r="D63" s="25" t="s">
+      <c r="E63" s="23" t="s">
         <v>519</v>
       </c>
-      <c r="E63" s="23" t="s">
+      <c r="F63" s="23" t="s">
         <v>520</v>
-      </c>
-      <c r="F63" s="23" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="27.9">
       <c r="A64" s="22" t="s">
+        <v>521</v>
+      </c>
+      <c r="B64" s="23" t="s">
         <v>522</v>
       </c>
-      <c r="B64" s="23" t="s">
+      <c r="C64" s="22" t="s">
         <v>523</v>
       </c>
-      <c r="C64" s="22" t="s">
+      <c r="D64" s="25" t="s">
         <v>524</v>
       </c>
-      <c r="D64" s="25" t="s">
+      <c r="E64" s="23" t="s">
         <v>525</v>
       </c>
-      <c r="E64" s="23" t="s">
+      <c r="F64" s="23" t="s">
         <v>526</v>
-      </c>
-      <c r="F64" s="23" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="27.6">
       <c r="A65" s="22" t="s">
+        <v>527</v>
+      </c>
+      <c r="B65" s="24" t="s">
         <v>528</v>
       </c>
-      <c r="B65" s="24" t="s">
-        <v>529</v>
-      </c>
       <c r="C65" s="22" t="s">
+        <v>500</v>
+      </c>
+      <c r="D65" s="25" t="s">
         <v>501</v>
       </c>
-      <c r="D65" s="25" t="s">
+      <c r="E65" s="23" t="s">
         <v>502</v>
       </c>
-      <c r="E65" s="23" t="s">
+      <c r="F65" s="23" t="s">
         <v>503</v>
-      </c>
-      <c r="F65" s="23" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="66" spans="1:6">

--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\Codes\Restarant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EEFFA9A-DBB0-449E-8E51-ED748B2E6E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9A64FD-BE89-4ECA-A167-DF2B27479D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
@@ -644,9 +644,6 @@
     <t>Rice flour 500g, Coconut 100g, Water, Salt</t>
   </si>
   <si>
-    <t>Rice 500g, Coconut milk 200ml, Yeast, Sugar</t>
-  </si>
-  <si>
     <t>Flaky, multi-layered roasted flatbread</t>
   </si>
   <si>
@@ -2390,13 +2387,16 @@
     <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/banner/Banner01.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/banner/Banner02.jpg</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM002.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM002.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg</t>
-  </si>
-  <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM002.jpg</t>
   </si>
   <si>
-    <t>Soft, lace-edged fermented rice pancake . Kerala Appam (or Palappam) is a traditional South Indian fermented pancake made with ground rice, coconut, and coconut milk . It is characterized by its fluffy, spongy center and ultra-crispy, lacy edges. Cooked in a specialized curved pan called an appachatti, it is famously served with meat or vegetable stew, egg roast, or sweetened coconut milk .</t>
+    <t>https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM023.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM024.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soft, lace-edged fermented rice pancake . </t>
+  </si>
+  <si>
+    <t>Rice 500g, Coconut milk 200ml, Yeast, Sugar - Kerala Appam (or Palappam) is a traditional South Indian fermented pancake made with ground rice, coconut, and coconut milk . It is characterized by its fluffy, spongy center and ultra-crispy, lacy edges. Cooked in a specialized curved pan called an appachatti, it is famously served with meat or vegetable stew, egg roast, or sweetened coconut milk .</t>
   </si>
 </sst>
 </file>
@@ -3113,7 +3113,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -3193,16 +3193,16 @@
         <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="M2">
         <v>15</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -3287,7 +3287,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3324,7 +3324,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3472,7 +3472,7 @@
         <v>73</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="31.8" customHeight="1">
@@ -3496,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H3" s="14">
         <v>124</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>199</v>
+        <v>541</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="2" t="s">
@@ -3531,7 +3531,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H4" s="14">
         <v>300</v>
@@ -3611,7 +3611,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="3"/>
       <c r="N6" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -3647,7 +3647,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="3"/>
       <c r="N7" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3740,13 +3740,13 @@
         <v>8</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H10" s="14">
         <v>521</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="2"/>
@@ -3773,13 +3773,13 @@
         <v>10</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H11" s="14">
         <v>154</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="2"/>
@@ -3839,13 +3839,13 @@
         <v>6</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H13" s="14">
         <v>523</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="2"/>
@@ -3872,13 +3872,13 @@
         <v>11</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H14" s="14">
         <v>620</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="2"/>
@@ -3905,19 +3905,19 @@
         <v>12</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H15" s="14">
         <v>856</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="2"/>
       <c r="L15" s="3"/>
       <c r="N15" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -4045,7 +4045,7 @@
         <v>25</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H19" s="14">
         <v>400</v>
@@ -4146,7 +4146,7 @@
         <v>17</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H22" s="14">
         <v>850</v>
@@ -4240,13 +4240,13 @@
         <v>12</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H25" s="14">
         <v>450</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J25" s="13"/>
       <c r="K25" s="2"/>
@@ -4272,7 +4272,7 @@
         <v>22</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H26" s="14">
         <v>600</v>
@@ -4306,13 +4306,13 @@
         <v>10</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H27" s="14">
         <v>521</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J27" s="13"/>
       <c r="K27" s="2"/>
@@ -4402,13 +4402,13 @@
         <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H30" s="14">
         <v>5</v>
       </c>
       <c r="I30" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>60</v>
@@ -4436,13 +4436,13 @@
         <v>3</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H31" s="14">
         <v>65</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J31" s="13"/>
       <c r="K31" s="2"/>
@@ -4474,7 +4474,7 @@
         <v>30</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J32" s="13"/>
       <c r="K32" s="2"/>
@@ -4500,13 +4500,13 @@
         <v>3</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H33" s="14">
         <v>10</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J33" s="13"/>
       <c r="K33" s="2"/>
@@ -4532,13 +4532,13 @@
         <v>4</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H34" s="14">
         <v>85</v>
       </c>
       <c r="I34" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J34" s="13"/>
       <c r="K34" s="2"/>
@@ -4564,13 +4564,13 @@
         <v>1</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H35" s="14">
         <v>0</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J35" s="13"/>
       <c r="K35" s="2"/>
@@ -4596,13 +4596,13 @@
         <v>2</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H36" s="14">
         <v>0</v>
       </c>
       <c r="I36" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J36" s="13"/>
       <c r="K36" s="2"/>
@@ -4628,13 +4628,13 @@
         <v>3</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H37" s="14">
         <v>0</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J37" s="13"/>
       <c r="K37" s="2"/>
@@ -4647,7 +4647,7 @@
         <v>33</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D38" s="13" t="str">
         <f>VLOOKUP(A38,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4660,13 +4660,13 @@
         <v>3</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H38" s="14">
         <v>150</v>
       </c>
       <c r="I38" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>60</v>
@@ -4681,7 +4681,7 @@
         <v>33</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D39" s="13" t="str">
         <f>VLOOKUP(A39,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4694,13 +4694,13 @@
         <v>3</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H39" s="14">
         <v>140</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J39" s="13"/>
       <c r="K39" s="2"/>
@@ -4713,7 +4713,7 @@
         <v>33</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D40" s="13" t="str">
         <f>VLOOKUP(A40,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4726,13 +4726,13 @@
         <v>3</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H40" s="14">
         <v>140</v>
       </c>
       <c r="I40" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J40" s="13"/>
       <c r="K40" s="2"/>
@@ -4745,7 +4745,7 @@
         <v>33</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D41" s="13" t="str">
         <f>VLOOKUP(A41,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4758,13 +4758,13 @@
         <v>3</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H41" s="14">
         <v>160</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J41" s="13"/>
       <c r="K41" s="2"/>
@@ -4777,7 +4777,7 @@
         <v>33</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D42" s="13" t="str">
         <f>VLOOKUP(A42,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4790,13 +4790,13 @@
         <v>3</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H42" s="14">
         <v>145</v>
       </c>
       <c r="I42" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J42" s="13"/>
       <c r="K42" s="2"/>
@@ -4809,7 +4809,7 @@
         <v>33</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D43" s="13" t="str">
         <f>VLOOKUP(A43,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -4822,13 +4822,13 @@
         <v>3</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H43" s="14">
         <v>150</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>60</v>
@@ -4856,13 +4856,13 @@
         <v>10</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H44" s="14">
         <v>135</v>
       </c>
       <c r="I44" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J44" s="13"/>
       <c r="K44" s="2"/>
@@ -4888,17 +4888,17 @@
         <v>12</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H45" s="14">
         <v>150</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J45" s="13"/>
       <c r="K45" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -4935,7 +4935,7 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B47" s="13" t="s">
         <v>33</v>
@@ -4967,7 +4967,7 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B48" s="13" t="s">
         <v>33</v>
@@ -4999,7 +4999,7 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B49" s="13" t="s">
         <v>171</v>
@@ -5018,13 +5018,13 @@
         <v>5</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H49" s="14">
         <v>220</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>60</v>
@@ -5033,7 +5033,7 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B50" s="13" t="s">
         <v>171</v>
@@ -5052,26 +5052,26 @@
         <v>5</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H50" s="14">
         <v>210</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J50" s="13"/>
       <c r="K50" s="2"/>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B51" s="13" t="s">
         <v>171</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D51" s="13" t="str">
         <f>VLOOKUP(A51,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -5097,13 +5097,13 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B52" s="13" t="s">
         <v>171</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D52" s="13" t="str">
         <f>VLOOKUP(A52,Inventory!$B$2:$C$201,2,FALSE)</f>
@@ -5426,7 +5426,7 @@
     <hyperlink ref="M9" r:id="rId2" xr:uid="{58671AAD-F2F2-47B6-9253-073208E89680}"/>
     <hyperlink ref="M16" r:id="rId3" xr:uid="{9936B76F-B377-4FE6-9BE3-317950F81D0C}"/>
     <hyperlink ref="N7" r:id="rId4" xr:uid="{34EB5817-7AEF-4055-973E-042FD52EDB95}"/>
-    <hyperlink ref="K3" r:id="rId5" display="https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM002.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM002.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg" xr:uid="{9D55401A-734C-478F-B8D1-3EA1DBF1054B}"/>
+    <hyperlink ref="K3" r:id="rId5" display="https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM023.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM024.jpg,https://raw.githubusercontent.com/Rmoosa2014/Restaurant-menu/main/images/ItemImages/ITM001.jpg" xr:uid="{9D55401A-734C-478F-B8D1-3EA1DBF1054B}"/>
     <hyperlink ref="N15" r:id="rId6" xr:uid="{367C55C2-5B31-4F6C-8B5B-778B591A5594}"/>
     <hyperlink ref="N2" r:id="rId7" xr:uid="{92E7935C-C54F-4FA7-AD23-121F6D1B83AE}"/>
     <hyperlink ref="N6" r:id="rId8" xr:uid="{E50CEE3F-8265-4EFB-B2C2-60689A7334BB}"/>
@@ -6672,7 +6672,7 @@
         <v>86</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6760,7 +6760,7 @@
         <v>94</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6771,7 +6771,7 @@
         <v>100</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6859,7 +6859,7 @@
         <v>134</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6870,7 +6870,7 @@
         <v>137</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6892,7 +6892,7 @@
         <v>145</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6903,7 +6903,7 @@
         <v>147</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6914,7 +6914,7 @@
         <v>151</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6925,7 +6925,7 @@
         <v>154</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6936,7 +6936,7 @@
         <v>158</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6947,7 +6947,7 @@
         <v>162</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -6958,7 +6958,7 @@
         <v>167</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -6969,7 +6969,7 @@
         <v>170</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -6980,7 +6980,7 @@
         <v>174</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -6991,7 +6991,7 @@
         <v>177</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -7002,7 +7002,7 @@
         <v>181</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -7013,7 +7013,7 @@
         <v>185</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -7024,7 +7024,7 @@
         <v>189</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -7043,7 +7043,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C47" s="13" t="s">
         <v>194</v>
@@ -7054,7 +7054,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C48" s="13" t="s">
         <v>164</v>
@@ -7065,10 +7065,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>265</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -7076,10 +7076,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="C50" s="13" t="s">
         <v>269</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -7087,10 +7087,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -7098,10 +7098,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>276</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -7109,7 +7109,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -7117,7 +7117,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -7125,7 +7125,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -7133,7 +7133,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -7141,7 +7141,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -7149,7 +7149,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -7157,7 +7157,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -7165,7 +7165,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -7173,7 +7173,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -7181,7 +7181,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -7189,7 +7189,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -7197,7 +7197,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -7205,7 +7205,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -7213,7 +7213,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -7221,7 +7221,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -7229,7 +7229,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -7237,7 +7237,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -7245,7 +7245,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -7253,7 +7253,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -7261,7 +7261,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -7269,7 +7269,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -7277,7 +7277,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -7285,7 +7285,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -7293,7 +7293,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -7301,7 +7301,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -7309,7 +7309,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -7317,7 +7317,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -7325,7 +7325,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -7333,7 +7333,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -7341,7 +7341,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -7349,7 +7349,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -7357,7 +7357,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -7365,7 +7365,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -7373,7 +7373,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -7381,7 +7381,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -7389,7 +7389,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -7397,7 +7397,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -7405,7 +7405,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -7413,7 +7413,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -7421,7 +7421,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -7429,7 +7429,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -7437,7 +7437,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -7445,7 +7445,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -7453,7 +7453,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -7461,7 +7461,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -7469,7 +7469,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -7477,7 +7477,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -7485,7 +7485,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -7493,7 +7493,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -7501,7 +7501,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -7509,7 +7509,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -7517,7 +7517,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -7525,7 +7525,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -7533,7 +7533,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -7541,7 +7541,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -7549,7 +7549,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -7557,7 +7557,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="13" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -7565,7 +7565,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -7573,7 +7573,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -7581,7 +7581,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -7589,7 +7589,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -7597,7 +7597,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -7605,7 +7605,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -7613,7 +7613,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -7621,7 +7621,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -7629,7 +7629,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -7637,7 +7637,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -7645,7 +7645,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -7653,7 +7653,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -7661,7 +7661,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -7669,7 +7669,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -7677,7 +7677,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -7685,7 +7685,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -7693,7 +7693,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -7701,7 +7701,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -7709,7 +7709,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -7717,7 +7717,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -7725,7 +7725,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -7733,7 +7733,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="13" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -7741,7 +7741,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -7749,7 +7749,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -7757,7 +7757,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -7765,7 +7765,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -7773,7 +7773,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -7781,7 +7781,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="13" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -7789,7 +7789,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -7797,7 +7797,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -7805,7 +7805,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -7813,7 +7813,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="13" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -7821,7 +7821,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -7829,7 +7829,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -7837,7 +7837,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -7845,7 +7845,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -7853,7 +7853,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -7861,7 +7861,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -7869,7 +7869,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -7877,7 +7877,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="13" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -7885,7 +7885,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -7893,7 +7893,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -7901,7 +7901,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -7909,7 +7909,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -7917,7 +7917,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -7925,7 +7925,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -7933,7 +7933,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -7941,7 +7941,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -7949,7 +7949,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -7957,7 +7957,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="13" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -7965,7 +7965,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -7973,7 +7973,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="13" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -7981,7 +7981,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="13" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -7989,7 +7989,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="13" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -7997,7 +7997,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -8005,7 +8005,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -8013,7 +8013,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -8021,7 +8021,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="13" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -8029,7 +8029,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="13" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -8037,7 +8037,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="13" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -8045,7 +8045,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -8053,7 +8053,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="13" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -8061,7 +8061,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -8069,7 +8069,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="13" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -8077,7 +8077,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -8085,7 +8085,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -8093,7 +8093,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -8101,7 +8101,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -8109,7 +8109,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -8117,7 +8117,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="13" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -8125,7 +8125,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -8133,7 +8133,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -8141,7 +8141,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="13" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -8149,7 +8149,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="13" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -8157,7 +8157,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="13" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -8165,7 +8165,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -8173,7 +8173,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="13" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -8181,7 +8181,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="13" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -8189,7 +8189,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="13" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -8197,7 +8197,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -8205,7 +8205,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -8213,7 +8213,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="13" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -8221,7 +8221,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="13" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -8229,7 +8229,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="13" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -8237,7 +8237,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="13" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -8245,7 +8245,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="13" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -8253,7 +8253,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="13" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -8261,7 +8261,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="13" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -8269,7 +8269,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="13" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -8277,7 +8277,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="13" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -8285,7 +8285,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="13" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -8293,7 +8293,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="13" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -8318,169 +8318,169 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999">
       <c r="A1" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I1" t="s">
+        <v>452</v>
+      </c>
+      <c r="J1" t="s">
         <v>453</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>454</v>
-      </c>
-      <c r="K1" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="I2" t="s">
+        <v>455</v>
+      </c>
+      <c r="J2" t="s">
         <v>456</v>
       </c>
-      <c r="J2" t="s">
-        <v>457</v>
-      </c>
       <c r="K2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I3" t="s">
+        <v>457</v>
+      </c>
+      <c r="J3" t="s">
         <v>458</v>
       </c>
-      <c r="J3" t="s">
-        <v>459</v>
-      </c>
       <c r="K3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="18"/>
       <c r="I4" t="s">
+        <v>459</v>
+      </c>
+      <c r="J4" t="s">
         <v>460</v>
       </c>
-      <c r="J4" t="s">
-        <v>461</v>
-      </c>
       <c r="K4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I5" t="s">
+        <v>461</v>
+      </c>
+      <c r="J5" t="s">
         <v>462</v>
       </c>
-      <c r="J5" t="s">
-        <v>463</v>
-      </c>
       <c r="K5" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="18"/>
       <c r="I6" t="s">
+        <v>463</v>
+      </c>
+      <c r="J6" t="s">
         <v>464</v>
       </c>
-      <c r="J6" t="s">
-        <v>465</v>
-      </c>
       <c r="K6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I7" t="s">
+        <v>465</v>
+      </c>
+      <c r="J7" t="s">
         <v>466</v>
       </c>
-      <c r="J7" t="s">
-        <v>467</v>
-      </c>
       <c r="K7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="18"/>
       <c r="I8" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J8" t="s">
+        <v>473</v>
+      </c>
+      <c r="K8" t="s">
         <v>474</v>
-      </c>
-      <c r="K8" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I9" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J9" t="s">
+        <v>475</v>
+      </c>
+      <c r="K9" t="s">
         <v>476</v>
-      </c>
-      <c r="K9" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="I10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J10" t="s">
+        <v>477</v>
+      </c>
+      <c r="K10" t="s">
         <v>478</v>
-      </c>
-      <c r="K10" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="17.399999999999999">
       <c r="A11" s="17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J11" t="s">
+        <v>479</v>
+      </c>
+      <c r="K11" t="s">
         <v>480</v>
-      </c>
-      <c r="K11" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="I12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J12" t="s">
+        <v>481</v>
+      </c>
+      <c r="K12" t="s">
         <v>482</v>
-      </c>
-      <c r="K12" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I13" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="J13" t="s">
+        <v>483</v>
+      </c>
+      <c r="K13" t="s">
         <v>484</v>
-      </c>
-      <c r="K13" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -8488,7 +8488,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -8496,7 +8496,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="19" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -8504,17 +8504,17 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="17.399999999999999">
       <c r="A21" s="17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -8522,7 +8522,7 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="19" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -8530,17 +8530,17 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="19" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="17.399999999999999">
       <c r="A31" s="17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -8548,7 +8548,7 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="19" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -8556,7 +8556,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="19" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -8564,7 +8564,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -8572,17 +8572,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="19" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="17.399999999999999">
       <c r="A43" s="17" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -8590,7 +8590,7 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="19" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="48" spans="1:1">
@@ -8598,7 +8598,7 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="19" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -8606,7 +8606,7 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -8614,147 +8614,147 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="42.3">
       <c r="A59" s="22" t="s">
+        <v>491</v>
+      </c>
+      <c r="B59" s="22" t="s">
         <v>492</v>
       </c>
-      <c r="B59" s="22" t="s">
+      <c r="C59" s="22" t="s">
         <v>493</v>
       </c>
-      <c r="C59" s="22" t="s">
+      <c r="D59" s="22" t="s">
         <v>494</v>
       </c>
-      <c r="D59" s="22" t="s">
+      <c r="E59" s="22" t="s">
         <v>495</v>
       </c>
-      <c r="E59" s="22" t="s">
+      <c r="F59" s="22" t="s">
         <v>496</v>
-      </c>
-      <c r="F59" s="22" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="27.6">
       <c r="A60" s="22" t="s">
+        <v>497</v>
+      </c>
+      <c r="B60" s="23" t="s">
         <v>498</v>
       </c>
-      <c r="B60" s="23" t="s">
+      <c r="C60" s="22" t="s">
         <v>499</v>
       </c>
-      <c r="C60" s="22" t="s">
+      <c r="D60" s="25" t="s">
         <v>500</v>
       </c>
-      <c r="D60" s="25" t="s">
+      <c r="E60" s="23" t="s">
         <v>501</v>
       </c>
-      <c r="E60" s="23" t="s">
+      <c r="F60" s="23" t="s">
         <v>502</v>
-      </c>
-      <c r="F60" s="23" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="27.9">
       <c r="A61" s="22" t="s">
+        <v>503</v>
+      </c>
+      <c r="B61" s="23" t="s">
         <v>504</v>
       </c>
-      <c r="B61" s="23" t="s">
+      <c r="C61" s="22" t="s">
         <v>505</v>
       </c>
-      <c r="C61" s="22" t="s">
+      <c r="D61" s="25" t="s">
         <v>506</v>
       </c>
-      <c r="D61" s="25" t="s">
+      <c r="E61" s="23" t="s">
         <v>507</v>
       </c>
-      <c r="E61" s="23" t="s">
+      <c r="F61" s="23" t="s">
         <v>508</v>
-      </c>
-      <c r="F61" s="23" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="27.6">
       <c r="A62" s="22" t="s">
+        <v>509</v>
+      </c>
+      <c r="B62" s="23" t="s">
         <v>510</v>
       </c>
-      <c r="B62" s="23" t="s">
+      <c r="C62" s="22" t="s">
         <v>511</v>
       </c>
-      <c r="C62" s="22" t="s">
+      <c r="D62" s="25" t="s">
         <v>512</v>
       </c>
-      <c r="D62" s="25" t="s">
+      <c r="E62" s="23" t="s">
         <v>513</v>
       </c>
-      <c r="E62" s="23" t="s">
-        <v>514</v>
-      </c>
       <c r="F62" s="23" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="27.6">
       <c r="A63" s="22" t="s">
+        <v>514</v>
+      </c>
+      <c r="B63" s="23" t="s">
         <v>515</v>
       </c>
-      <c r="B63" s="23" t="s">
+      <c r="C63" s="22" t="s">
         <v>516</v>
       </c>
-      <c r="C63" s="22" t="s">
+      <c r="D63" s="25" t="s">
         <v>517</v>
       </c>
-      <c r="D63" s="25" t="s">
+      <c r="E63" s="23" t="s">
         <v>518</v>
       </c>
-      <c r="E63" s="23" t="s">
+      <c r="F63" s="23" t="s">
         <v>519</v>
-      </c>
-      <c r="F63" s="23" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="27.9">
       <c r="A64" s="22" t="s">
+        <v>520</v>
+      </c>
+      <c r="B64" s="23" t="s">
         <v>521</v>
       </c>
-      <c r="B64" s="23" t="s">
+      <c r="C64" s="22" t="s">
         <v>522</v>
       </c>
-      <c r="C64" s="22" t="s">
+      <c r="D64" s="25" t="s">
         <v>523</v>
       </c>
-      <c r="D64" s="25" t="s">
+      <c r="E64" s="23" t="s">
         <v>524</v>
       </c>
-      <c r="E64" s="23" t="s">
+      <c r="F64" s="23" t="s">
         <v>525</v>
-      </c>
-      <c r="F64" s="23" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="27.6">
       <c r="A65" s="22" t="s">
+        <v>526</v>
+      </c>
+      <c r="B65" s="24" t="s">
         <v>527</v>
       </c>
-      <c r="B65" s="24" t="s">
-        <v>528</v>
-      </c>
       <c r="C65" s="22" t="s">
+        <v>499</v>
+      </c>
+      <c r="D65" s="25" t="s">
         <v>500</v>
       </c>
-      <c r="D65" s="25" t="s">
+      <c r="E65" s="23" t="s">
         <v>501</v>
       </c>
-      <c r="E65" s="23" t="s">
+      <c r="F65" s="23" t="s">
         <v>502</v>
-      </c>
-      <c r="F65" s="23" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="66" spans="1:6">
